--- a/システム開発演習/030-試験/031-単体試験計画書兼結果書.xlsx
+++ b/システム開発演習/030-試験/031-単体試験計画書兼結果書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\システム開発演習\030-試験\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1831EC-307B-4076-9033-686D93F5B6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FDB99E-3DC9-486F-B5CF-562881EC15A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="779" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="164">
   <si>
     <t>システム名称</t>
     <rPh sb="4" eb="6">
@@ -1085,6 +1085,17 @@
   </si>
   <si>
     <t>データシート②</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>髙木</t>
+    <rPh sb="0" eb="2">
+      <t>タカギ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ok</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -1609,7 +1620,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1962,183 +1973,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2233,6 +2067,192 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2627,7 +2647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{449C9348-9E52-44F7-9A2B-4D52FB69C5EC}">
-  <dimension ref="A1:CE72"/>
+  <dimension ref="A1:CC72"/>
   <sheetFormatPr defaultColWidth="2.6640625" defaultRowHeight="9.6"/>
   <cols>
     <col min="1" max="1" width="5.44140625" style="13" customWidth="1"/>
@@ -2635,305 +2655,306 @@
     <col min="5" max="5" width="6.5546875" style="13" customWidth="1"/>
     <col min="6" max="25" width="2.6640625" style="13" customWidth="1"/>
     <col min="26" max="26" width="2.77734375" style="13" customWidth="1"/>
-    <col min="27" max="62" width="2.6640625" style="13"/>
-    <col min="63" max="63" width="2.6640625" style="75"/>
-    <col min="64" max="16384" width="2.6640625" style="13"/>
+    <col min="27" max="60" width="2.6640625" style="13"/>
+    <col min="61" max="61" width="2.6640625" style="13" customWidth="1"/>
+    <col min="62" max="63" width="2.6640625" style="75" customWidth="1"/>
+    <col min="64" max="64" width="2.6640625" style="13" customWidth="1"/>
+    <col min="65" max="65" width="8.109375" style="13" customWidth="1"/>
+    <col min="66" max="16384" width="2.6640625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83" s="12" customFormat="1" ht="14.25" customHeight="1" thickTop="1">
-      <c r="A1" s="142" t="s">
+    <row r="1" spans="1:81" s="12" customFormat="1" ht="14.25" customHeight="1" thickTop="1">
+      <c r="A1" s="210" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="148" t="s">
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="148"/>
-      <c r="S1" s="148"/>
-      <c r="T1" s="148"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
-      <c r="Z1" s="149"/>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
-      <c r="AC1" s="149"/>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="148" t="s">
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="217"/>
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="217"/>
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="217"/>
+      <c r="AE1" s="216" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="148"/>
-      <c r="AG1" s="148"/>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="150">
+      <c r="AF1" s="216"/>
+      <c r="AG1" s="216"/>
+      <c r="AH1" s="216"/>
+      <c r="AI1" s="218">
         <v>45575</v>
       </c>
-      <c r="AJ1" s="150"/>
-      <c r="AK1" s="150"/>
-      <c r="AL1" s="150"/>
-      <c r="AM1" s="150"/>
-      <c r="AN1" s="150"/>
-      <c r="AO1" s="150"/>
-      <c r="AP1" s="150"/>
-      <c r="AQ1" s="150"/>
-      <c r="AR1" s="172" t="s">
+      <c r="AJ1" s="218"/>
+      <c r="AK1" s="218"/>
+      <c r="AL1" s="218"/>
+      <c r="AM1" s="218"/>
+      <c r="AN1" s="218"/>
+      <c r="AO1" s="218"/>
+      <c r="AP1" s="218"/>
+      <c r="AQ1" s="218"/>
+      <c r="AR1" s="196" t="s">
         <v>3</v>
       </c>
-      <c r="AS1" s="173"/>
-      <c r="AT1" s="163"/>
-      <c r="AU1" s="164"/>
-      <c r="AV1" s="165"/>
-      <c r="BK1" s="74"/>
-    </row>
-    <row r="2" spans="1:83" s="12" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A2" s="145"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="169" t="s">
+      <c r="AS1" s="197"/>
+      <c r="AT1" s="187"/>
+      <c r="AU1" s="188"/>
+      <c r="AV1" s="189"/>
+      <c r="BJ1" s="145"/>
+      <c r="BK1" s="145"/>
+    </row>
+    <row r="2" spans="1:81" s="12" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A2" s="213"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="214"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="214"/>
+      <c r="L2" s="214"/>
+      <c r="M2" s="214"/>
+      <c r="N2" s="214"/>
+      <c r="O2" s="214"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="193" t="s">
         <v>0</v>
       </c>
-      <c r="R2" s="169"/>
-      <c r="S2" s="169"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="170" t="s">
+      <c r="R2" s="193"/>
+      <c r="S2" s="193"/>
+      <c r="T2" s="193"/>
+      <c r="U2" s="194" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="170"/>
-      <c r="W2" s="170"/>
-      <c r="X2" s="170"/>
-      <c r="Y2" s="170"/>
-      <c r="Z2" s="170"/>
-      <c r="AA2" s="170"/>
-      <c r="AB2" s="170"/>
-      <c r="AC2" s="170"/>
-      <c r="AD2" s="170"/>
-      <c r="AE2" s="169" t="s">
+      <c r="V2" s="194"/>
+      <c r="W2" s="194"/>
+      <c r="X2" s="194"/>
+      <c r="Y2" s="194"/>
+      <c r="Z2" s="194"/>
+      <c r="AA2" s="194"/>
+      <c r="AB2" s="194"/>
+      <c r="AC2" s="194"/>
+      <c r="AD2" s="194"/>
+      <c r="AE2" s="193" t="s">
         <v>1</v>
       </c>
-      <c r="AF2" s="169"/>
-      <c r="AG2" s="169"/>
-      <c r="AH2" s="169"/>
-      <c r="AI2" s="171" t="s">
+      <c r="AF2" s="193"/>
+      <c r="AG2" s="193"/>
+      <c r="AH2" s="193"/>
+      <c r="AI2" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="AJ2" s="171"/>
-      <c r="AK2" s="171"/>
-      <c r="AL2" s="171"/>
-      <c r="AM2" s="171"/>
-      <c r="AN2" s="171"/>
-      <c r="AO2" s="171"/>
-      <c r="AP2" s="171"/>
-      <c r="AQ2" s="171"/>
-      <c r="AR2" s="174"/>
-      <c r="AS2" s="175"/>
-      <c r="AT2" s="166"/>
-      <c r="AU2" s="167"/>
-      <c r="AV2" s="168"/>
-      <c r="BK2" s="74"/>
-    </row>
-    <row r="3" spans="1:83" ht="10.199999999999999" thickTop="1"/>
-    <row r="4" spans="1:83" ht="10.5" customHeight="1">
-      <c r="A4" s="151" t="s">
+      <c r="AJ2" s="195"/>
+      <c r="AK2" s="195"/>
+      <c r="AL2" s="195"/>
+      <c r="AM2" s="195"/>
+      <c r="AN2" s="195"/>
+      <c r="AO2" s="195"/>
+      <c r="AP2" s="195"/>
+      <c r="AQ2" s="195"/>
+      <c r="AR2" s="198"/>
+      <c r="AS2" s="199"/>
+      <c r="AT2" s="190"/>
+      <c r="AU2" s="191"/>
+      <c r="AV2" s="192"/>
+      <c r="BJ2" s="145"/>
+      <c r="BK2" s="145"/>
+    </row>
+    <row r="3" spans="1:81" ht="10.199999999999999" thickTop="1"/>
+    <row r="4" spans="1:81" ht="10.5" customHeight="1">
+      <c r="A4" s="200" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="153" t="s">
+      <c r="B4" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="153"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="153"/>
-      <c r="F4" s="154" t="s">
+      <c r="C4" s="179"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="180" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="155"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="155"/>
-      <c r="L4" s="155"/>
-      <c r="M4" s="155"/>
-      <c r="N4" s="155"/>
-      <c r="O4" s="155"/>
-      <c r="P4" s="155"/>
-      <c r="Q4" s="155"/>
-      <c r="R4" s="156" t="s">
+      <c r="G4" s="202"/>
+      <c r="H4" s="202"/>
+      <c r="I4" s="202"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="202"/>
+      <c r="L4" s="202"/>
+      <c r="M4" s="202"/>
+      <c r="N4" s="202"/>
+      <c r="O4" s="202"/>
+      <c r="P4" s="202"/>
+      <c r="Q4" s="202"/>
+      <c r="R4" s="203" t="s">
         <v>22</v>
       </c>
-      <c r="S4" s="157"/>
-      <c r="T4" s="157"/>
-      <c r="U4" s="157"/>
-      <c r="V4" s="157"/>
-      <c r="W4" s="158"/>
-      <c r="X4" s="162" t="s">
+      <c r="S4" s="204"/>
+      <c r="T4" s="204"/>
+      <c r="U4" s="204"/>
+      <c r="V4" s="204"/>
+      <c r="W4" s="205"/>
+      <c r="X4" s="209" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" s="153"/>
-      <c r="Z4" s="153"/>
-      <c r="AA4" s="153"/>
-      <c r="AB4" s="153"/>
-      <c r="AC4" s="153"/>
-      <c r="AD4" s="153"/>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="153"/>
-      <c r="AG4" s="153"/>
-      <c r="AH4" s="153"/>
-      <c r="AI4" s="153"/>
-      <c r="AJ4" s="153"/>
-      <c r="AK4" s="153"/>
-      <c r="AL4" s="176" t="s">
+      <c r="Y4" s="179"/>
+      <c r="Z4" s="179"/>
+      <c r="AA4" s="179"/>
+      <c r="AB4" s="179"/>
+      <c r="AC4" s="179"/>
+      <c r="AD4" s="179"/>
+      <c r="AE4" s="179"/>
+      <c r="AF4" s="179"/>
+      <c r="AG4" s="179"/>
+      <c r="AH4" s="179"/>
+      <c r="AI4" s="179"/>
+      <c r="AJ4" s="179"/>
+      <c r="AK4" s="179"/>
+      <c r="AL4" s="178" t="s">
         <v>12</v>
       </c>
-      <c r="AM4" s="176"/>
-      <c r="AN4" s="176"/>
-      <c r="AO4" s="176"/>
-      <c r="AP4" s="176"/>
-      <c r="AQ4" s="176"/>
-      <c r="AR4" s="176"/>
-      <c r="AS4" s="176"/>
-      <c r="AT4" s="176"/>
-      <c r="AU4" s="176"/>
-      <c r="AV4" s="176"/>
-      <c r="AW4" s="176"/>
-      <c r="AX4" s="177" t="s">
+      <c r="AM4" s="178"/>
+      <c r="AN4" s="178"/>
+      <c r="AO4" s="178"/>
+      <c r="AP4" s="178"/>
+      <c r="AQ4" s="178"/>
+      <c r="AR4" s="178"/>
+      <c r="AS4" s="178"/>
+      <c r="AT4" s="178"/>
+      <c r="AU4" s="178"/>
+      <c r="AV4" s="178"/>
+      <c r="AW4" s="178"/>
+      <c r="AX4" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="AY4" s="178"/>
-      <c r="AZ4" s="178"/>
-      <c r="BA4" s="178"/>
-      <c r="BB4" s="178"/>
-      <c r="BC4" s="178"/>
-      <c r="BD4" s="178"/>
-      <c r="BE4" s="178"/>
-      <c r="BF4" s="178"/>
-      <c r="BG4" s="178"/>
-      <c r="BH4" s="179"/>
-      <c r="BI4" s="177" t="s">
+      <c r="AY4" s="182"/>
+      <c r="AZ4" s="182"/>
+      <c r="BA4" s="182"/>
+      <c r="BB4" s="182"/>
+      <c r="BC4" s="182"/>
+      <c r="BD4" s="182"/>
+      <c r="BE4" s="182"/>
+      <c r="BF4" s="182"/>
+      <c r="BG4" s="182"/>
+      <c r="BH4" s="183"/>
+      <c r="BI4" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="BJ4" s="178"/>
-      <c r="BK4" s="178"/>
-      <c r="BL4" s="179"/>
-      <c r="BM4" s="176" t="s">
+      <c r="BJ4" s="182"/>
+      <c r="BK4" s="182"/>
+      <c r="BL4" s="183"/>
+      <c r="BM4" s="178" t="s">
         <v>15</v>
       </c>
-      <c r="BN4" s="176"/>
-      <c r="BO4" s="176"/>
-      <c r="BP4" s="176"/>
-      <c r="BQ4" s="176" t="s">
+      <c r="BN4" s="178"/>
+      <c r="BO4" s="178" t="s">
         <v>16</v>
       </c>
-      <c r="BR4" s="176"/>
-      <c r="BS4" s="176"/>
-      <c r="BT4" s="176"/>
-    </row>
-    <row r="5" spans="1:83" ht="10.5" customHeight="1">
-      <c r="A5" s="152"/>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153" t="s">
+      <c r="BP4" s="178"/>
+      <c r="BQ4" s="178"/>
+      <c r="BR4" s="178"/>
+    </row>
+    <row r="5" spans="1:81" ht="10.5" customHeight="1">
+      <c r="A5" s="201"/>
+      <c r="B5" s="179"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153" t="s">
+      <c r="G5" s="179"/>
+      <c r="H5" s="179"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="179"/>
+      <c r="L5" s="179" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="154"/>
-      <c r="R5" s="159"/>
-      <c r="S5" s="160"/>
-      <c r="T5" s="160"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="160"/>
-      <c r="W5" s="161"/>
-      <c r="X5" s="162"/>
-      <c r="Y5" s="153"/>
-      <c r="Z5" s="153"/>
-      <c r="AA5" s="153"/>
-      <c r="AB5" s="153"/>
-      <c r="AC5" s="153"/>
-      <c r="AD5" s="153"/>
-      <c r="AE5" s="153"/>
-      <c r="AF5" s="153"/>
-      <c r="AG5" s="153"/>
-      <c r="AH5" s="153"/>
-      <c r="AI5" s="153"/>
-      <c r="AJ5" s="153"/>
-      <c r="AK5" s="153"/>
-      <c r="AL5" s="176"/>
-      <c r="AM5" s="176"/>
-      <c r="AN5" s="176"/>
-      <c r="AO5" s="176"/>
-      <c r="AP5" s="176"/>
-      <c r="AQ5" s="176"/>
-      <c r="AR5" s="176"/>
-      <c r="AS5" s="176"/>
-      <c r="AT5" s="176"/>
-      <c r="AU5" s="176"/>
-      <c r="AV5" s="176"/>
-      <c r="AW5" s="176"/>
-      <c r="AX5" s="180"/>
-      <c r="AY5" s="181"/>
-      <c r="AZ5" s="181"/>
-      <c r="BA5" s="181"/>
-      <c r="BB5" s="181"/>
-      <c r="BC5" s="181"/>
-      <c r="BD5" s="181"/>
-      <c r="BE5" s="181"/>
-      <c r="BF5" s="181"/>
-      <c r="BG5" s="181"/>
-      <c r="BH5" s="182"/>
-      <c r="BI5" s="180"/>
-      <c r="BJ5" s="181"/>
-      <c r="BK5" s="181"/>
-      <c r="BL5" s="182"/>
-      <c r="BM5" s="176"/>
-      <c r="BN5" s="176"/>
-      <c r="BO5" s="176"/>
-      <c r="BP5" s="176"/>
-      <c r="BQ5" s="176"/>
-      <c r="BR5" s="176"/>
-      <c r="BS5" s="176"/>
-      <c r="BT5" s="176"/>
-    </row>
-    <row r="6" spans="1:83" ht="10.5" customHeight="1">
+      <c r="M5" s="179"/>
+      <c r="N5" s="179"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="179"/>
+      <c r="Q5" s="180"/>
+      <c r="R5" s="206"/>
+      <c r="S5" s="207"/>
+      <c r="T5" s="207"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="207"/>
+      <c r="W5" s="208"/>
+      <c r="X5" s="209"/>
+      <c r="Y5" s="179"/>
+      <c r="Z5" s="179"/>
+      <c r="AA5" s="179"/>
+      <c r="AB5" s="179"/>
+      <c r="AC5" s="179"/>
+      <c r="AD5" s="179"/>
+      <c r="AE5" s="179"/>
+      <c r="AF5" s="179"/>
+      <c r="AG5" s="179"/>
+      <c r="AH5" s="179"/>
+      <c r="AI5" s="179"/>
+      <c r="AJ5" s="179"/>
+      <c r="AK5" s="179"/>
+      <c r="AL5" s="178"/>
+      <c r="AM5" s="178"/>
+      <c r="AN5" s="178"/>
+      <c r="AO5" s="178"/>
+      <c r="AP5" s="178"/>
+      <c r="AQ5" s="178"/>
+      <c r="AR5" s="178"/>
+      <c r="AS5" s="178"/>
+      <c r="AT5" s="178"/>
+      <c r="AU5" s="178"/>
+      <c r="AV5" s="178"/>
+      <c r="AW5" s="178"/>
+      <c r="AX5" s="184"/>
+      <c r="AY5" s="185"/>
+      <c r="AZ5" s="185"/>
+      <c r="BA5" s="185"/>
+      <c r="BB5" s="185"/>
+      <c r="BC5" s="185"/>
+      <c r="BD5" s="185"/>
+      <c r="BE5" s="185"/>
+      <c r="BF5" s="185"/>
+      <c r="BG5" s="185"/>
+      <c r="BH5" s="186"/>
+      <c r="BI5" s="184"/>
+      <c r="BJ5" s="185"/>
+      <c r="BK5" s="185"/>
+      <c r="BL5" s="186"/>
+      <c r="BM5" s="178"/>
+      <c r="BN5" s="178"/>
+      <c r="BO5" s="178"/>
+      <c r="BP5" s="178"/>
+      <c r="BQ5" s="178"/>
+      <c r="BR5" s="178"/>
+    </row>
+    <row r="6" spans="1:81" ht="10.5" customHeight="1">
       <c r="A6" s="26">
         <v>1</v>
       </c>
@@ -3010,23 +3031,27 @@
       <c r="BF6" s="17"/>
       <c r="BG6" s="17"/>
       <c r="BH6" s="17"/>
-      <c r="BI6" s="39"/>
-      <c r="BJ6" s="40"/>
-      <c r="BK6" s="40"/>
+      <c r="BI6" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ6" s="238"/>
+      <c r="BK6" s="238"/>
       <c r="BL6" s="38"/>
-      <c r="BM6" s="17"/>
+      <c r="BM6" s="237">
+        <v>45594</v>
+      </c>
       <c r="BN6" s="17"/>
-      <c r="BO6" s="17"/>
-      <c r="BP6" s="17"/>
-      <c r="BQ6" s="39"/>
-      <c r="BR6" s="40"/>
-      <c r="BS6" s="40"/>
-      <c r="BT6" s="38"/>
-      <c r="CE6" s="13" t="s">
+      <c r="BO6" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP6" s="40"/>
+      <c r="BQ6" s="40"/>
+      <c r="BR6" s="38"/>
+      <c r="CC6" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:83" ht="10.5" customHeight="1">
+    <row r="7" spans="1:81" ht="10.5" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="43" t="s">
         <v>65</v>
@@ -3097,16 +3122,14 @@
       <c r="BJ7" s="17"/>
       <c r="BK7" s="17"/>
       <c r="BL7" s="19"/>
-      <c r="BM7" s="17"/>
+      <c r="BM7" s="14"/>
       <c r="BN7" s="17"/>
-      <c r="BO7" s="17"/>
+      <c r="BO7" s="14"/>
       <c r="BP7" s="17"/>
-      <c r="BQ7" s="14"/>
-      <c r="BR7" s="17"/>
-      <c r="BS7" s="17"/>
-      <c r="BT7" s="19"/>
-    </row>
-    <row r="8" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BQ7" s="17"/>
+      <c r="BR7" s="19"/>
+    </row>
+    <row r="8" spans="1:81" ht="10.5" customHeight="1">
       <c r="A8" s="18"/>
       <c r="B8" s="43"/>
       <c r="C8" s="1"/>
@@ -3171,16 +3194,14 @@
       <c r="BJ8" s="17"/>
       <c r="BK8" s="17"/>
       <c r="BL8" s="19"/>
-      <c r="BM8" s="17"/>
+      <c r="BM8" s="14"/>
       <c r="BN8" s="17"/>
-      <c r="BO8" s="17"/>
-      <c r="BP8" s="17"/>
-      <c r="BQ8" s="41"/>
-      <c r="BR8" s="24"/>
-      <c r="BS8" s="24"/>
-      <c r="BT8" s="25"/>
-    </row>
-    <row r="9" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BO8" s="41"/>
+      <c r="BP8" s="24"/>
+      <c r="BQ8" s="24"/>
+      <c r="BR8" s="25"/>
+    </row>
+    <row r="9" spans="1:81" ht="10.5" customHeight="1">
       <c r="A9" s="26">
         <v>2</v>
       </c>
@@ -3257,20 +3278,24 @@
       <c r="BF9" s="40"/>
       <c r="BG9" s="40"/>
       <c r="BH9" s="40"/>
-      <c r="BI9" s="39"/>
-      <c r="BJ9" s="40"/>
-      <c r="BK9" s="40"/>
+      <c r="BI9" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ9" s="238"/>
+      <c r="BK9" s="238"/>
       <c r="BL9" s="38"/>
-      <c r="BM9" s="40"/>
-      <c r="BN9" s="40"/>
-      <c r="BO9" s="40"/>
-      <c r="BP9" s="38"/>
-      <c r="BQ9" s="14"/>
-      <c r="BR9" s="17"/>
-      <c r="BS9" s="17"/>
-      <c r="BT9" s="19"/>
-    </row>
-    <row r="10" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BM9" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN9" s="38"/>
+      <c r="BO9" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP9" s="17"/>
+      <c r="BQ9" s="17"/>
+      <c r="BR9" s="19"/>
+    </row>
+    <row r="10" spans="1:81" ht="10.5" customHeight="1">
       <c r="A10" s="18"/>
       <c r="B10" s="43" t="s">
         <v>79</v>
@@ -3341,16 +3366,14 @@
       <c r="BJ10" s="17"/>
       <c r="BK10" s="17"/>
       <c r="BL10" s="19"/>
-      <c r="BM10" s="17"/>
+      <c r="BM10" s="14"/>
       <c r="BN10" s="17"/>
-      <c r="BO10" s="17"/>
+      <c r="BO10" s="14"/>
       <c r="BP10" s="17"/>
-      <c r="BQ10" s="14"/>
-      <c r="BR10" s="17"/>
-      <c r="BS10" s="17"/>
-      <c r="BT10" s="19"/>
-    </row>
-    <row r="11" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BQ10" s="17"/>
+      <c r="BR10" s="19"/>
+    </row>
+    <row r="11" spans="1:81" ht="10.5" customHeight="1">
       <c r="A11" s="18"/>
       <c r="B11" s="33"/>
       <c r="C11" s="3"/>
@@ -3417,16 +3440,14 @@
       <c r="BJ11" s="17"/>
       <c r="BK11" s="17"/>
       <c r="BL11" s="19"/>
-      <c r="BM11" s="17"/>
+      <c r="BM11" s="14"/>
       <c r="BN11" s="17"/>
-      <c r="BO11" s="17"/>
+      <c r="BO11" s="14"/>
       <c r="BP11" s="17"/>
-      <c r="BQ11" s="14"/>
-      <c r="BR11" s="17"/>
-      <c r="BS11" s="17"/>
-      <c r="BT11" s="19"/>
-    </row>
-    <row r="12" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BQ11" s="17"/>
+      <c r="BR11" s="19"/>
+    </row>
+    <row r="12" spans="1:81" ht="10.5" customHeight="1">
       <c r="A12" s="26">
         <v>3</v>
       </c>
@@ -3503,20 +3524,24 @@
       <c r="BF12" s="40"/>
       <c r="BG12" s="40"/>
       <c r="BH12" s="40"/>
-      <c r="BI12" s="39"/>
-      <c r="BJ12" s="40"/>
-      <c r="BK12" s="40"/>
+      <c r="BI12" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ12" s="238"/>
+      <c r="BK12" s="238"/>
       <c r="BL12" s="38"/>
-      <c r="BM12" s="40"/>
+      <c r="BM12" s="237">
+        <v>45594</v>
+      </c>
       <c r="BN12" s="40"/>
-      <c r="BO12" s="40"/>
+      <c r="BO12" s="39" t="s">
+        <v>162</v>
+      </c>
       <c r="BP12" s="40"/>
-      <c r="BQ12" s="39"/>
-      <c r="BR12" s="40"/>
-      <c r="BS12" s="40"/>
-      <c r="BT12" s="38"/>
-    </row>
-    <row r="13" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BQ12" s="40"/>
+      <c r="BR12" s="38"/>
+    </row>
+    <row r="13" spans="1:81" ht="10.5" customHeight="1">
       <c r="A13" s="18"/>
       <c r="B13" s="43" t="s">
         <v>78</v>
@@ -3587,16 +3612,14 @@
       <c r="BJ13" s="17"/>
       <c r="BK13" s="17"/>
       <c r="BL13" s="19"/>
-      <c r="BM13" s="17"/>
+      <c r="BM13" s="14"/>
       <c r="BN13" s="17"/>
-      <c r="BO13" s="17"/>
+      <c r="BO13" s="14"/>
       <c r="BP13" s="17"/>
-      <c r="BQ13" s="14"/>
-      <c r="BR13" s="17"/>
-      <c r="BS13" s="17"/>
-      <c r="BT13" s="19"/>
-    </row>
-    <row r="14" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BQ13" s="17"/>
+      <c r="BR13" s="19"/>
+    </row>
+    <row r="14" spans="1:81" ht="10.5" customHeight="1">
       <c r="A14" s="73"/>
       <c r="B14" s="54"/>
       <c r="C14" s="55"/>
@@ -3663,16 +3686,14 @@
       <c r="BJ14" s="24"/>
       <c r="BK14" s="24"/>
       <c r="BL14" s="25"/>
-      <c r="BM14" s="24"/>
+      <c r="BM14" s="41"/>
       <c r="BN14" s="24"/>
-      <c r="BO14" s="24"/>
+      <c r="BO14" s="41"/>
       <c r="BP14" s="24"/>
-      <c r="BQ14" s="41"/>
-      <c r="BR14" s="24"/>
-      <c r="BS14" s="24"/>
-      <c r="BT14" s="25"/>
-    </row>
-    <row r="15" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BQ14" s="24"/>
+      <c r="BR14" s="25"/>
+    </row>
+    <row r="15" spans="1:81" ht="10.5" customHeight="1">
       <c r="A15" s="18">
         <v>4</v>
       </c>
@@ -3749,20 +3770,24 @@
       <c r="BF15" s="17"/>
       <c r="BG15" s="17"/>
       <c r="BH15" s="17"/>
-      <c r="BI15" s="14"/>
-      <c r="BJ15" s="17"/>
-      <c r="BK15" s="17"/>
+      <c r="BI15" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ15" s="239"/>
+      <c r="BK15" s="239"/>
       <c r="BL15" s="19"/>
-      <c r="BM15" s="17"/>
+      <c r="BM15" s="237">
+        <v>45594</v>
+      </c>
       <c r="BN15" s="17"/>
-      <c r="BO15" s="17"/>
+      <c r="BO15" s="39" t="s">
+        <v>162</v>
+      </c>
       <c r="BP15" s="17"/>
-      <c r="BQ15" s="14"/>
-      <c r="BR15" s="17"/>
-      <c r="BS15" s="17"/>
-      <c r="BT15" s="19"/>
-    </row>
-    <row r="16" spans="1:83" ht="10.5" customHeight="1">
+      <c r="BQ15" s="17"/>
+      <c r="BR15" s="19"/>
+    </row>
+    <row r="16" spans="1:81" ht="10.5" customHeight="1">
       <c r="A16" s="18"/>
       <c r="B16" s="43" t="s">
         <v>80</v>
@@ -3833,16 +3858,14 @@
       <c r="BJ16" s="17"/>
       <c r="BK16" s="17"/>
       <c r="BL16" s="19"/>
-      <c r="BM16" s="17"/>
+      <c r="BM16" s="14"/>
       <c r="BN16" s="17"/>
-      <c r="BO16" s="17"/>
+      <c r="BO16" s="14"/>
       <c r="BP16" s="17"/>
-      <c r="BQ16" s="14"/>
-      <c r="BR16" s="17"/>
-      <c r="BS16" s="17"/>
-      <c r="BT16" s="19"/>
-    </row>
-    <row r="17" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ16" s="17"/>
+      <c r="BR16" s="19"/>
+    </row>
+    <row r="17" spans="1:70" ht="10.5" customHeight="1">
       <c r="A17" s="18"/>
       <c r="B17" s="43"/>
       <c r="C17" s="1"/>
@@ -3909,16 +3932,14 @@
       <c r="BJ17" s="17"/>
       <c r="BK17" s="17"/>
       <c r="BL17" s="19"/>
-      <c r="BM17" s="17"/>
+      <c r="BM17" s="14"/>
       <c r="BN17" s="17"/>
-      <c r="BO17" s="17"/>
+      <c r="BO17" s="14"/>
       <c r="BP17" s="17"/>
-      <c r="BQ17" s="14"/>
-      <c r="BR17" s="17"/>
-      <c r="BS17" s="17"/>
-      <c r="BT17" s="19"/>
-    </row>
-    <row r="18" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ17" s="17"/>
+      <c r="BR17" s="19"/>
+    </row>
+    <row r="18" spans="1:70" ht="10.5" customHeight="1">
       <c r="A18" s="26">
         <v>5</v>
       </c>
@@ -3995,20 +4016,24 @@
       <c r="BF18" s="40"/>
       <c r="BG18" s="40"/>
       <c r="BH18" s="40"/>
-      <c r="BI18" s="39"/>
-      <c r="BJ18" s="40"/>
-      <c r="BK18" s="40"/>
+      <c r="BI18" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ18" s="238"/>
+      <c r="BK18" s="238"/>
       <c r="BL18" s="38"/>
-      <c r="BM18" s="40"/>
+      <c r="BM18" s="237">
+        <v>45594</v>
+      </c>
       <c r="BN18" s="40"/>
-      <c r="BO18" s="40"/>
+      <c r="BO18" s="39" t="s">
+        <v>162</v>
+      </c>
       <c r="BP18" s="40"/>
-      <c r="BQ18" s="39"/>
-      <c r="BR18" s="40"/>
-      <c r="BS18" s="40"/>
-      <c r="BT18" s="38"/>
-    </row>
-    <row r="19" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ18" s="40"/>
+      <c r="BR18" s="38"/>
+    </row>
+    <row r="19" spans="1:70" ht="10.5" customHeight="1">
       <c r="A19" s="18"/>
       <c r="B19" s="43" t="s">
         <v>80</v>
@@ -4079,16 +4104,14 @@
       <c r="BJ19" s="17"/>
       <c r="BK19" s="17"/>
       <c r="BL19" s="19"/>
-      <c r="BM19" s="17"/>
+      <c r="BM19" s="14"/>
       <c r="BN19" s="17"/>
-      <c r="BO19" s="17"/>
+      <c r="BO19" s="14"/>
       <c r="BP19" s="17"/>
-      <c r="BQ19" s="14"/>
-      <c r="BR19" s="17"/>
-      <c r="BS19" s="17"/>
-      <c r="BT19" s="19"/>
-    </row>
-    <row r="20" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ19" s="17"/>
+      <c r="BR19" s="19"/>
+    </row>
+    <row r="20" spans="1:70" ht="10.5" customHeight="1">
       <c r="A20" s="18"/>
       <c r="B20" s="33"/>
       <c r="C20" s="3"/>
@@ -4155,16 +4178,14 @@
       <c r="BJ20" s="17"/>
       <c r="BK20" s="17"/>
       <c r="BL20" s="19"/>
-      <c r="BM20" s="17"/>
+      <c r="BM20" s="14"/>
       <c r="BN20" s="17"/>
-      <c r="BO20" s="17"/>
+      <c r="BO20" s="14"/>
       <c r="BP20" s="17"/>
-      <c r="BQ20" s="14"/>
-      <c r="BR20" s="17"/>
-      <c r="BS20" s="17"/>
-      <c r="BT20" s="19"/>
-    </row>
-    <row r="21" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ20" s="17"/>
+      <c r="BR20" s="19"/>
+    </row>
+    <row r="21" spans="1:70" ht="10.5" customHeight="1">
       <c r="A21" s="73"/>
       <c r="B21" s="97"/>
       <c r="C21" s="95"/>
@@ -4231,16 +4252,14 @@
       <c r="BJ21" s="24"/>
       <c r="BK21" s="24"/>
       <c r="BL21" s="25"/>
-      <c r="BM21" s="24"/>
+      <c r="BM21" s="41"/>
       <c r="BN21" s="24"/>
-      <c r="BO21" s="24"/>
+      <c r="BO21" s="41"/>
       <c r="BP21" s="24"/>
-      <c r="BQ21" s="41"/>
-      <c r="BR21" s="24"/>
-      <c r="BS21" s="24"/>
-      <c r="BT21" s="25"/>
-    </row>
-    <row r="22" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ21" s="24"/>
+      <c r="BR21" s="25"/>
+    </row>
+    <row r="22" spans="1:70" ht="10.5" customHeight="1">
       <c r="A22" s="26">
         <v>6</v>
       </c>
@@ -4317,20 +4336,24 @@
       <c r="BF22" s="40"/>
       <c r="BG22" s="40"/>
       <c r="BH22" s="40"/>
-      <c r="BI22" s="39"/>
-      <c r="BJ22" s="40"/>
-      <c r="BK22" s="40"/>
+      <c r="BI22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ22" s="238"/>
+      <c r="BK22" s="238"/>
       <c r="BL22" s="38"/>
-      <c r="BM22" s="40"/>
+      <c r="BM22" s="237">
+        <v>45594</v>
+      </c>
       <c r="BN22" s="40"/>
-      <c r="BO22" s="40"/>
+      <c r="BO22" s="39" t="s">
+        <v>162</v>
+      </c>
       <c r="BP22" s="40"/>
-      <c r="BQ22" s="39"/>
-      <c r="BR22" s="40"/>
-      <c r="BS22" s="40"/>
-      <c r="BT22" s="38"/>
-    </row>
-    <row r="23" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ22" s="40"/>
+      <c r="BR22" s="38"/>
+    </row>
+    <row r="23" spans="1:70" ht="10.5" customHeight="1">
       <c r="A23" s="18"/>
       <c r="B23" s="33" t="s">
         <v>112</v>
@@ -4401,16 +4424,14 @@
       <c r="BJ23" s="17"/>
       <c r="BK23" s="17"/>
       <c r="BL23" s="19"/>
-      <c r="BM23" s="17"/>
+      <c r="BM23" s="14"/>
       <c r="BN23" s="17"/>
-      <c r="BO23" s="17"/>
+      <c r="BO23" s="14"/>
       <c r="BP23" s="17"/>
-      <c r="BQ23" s="14"/>
-      <c r="BR23" s="17"/>
-      <c r="BS23" s="17"/>
-      <c r="BT23" s="19"/>
-    </row>
-    <row r="24" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ23" s="17"/>
+      <c r="BR23" s="19"/>
+    </row>
+    <row r="24" spans="1:70" ht="10.5" customHeight="1">
       <c r="A24" s="18"/>
       <c r="B24" s="33" t="s">
         <v>113</v>
@@ -4479,16 +4500,14 @@
       <c r="BJ24" s="17"/>
       <c r="BK24" s="17"/>
       <c r="BL24" s="19"/>
-      <c r="BM24" s="17"/>
+      <c r="BM24" s="14"/>
       <c r="BN24" s="17"/>
-      <c r="BO24" s="17"/>
+      <c r="BO24" s="14"/>
       <c r="BP24" s="17"/>
-      <c r="BQ24" s="14"/>
-      <c r="BR24" s="17"/>
-      <c r="BS24" s="17"/>
-      <c r="BT24" s="19"/>
-    </row>
-    <row r="25" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ24" s="17"/>
+      <c r="BR24" s="19"/>
+    </row>
+    <row r="25" spans="1:70" ht="10.5" customHeight="1">
       <c r="A25" s="73"/>
       <c r="B25" s="97"/>
       <c r="C25" s="95"/>
@@ -4555,16 +4574,14 @@
       <c r="BJ25" s="24"/>
       <c r="BK25" s="24"/>
       <c r="BL25" s="25"/>
-      <c r="BM25" s="24"/>
+      <c r="BM25" s="41"/>
       <c r="BN25" s="24"/>
-      <c r="BO25" s="24"/>
+      <c r="BO25" s="41"/>
       <c r="BP25" s="24"/>
-      <c r="BQ25" s="41"/>
-      <c r="BR25" s="24"/>
-      <c r="BS25" s="24"/>
-      <c r="BT25" s="25"/>
-    </row>
-    <row r="26" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ25" s="24"/>
+      <c r="BR25" s="25"/>
+    </row>
+    <row r="26" spans="1:70" ht="10.5" customHeight="1">
       <c r="A26" s="20">
         <v>7</v>
       </c>
@@ -4641,20 +4658,24 @@
       <c r="BF26" s="17"/>
       <c r="BG26" s="17"/>
       <c r="BH26" s="17"/>
-      <c r="BI26" s="14"/>
-      <c r="BJ26" s="17"/>
-      <c r="BK26" s="17"/>
+      <c r="BI26" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ26" s="239"/>
+      <c r="BK26" s="239"/>
       <c r="BL26" s="19"/>
-      <c r="BM26" s="17"/>
+      <c r="BM26" s="237">
+        <v>45594</v>
+      </c>
       <c r="BN26" s="17"/>
-      <c r="BO26" s="17"/>
+      <c r="BO26" s="39" t="s">
+        <v>162</v>
+      </c>
       <c r="BP26" s="17"/>
-      <c r="BQ26" s="14"/>
-      <c r="BR26" s="17"/>
-      <c r="BS26" s="17"/>
-      <c r="BT26" s="19"/>
-    </row>
-    <row r="27" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ26" s="17"/>
+      <c r="BR26" s="19"/>
+    </row>
+    <row r="27" spans="1:70" ht="10.5" customHeight="1">
       <c r="A27" s="20"/>
       <c r="B27" s="34" t="s">
         <v>114</v>
@@ -4727,14 +4748,12 @@
       <c r="BL27" s="19"/>
       <c r="BM27" s="17"/>
       <c r="BN27" s="17"/>
-      <c r="BO27" s="17"/>
+      <c r="BO27" s="14"/>
       <c r="BP27" s="17"/>
-      <c r="BQ27" s="14"/>
-      <c r="BR27" s="17"/>
-      <c r="BS27" s="17"/>
-      <c r="BT27" s="19"/>
-    </row>
-    <row r="28" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ27" s="17"/>
+      <c r="BR27" s="19"/>
+    </row>
+    <row r="28" spans="1:70" ht="10.5" customHeight="1">
       <c r="A28" s="20"/>
       <c r="B28" s="34"/>
       <c r="C28" s="9"/>
@@ -4805,14 +4824,12 @@
       <c r="BL28" s="19"/>
       <c r="BM28" s="17"/>
       <c r="BN28" s="17"/>
-      <c r="BO28" s="17"/>
+      <c r="BO28" s="14"/>
       <c r="BP28" s="17"/>
-      <c r="BQ28" s="14"/>
-      <c r="BR28" s="17"/>
-      <c r="BS28" s="17"/>
-      <c r="BT28" s="19"/>
-    </row>
-    <row r="29" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ28" s="17"/>
+      <c r="BR28" s="19"/>
+    </row>
+    <row r="29" spans="1:70" ht="10.5" customHeight="1">
       <c r="A29" s="20"/>
       <c r="B29" s="34"/>
       <c r="C29" s="9"/>
@@ -4883,14 +4900,12 @@
       <c r="BL29" s="19"/>
       <c r="BM29" s="17"/>
       <c r="BN29" s="17"/>
-      <c r="BO29" s="17"/>
+      <c r="BO29" s="14"/>
       <c r="BP29" s="17"/>
-      <c r="BQ29" s="14"/>
-      <c r="BR29" s="17"/>
-      <c r="BS29" s="17"/>
-      <c r="BT29" s="19"/>
-    </row>
-    <row r="30" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ29" s="17"/>
+      <c r="BR29" s="19"/>
+    </row>
+    <row r="30" spans="1:70" ht="10.5" customHeight="1">
       <c r="A30" s="20"/>
       <c r="B30" s="44"/>
       <c r="C30" s="7"/>
@@ -4961,14 +4976,12 @@
       <c r="BL30" s="19"/>
       <c r="BM30" s="17"/>
       <c r="BN30" s="17"/>
-      <c r="BO30" s="17"/>
+      <c r="BO30" s="14"/>
       <c r="BP30" s="17"/>
-      <c r="BQ30" s="14"/>
-      <c r="BR30" s="17"/>
-      <c r="BS30" s="17"/>
-      <c r="BT30" s="19"/>
-    </row>
-    <row r="31" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ30" s="17"/>
+      <c r="BR30" s="19"/>
+    </row>
+    <row r="31" spans="1:70" ht="10.5" customHeight="1">
       <c r="A31" s="20"/>
       <c r="B31" s="34"/>
       <c r="C31" s="9"/>
@@ -5037,14 +5050,12 @@
       <c r="BL31" s="19"/>
       <c r="BM31" s="17"/>
       <c r="BN31" s="17"/>
-      <c r="BO31" s="17"/>
+      <c r="BO31" s="14"/>
       <c r="BP31" s="17"/>
-      <c r="BQ31" s="14"/>
-      <c r="BR31" s="17"/>
-      <c r="BS31" s="17"/>
-      <c r="BT31" s="19"/>
-    </row>
-    <row r="32" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ31" s="17"/>
+      <c r="BR31" s="19"/>
+    </row>
+    <row r="32" spans="1:70" ht="10.5" customHeight="1">
       <c r="A32" s="20"/>
       <c r="B32" s="34"/>
       <c r="C32" s="9"/>
@@ -5113,14 +5124,12 @@
       <c r="BL32" s="19"/>
       <c r="BM32" s="17"/>
       <c r="BN32" s="17"/>
-      <c r="BO32" s="17"/>
+      <c r="BO32" s="14"/>
       <c r="BP32" s="17"/>
-      <c r="BQ32" s="14"/>
-      <c r="BR32" s="17"/>
-      <c r="BS32" s="17"/>
-      <c r="BT32" s="19"/>
-    </row>
-    <row r="33" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BQ32" s="17"/>
+      <c r="BR32" s="19"/>
+    </row>
+    <row r="33" spans="1:70" ht="10.5" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="34"/>
       <c r="C33" s="9"/>
@@ -5183,13 +5192,13 @@
       <c r="BF33" s="111"/>
       <c r="BH33" s="19"/>
       <c r="BL33" s="19"/>
-      <c r="BP33" s="19"/>
+      <c r="BN33" s="19"/>
+      <c r="BO33" s="17"/>
+      <c r="BP33" s="17"/>
       <c r="BQ33" s="17"/>
-      <c r="BR33" s="17"/>
-      <c r="BS33" s="17"/>
-      <c r="BT33" s="19"/>
-    </row>
-    <row r="34" spans="1:72" ht="10.5" customHeight="1">
+      <c r="BR33" s="19"/>
+    </row>
+    <row r="34" spans="1:70" ht="10.5" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="34"/>
       <c r="C34" s="9"/>
@@ -5252,14 +5261,14 @@
       <c r="BF34" s="111"/>
       <c r="BH34" s="19"/>
       <c r="BL34" s="19"/>
-      <c r="BP34" s="19"/>
+      <c r="BN34" s="19"/>
+      <c r="BO34" s="17"/>
+      <c r="BP34" s="17"/>
       <c r="BQ34" s="17"/>
-      <c r="BR34" s="17"/>
-      <c r="BS34" s="17"/>
-      <c r="BT34" s="19"/>
-    </row>
-    <row r="35" spans="1:72" ht="10.5" customHeight="1">
-      <c r="A35" s="203"/>
+      <c r="BR34" s="19"/>
+    </row>
+    <row r="35" spans="1:70" ht="10.5" customHeight="1">
+      <c r="A35" s="144"/>
       <c r="B35" s="35"/>
       <c r="C35" s="21"/>
       <c r="D35" s="21"/>
@@ -5282,19 +5291,19 @@
       <c r="U35" s="22"/>
       <c r="V35" s="21"/>
       <c r="W35" s="30"/>
-      <c r="X35" s="235"/>
-      <c r="Y35" s="208"/>
-      <c r="Z35" s="209"/>
-      <c r="AA35" s="209"/>
-      <c r="AB35" s="209"/>
-      <c r="AC35" s="209"/>
-      <c r="AD35" s="208"/>
-      <c r="AE35" s="208"/>
-      <c r="AF35" s="208"/>
-      <c r="AG35" s="208"/>
-      <c r="AH35" s="208"/>
-      <c r="AI35" s="208"/>
-      <c r="AJ35" s="208"/>
+      <c r="X35" s="176"/>
+      <c r="Y35" s="149"/>
+      <c r="Z35" s="150"/>
+      <c r="AA35" s="150"/>
+      <c r="AB35" s="150"/>
+      <c r="AC35" s="150"/>
+      <c r="AD35" s="149"/>
+      <c r="AE35" s="149"/>
+      <c r="AF35" s="149"/>
+      <c r="AG35" s="149"/>
+      <c r="AH35" s="149"/>
+      <c r="AI35" s="149"/>
+      <c r="AJ35" s="149"/>
       <c r="AK35" s="30"/>
       <c r="AL35" s="35"/>
       <c r="AM35" s="21"/>
@@ -5308,17 +5317,17 @@
       <c r="AU35" s="21"/>
       <c r="AV35" s="21"/>
       <c r="AW35" s="25"/>
-      <c r="AX35" s="207" t="s">
+      <c r="AX35" s="148" t="s">
         <v>98</v>
       </c>
-      <c r="AY35" s="206"/>
-      <c r="AZ35" s="206"/>
-      <c r="BA35" s="206"/>
-      <c r="BB35" s="206"/>
-      <c r="BC35" s="206"/>
-      <c r="BD35" s="206"/>
-      <c r="BE35" s="206"/>
-      <c r="BF35" s="208"/>
+      <c r="AY35" s="147"/>
+      <c r="AZ35" s="147"/>
+      <c r="BA35" s="147"/>
+      <c r="BB35" s="147"/>
+      <c r="BC35" s="147"/>
+      <c r="BD35" s="147"/>
+      <c r="BE35" s="147"/>
+      <c r="BF35" s="149"/>
       <c r="BG35" s="24"/>
       <c r="BH35" s="25"/>
       <c r="BI35" s="24"/>
@@ -5326,2891 +5335,2887 @@
       <c r="BK35" s="24"/>
       <c r="BL35" s="25"/>
       <c r="BM35" s="24"/>
-      <c r="BN35" s="24"/>
+      <c r="BN35" s="25"/>
       <c r="BO35" s="24"/>
-      <c r="BP35" s="25"/>
+      <c r="BP35" s="24"/>
       <c r="BQ35" s="24"/>
-      <c r="BR35" s="24"/>
-      <c r="BS35" s="24"/>
-      <c r="BT35" s="25"/>
-    </row>
-    <row r="36" spans="1:72" ht="12">
-      <c r="A36" s="230" t="s">
+      <c r="BR35" s="25"/>
+    </row>
+    <row r="36" spans="1:70" ht="12">
+      <c r="A36" s="171" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="217" t="s">
+      <c r="B36" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C36" s="226"/>
-      <c r="D36" s="226"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="217" t="s">
+      <c r="C36" s="167"/>
+      <c r="D36" s="167"/>
+      <c r="E36" s="159"/>
+      <c r="F36" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="226"/>
-      <c r="H36" s="226"/>
-      <c r="I36" s="226"/>
+      <c r="G36" s="167"/>
+      <c r="H36" s="167"/>
+      <c r="I36" s="167"/>
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
-      <c r="L36" s="217" t="s">
+      <c r="L36" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M36" s="226"/>
-      <c r="N36" s="226"/>
-      <c r="O36" s="226"/>
-      <c r="P36" s="226"/>
-      <c r="Q36" s="218"/>
-      <c r="R36" s="217" t="s">
+      <c r="M36" s="167"/>
+      <c r="N36" s="167"/>
+      <c r="O36" s="167"/>
+      <c r="P36" s="167"/>
+      <c r="Q36" s="159"/>
+      <c r="R36" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S36" s="226"/>
-      <c r="T36" s="226"/>
-      <c r="U36" s="226"/>
-      <c r="V36" s="226"/>
-      <c r="W36" s="226"/>
-      <c r="X36" s="217" t="s">
+      <c r="S36" s="167"/>
+      <c r="T36" s="167"/>
+      <c r="U36" s="167"/>
+      <c r="V36" s="167"/>
+      <c r="W36" s="167"/>
+      <c r="X36" s="158" t="s">
         <v>120</v>
       </c>
-      <c r="Y36" s="215"/>
-      <c r="Z36" s="216"/>
-      <c r="AA36" s="216"/>
-      <c r="AB36" s="216"/>
-      <c r="AC36" s="216"/>
-      <c r="AD36" s="215"/>
-      <c r="AE36" s="215"/>
-      <c r="AF36" s="215"/>
-      <c r="AG36" s="215"/>
-      <c r="AH36" s="215"/>
-      <c r="AI36" s="215"/>
-      <c r="AJ36" s="215"/>
-      <c r="AK36" s="213"/>
-      <c r="AL36" s="214" t="s">
+      <c r="Y36" s="156"/>
+      <c r="Z36" s="157"/>
+      <c r="AA36" s="157"/>
+      <c r="AB36" s="157"/>
+      <c r="AC36" s="157"/>
+      <c r="AD36" s="156"/>
+      <c r="AE36" s="156"/>
+      <c r="AF36" s="156"/>
+      <c r="AG36" s="156"/>
+      <c r="AH36" s="156"/>
+      <c r="AI36" s="156"/>
+      <c r="AJ36" s="156"/>
+      <c r="AK36" s="154"/>
+      <c r="AL36" s="155" t="s">
         <v>121</v>
       </c>
-      <c r="AM36" s="213"/>
-      <c r="AN36" s="213"/>
-      <c r="AO36" s="213"/>
-      <c r="AP36" s="213"/>
-      <c r="AQ36" s="213"/>
-      <c r="AR36" s="213"/>
-      <c r="AS36" s="213"/>
-      <c r="AT36" s="215"/>
-      <c r="AU36" s="215"/>
-      <c r="AV36" s="215"/>
-      <c r="AW36" s="215"/>
-      <c r="AX36" s="214" t="s">
+      <c r="AM36" s="154"/>
+      <c r="AN36" s="154"/>
+      <c r="AO36" s="154"/>
+      <c r="AP36" s="154"/>
+      <c r="AQ36" s="154"/>
+      <c r="AR36" s="154"/>
+      <c r="AS36" s="154"/>
+      <c r="AT36" s="156"/>
+      <c r="AU36" s="156"/>
+      <c r="AV36" s="156"/>
+      <c r="AW36" s="156"/>
+      <c r="AX36" s="155" t="s">
         <v>122</v>
       </c>
-      <c r="AY36" s="213"/>
-      <c r="AZ36" s="213"/>
-      <c r="BA36" s="213"/>
-      <c r="BF36" s="213"/>
-      <c r="BG36" s="213"/>
-      <c r="BH36" s="213"/>
-      <c r="BI36" s="214"/>
-      <c r="BJ36" s="213"/>
-      <c r="BK36" s="213"/>
-      <c r="BL36" s="213"/>
-      <c r="BM36" s="214"/>
-      <c r="BN36" s="213"/>
-      <c r="BO36" s="213"/>
-      <c r="BP36" s="212"/>
-      <c r="BQ36" s="214"/>
-      <c r="BR36" s="213"/>
-      <c r="BS36" s="213"/>
-      <c r="BT36" s="212"/>
-    </row>
-    <row r="37" spans="1:72" ht="12">
-      <c r="A37" s="230"/>
-      <c r="B37" s="217"/>
-      <c r="C37" s="226"/>
-      <c r="D37" s="226"/>
-      <c r="E37" s="218"/>
-      <c r="F37" s="217"/>
-      <c r="G37" s="226"/>
-      <c r="H37" s="226"/>
-      <c r="I37" s="226"/>
+      <c r="AY36" s="154"/>
+      <c r="AZ36" s="154"/>
+      <c r="BA36" s="154"/>
+      <c r="BF36" s="154"/>
+      <c r="BG36" s="154"/>
+      <c r="BH36" s="154"/>
+      <c r="BI36" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ36" s="239"/>
+      <c r="BK36" s="239"/>
+      <c r="BL36" s="154"/>
+      <c r="BM36" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN36" s="153"/>
+      <c r="BO36" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP36" s="154"/>
+      <c r="BQ36" s="154"/>
+      <c r="BR36" s="153"/>
+    </row>
+    <row r="37" spans="1:70" ht="12">
+      <c r="A37" s="171"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="167"/>
+      <c r="D37" s="167"/>
+      <c r="E37" s="159"/>
+      <c r="F37" s="158"/>
+      <c r="G37" s="167"/>
+      <c r="H37" s="167"/>
+      <c r="I37" s="167"/>
       <c r="J37" s="17"/>
       <c r="K37" s="17"/>
-      <c r="L37" s="217"/>
-      <c r="M37" s="226"/>
-      <c r="N37" s="226"/>
-      <c r="O37" s="226"/>
-      <c r="P37" s="226"/>
-      <c r="Q37" s="218"/>
-      <c r="R37" s="217"/>
-      <c r="S37" s="226"/>
-      <c r="T37" s="226"/>
-      <c r="U37" s="226"/>
-      <c r="V37" s="226"/>
-      <c r="W37" s="226"/>
-      <c r="X37" s="217" t="s">
+      <c r="L37" s="158"/>
+      <c r="M37" s="167"/>
+      <c r="N37" s="167"/>
+      <c r="O37" s="167"/>
+      <c r="P37" s="167"/>
+      <c r="Q37" s="159"/>
+      <c r="R37" s="158"/>
+      <c r="S37" s="167"/>
+      <c r="T37" s="167"/>
+      <c r="U37" s="167"/>
+      <c r="V37" s="167"/>
+      <c r="W37" s="167"/>
+      <c r="X37" s="158" t="s">
         <v>123</v>
       </c>
-      <c r="Y37" s="215"/>
-      <c r="Z37" s="216"/>
-      <c r="AA37" s="216"/>
-      <c r="AB37" s="216"/>
-      <c r="AC37" s="216"/>
-      <c r="AD37" s="215"/>
-      <c r="AE37" s="215"/>
-      <c r="AF37" s="215"/>
-      <c r="AG37" s="215"/>
-      <c r="AH37" s="215"/>
-      <c r="AI37" s="215"/>
-      <c r="AJ37" s="215"/>
-      <c r="AK37" s="213"/>
-      <c r="AL37" s="214" t="s">
+      <c r="Y37" s="156"/>
+      <c r="Z37" s="157"/>
+      <c r="AA37" s="157"/>
+      <c r="AB37" s="157"/>
+      <c r="AC37" s="157"/>
+      <c r="AD37" s="156"/>
+      <c r="AE37" s="156"/>
+      <c r="AF37" s="156"/>
+      <c r="AG37" s="156"/>
+      <c r="AH37" s="156"/>
+      <c r="AI37" s="156"/>
+      <c r="AJ37" s="156"/>
+      <c r="AK37" s="154"/>
+      <c r="AL37" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM37" s="213"/>
-      <c r="AN37" s="213"/>
-      <c r="AO37" s="213"/>
-      <c r="AP37" s="213"/>
-      <c r="AQ37" s="213"/>
-      <c r="AR37" s="213"/>
-      <c r="AS37" s="213"/>
-      <c r="AT37" s="215"/>
-      <c r="AU37" s="215"/>
-      <c r="AV37" s="215"/>
-      <c r="AW37" s="215"/>
-      <c r="AX37" s="214"/>
-      <c r="AY37" s="213"/>
-      <c r="AZ37" s="213"/>
-      <c r="BA37" s="213"/>
-      <c r="BF37" s="213"/>
-      <c r="BG37" s="213"/>
-      <c r="BH37" s="213"/>
-      <c r="BI37" s="214"/>
-      <c r="BJ37" s="213"/>
-      <c r="BK37" s="213"/>
-      <c r="BL37" s="213"/>
-      <c r="BM37" s="214"/>
-      <c r="BN37" s="213"/>
-      <c r="BO37" s="213"/>
-      <c r="BP37" s="212"/>
-      <c r="BQ37" s="214"/>
-      <c r="BR37" s="213"/>
-      <c r="BS37" s="213"/>
-      <c r="BT37" s="212"/>
-    </row>
-    <row r="38" spans="1:72" ht="12">
-      <c r="A38" s="231"/>
-      <c r="B38" s="210"/>
-      <c r="C38" s="208"/>
-      <c r="D38" s="208"/>
-      <c r="E38" s="211"/>
-      <c r="F38" s="210"/>
-      <c r="G38" s="208"/>
-      <c r="H38" s="208"/>
-      <c r="I38" s="208"/>
+      <c r="AM37" s="154"/>
+      <c r="AN37" s="154"/>
+      <c r="AO37" s="154"/>
+      <c r="AP37" s="154"/>
+      <c r="AQ37" s="154"/>
+      <c r="AR37" s="154"/>
+      <c r="AS37" s="154"/>
+      <c r="AT37" s="156"/>
+      <c r="AU37" s="156"/>
+      <c r="AV37" s="156"/>
+      <c r="AW37" s="156"/>
+      <c r="AX37" s="155"/>
+      <c r="AY37" s="154"/>
+      <c r="AZ37" s="154"/>
+      <c r="BA37" s="154"/>
+      <c r="BF37" s="154"/>
+      <c r="BG37" s="154"/>
+      <c r="BH37" s="154"/>
+      <c r="BI37" s="155"/>
+      <c r="BJ37" s="173"/>
+      <c r="BK37" s="173"/>
+      <c r="BL37" s="154"/>
+      <c r="BM37" s="155"/>
+      <c r="BN37" s="153"/>
+      <c r="BO37" s="155"/>
+      <c r="BP37" s="154"/>
+      <c r="BQ37" s="154"/>
+      <c r="BR37" s="153"/>
+    </row>
+    <row r="38" spans="1:70" ht="12">
+      <c r="A38" s="172"/>
+      <c r="B38" s="151"/>
+      <c r="C38" s="149"/>
+      <c r="D38" s="149"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="151"/>
+      <c r="G38" s="149"/>
+      <c r="H38" s="149"/>
+      <c r="I38" s="149"/>
       <c r="J38" s="24"/>
       <c r="K38" s="25"/>
-      <c r="L38" s="210"/>
-      <c r="M38" s="208"/>
-      <c r="N38" s="208"/>
-      <c r="O38" s="208"/>
-      <c r="P38" s="208"/>
-      <c r="Q38" s="211"/>
-      <c r="R38" s="210"/>
-      <c r="S38" s="208"/>
-      <c r="T38" s="208"/>
-      <c r="U38" s="208"/>
-      <c r="V38" s="208"/>
-      <c r="W38" s="208"/>
-      <c r="X38" s="210"/>
-      <c r="Y38" s="208"/>
-      <c r="Z38" s="209"/>
-      <c r="AA38" s="209"/>
-      <c r="AB38" s="209"/>
-      <c r="AC38" s="209"/>
-      <c r="AD38" s="208"/>
-      <c r="AE38" s="208"/>
-      <c r="AF38" s="208"/>
-      <c r="AG38" s="208"/>
-      <c r="AH38" s="208"/>
-      <c r="AI38" s="208"/>
-      <c r="AJ38" s="208"/>
-      <c r="AK38" s="206"/>
-      <c r="AL38" s="207"/>
-      <c r="AM38" s="206"/>
-      <c r="AN38" s="206"/>
-      <c r="AO38" s="206"/>
-      <c r="AP38" s="206"/>
-      <c r="AQ38" s="206"/>
-      <c r="AR38" s="206"/>
-      <c r="AS38" s="206"/>
-      <c r="AT38" s="208"/>
-      <c r="AU38" s="208"/>
-      <c r="AV38" s="208"/>
-      <c r="AW38" s="208"/>
-      <c r="AX38" s="207"/>
-      <c r="AY38" s="206"/>
-      <c r="AZ38" s="206"/>
+      <c r="L38" s="151"/>
+      <c r="M38" s="149"/>
+      <c r="N38" s="149"/>
+      <c r="O38" s="149"/>
+      <c r="P38" s="149"/>
+      <c r="Q38" s="152"/>
+      <c r="R38" s="151"/>
+      <c r="S38" s="149"/>
+      <c r="T38" s="149"/>
+      <c r="U38" s="149"/>
+      <c r="V38" s="149"/>
+      <c r="W38" s="149"/>
+      <c r="X38" s="151"/>
+      <c r="Y38" s="149"/>
+      <c r="Z38" s="150"/>
+      <c r="AA38" s="150"/>
+      <c r="AB38" s="150"/>
+      <c r="AC38" s="150"/>
+      <c r="AD38" s="149"/>
+      <c r="AE38" s="149"/>
+      <c r="AF38" s="149"/>
+      <c r="AG38" s="149"/>
+      <c r="AH38" s="149"/>
+      <c r="AI38" s="149"/>
+      <c r="AJ38" s="149"/>
+      <c r="AK38" s="147"/>
+      <c r="AL38" s="148"/>
+      <c r="AM38" s="147"/>
+      <c r="AN38" s="147"/>
+      <c r="AO38" s="147"/>
+      <c r="AP38" s="147"/>
+      <c r="AQ38" s="147"/>
+      <c r="AR38" s="147"/>
+      <c r="AS38" s="147"/>
+      <c r="AT38" s="149"/>
+      <c r="AU38" s="149"/>
+      <c r="AV38" s="149"/>
+      <c r="AW38" s="149"/>
+      <c r="AX38" s="148"/>
+      <c r="AY38" s="147"/>
+      <c r="AZ38" s="147"/>
       <c r="BA38" s="23"/>
       <c r="BB38" s="23"/>
       <c r="BC38" s="23"/>
       <c r="BD38" s="21"/>
       <c r="BE38" s="21"/>
-      <c r="BF38" s="206"/>
-      <c r="BG38" s="206"/>
-      <c r="BH38" s="206"/>
-      <c r="BI38" s="207"/>
-      <c r="BJ38" s="206"/>
-      <c r="BK38" s="206"/>
-      <c r="BL38" s="206"/>
-      <c r="BM38" s="207"/>
-      <c r="BN38" s="206"/>
-      <c r="BO38" s="206"/>
-      <c r="BP38" s="205"/>
-      <c r="BQ38" s="207"/>
-      <c r="BR38" s="206"/>
-      <c r="BS38" s="206"/>
-      <c r="BT38" s="205"/>
-    </row>
-    <row r="39" spans="1:72" ht="12">
-      <c r="A39" s="230" t="s">
+      <c r="BF38" s="147"/>
+      <c r="BG38" s="147"/>
+      <c r="BH38" s="147"/>
+      <c r="BI38" s="148"/>
+      <c r="BJ38" s="147"/>
+      <c r="BK38" s="147"/>
+      <c r="BL38" s="147"/>
+      <c r="BM38" s="148"/>
+      <c r="BN38" s="146"/>
+      <c r="BO38" s="148"/>
+      <c r="BP38" s="147"/>
+      <c r="BQ38" s="147"/>
+      <c r="BR38" s="146"/>
+    </row>
+    <row r="39" spans="1:70" ht="12">
+      <c r="A39" s="171" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="217" t="s">
+      <c r="B39" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C39" s="226"/>
-      <c r="D39" s="226"/>
-      <c r="E39" s="218"/>
-      <c r="F39" s="217" t="s">
+      <c r="C39" s="167"/>
+      <c r="D39" s="167"/>
+      <c r="E39" s="159"/>
+      <c r="F39" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G39" s="226"/>
-      <c r="H39" s="226"/>
-      <c r="I39" s="226"/>
+      <c r="G39" s="167"/>
+      <c r="H39" s="167"/>
+      <c r="I39" s="167"/>
       <c r="J39" s="17"/>
       <c r="K39" s="17"/>
-      <c r="L39" s="217" t="s">
+      <c r="L39" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M39" s="226"/>
-      <c r="N39" s="226"/>
-      <c r="O39" s="226"/>
-      <c r="P39" s="226"/>
-      <c r="Q39" s="218"/>
-      <c r="R39" s="217" t="s">
+      <c r="M39" s="167"/>
+      <c r="N39" s="167"/>
+      <c r="O39" s="167"/>
+      <c r="P39" s="167"/>
+      <c r="Q39" s="159"/>
+      <c r="R39" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S39" s="226"/>
-      <c r="T39" s="226"/>
-      <c r="U39" s="226"/>
-      <c r="V39" s="226"/>
-      <c r="W39" s="226"/>
-      <c r="X39" s="217" t="s">
+      <c r="S39" s="167"/>
+      <c r="T39" s="167"/>
+      <c r="U39" s="167"/>
+      <c r="V39" s="167"/>
+      <c r="W39" s="167"/>
+      <c r="X39" s="158" t="s">
         <v>126</v>
       </c>
-      <c r="Y39" s="215"/>
-      <c r="Z39" s="216"/>
-      <c r="AA39" s="216"/>
-      <c r="AB39" s="216"/>
-      <c r="AC39" s="216"/>
-      <c r="AD39" s="215"/>
-      <c r="AE39" s="215"/>
-      <c r="AF39" s="215"/>
-      <c r="AG39" s="215"/>
-      <c r="AH39" s="215"/>
-      <c r="AI39" s="215"/>
-      <c r="AJ39" s="215"/>
-      <c r="AK39" s="213"/>
-      <c r="AL39" s="214" t="s">
+      <c r="Y39" s="156"/>
+      <c r="Z39" s="157"/>
+      <c r="AA39" s="157"/>
+      <c r="AB39" s="157"/>
+      <c r="AC39" s="157"/>
+      <c r="AD39" s="156"/>
+      <c r="AE39" s="156"/>
+      <c r="AF39" s="156"/>
+      <c r="AG39" s="156"/>
+      <c r="AH39" s="156"/>
+      <c r="AI39" s="156"/>
+      <c r="AJ39" s="156"/>
+      <c r="AK39" s="154"/>
+      <c r="AL39" s="155" t="s">
         <v>121</v>
       </c>
-      <c r="AM39" s="213"/>
-      <c r="AN39" s="213"/>
-      <c r="AO39" s="213"/>
-      <c r="AP39" s="213"/>
-      <c r="AQ39" s="213"/>
-      <c r="AR39" s="213"/>
-      <c r="AS39" s="213"/>
-      <c r="AT39" s="215"/>
-      <c r="AU39" s="215"/>
-      <c r="AV39" s="215"/>
-      <c r="AW39" s="215"/>
-      <c r="AX39" s="214" t="s">
+      <c r="AM39" s="154"/>
+      <c r="AN39" s="154"/>
+      <c r="AO39" s="154"/>
+      <c r="AP39" s="154"/>
+      <c r="AQ39" s="154"/>
+      <c r="AR39" s="154"/>
+      <c r="AS39" s="154"/>
+      <c r="AT39" s="156"/>
+      <c r="AU39" s="156"/>
+      <c r="AV39" s="156"/>
+      <c r="AW39" s="156"/>
+      <c r="AX39" s="155" t="s">
         <v>122</v>
       </c>
-      <c r="AY39" s="213"/>
-      <c r="AZ39" s="213"/>
-      <c r="BA39" s="213"/>
-      <c r="BF39" s="213"/>
-      <c r="BG39" s="213"/>
-      <c r="BH39" s="213"/>
-      <c r="BI39" s="214"/>
-      <c r="BJ39" s="213"/>
-      <c r="BK39" s="213"/>
-      <c r="BL39" s="213"/>
-      <c r="BM39" s="214"/>
-      <c r="BN39" s="213"/>
-      <c r="BO39" s="213"/>
-      <c r="BP39" s="212"/>
-      <c r="BQ39" s="214"/>
-      <c r="BR39" s="213"/>
-      <c r="BS39" s="213"/>
-      <c r="BT39" s="212"/>
-    </row>
-    <row r="40" spans="1:72" ht="12">
-      <c r="A40" s="230"/>
-      <c r="B40" s="217"/>
-      <c r="C40" s="226"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="218"/>
-      <c r="F40" s="217"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="226"/>
-      <c r="I40" s="226"/>
+      <c r="AY39" s="154"/>
+      <c r="AZ39" s="154"/>
+      <c r="BA39" s="154"/>
+      <c r="BF39" s="154"/>
+      <c r="BG39" s="154"/>
+      <c r="BH39" s="154"/>
+      <c r="BI39" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ39" s="239"/>
+      <c r="BK39" s="239"/>
+      <c r="BL39" s="154"/>
+      <c r="BM39" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN39" s="153"/>
+      <c r="BO39" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP39" s="154"/>
+      <c r="BQ39" s="154"/>
+      <c r="BR39" s="153"/>
+    </row>
+    <row r="40" spans="1:70" ht="12">
+      <c r="A40" s="171"/>
+      <c r="B40" s="158"/>
+      <c r="C40" s="167"/>
+      <c r="D40" s="167"/>
+      <c r="E40" s="159"/>
+      <c r="F40" s="158"/>
+      <c r="G40" s="167"/>
+      <c r="H40" s="167"/>
+      <c r="I40" s="167"/>
       <c r="J40" s="17"/>
       <c r="K40" s="17"/>
-      <c r="L40" s="217"/>
-      <c r="M40" s="226"/>
-      <c r="N40" s="226"/>
-      <c r="O40" s="226"/>
-      <c r="P40" s="226"/>
-      <c r="Q40" s="218"/>
-      <c r="R40" s="217"/>
-      <c r="S40" s="226"/>
-      <c r="T40" s="226"/>
-      <c r="U40" s="226"/>
-      <c r="V40" s="226"/>
-      <c r="W40" s="226"/>
-      <c r="X40" s="217" t="s">
+      <c r="L40" s="158"/>
+      <c r="M40" s="167"/>
+      <c r="N40" s="167"/>
+      <c r="O40" s="167"/>
+      <c r="P40" s="167"/>
+      <c r="Q40" s="159"/>
+      <c r="R40" s="158"/>
+      <c r="S40" s="167"/>
+      <c r="T40" s="167"/>
+      <c r="U40" s="167"/>
+      <c r="V40" s="167"/>
+      <c r="W40" s="167"/>
+      <c r="X40" s="158" t="s">
         <v>123</v>
       </c>
-      <c r="Y40" s="215"/>
-      <c r="Z40" s="216"/>
-      <c r="AA40" s="216"/>
-      <c r="AB40" s="216"/>
-      <c r="AC40" s="216"/>
-      <c r="AD40" s="215"/>
-      <c r="AE40" s="215"/>
-      <c r="AF40" s="215"/>
-      <c r="AG40" s="215"/>
-      <c r="AH40" s="215"/>
-      <c r="AI40" s="215"/>
-      <c r="AJ40" s="215"/>
-      <c r="AK40" s="213"/>
-      <c r="AL40" s="214" t="s">
+      <c r="Y40" s="156"/>
+      <c r="Z40" s="157"/>
+      <c r="AA40" s="157"/>
+      <c r="AB40" s="157"/>
+      <c r="AC40" s="157"/>
+      <c r="AD40" s="156"/>
+      <c r="AE40" s="156"/>
+      <c r="AF40" s="156"/>
+      <c r="AG40" s="156"/>
+      <c r="AH40" s="156"/>
+      <c r="AI40" s="156"/>
+      <c r="AJ40" s="156"/>
+      <c r="AK40" s="154"/>
+      <c r="AL40" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM40" s="213"/>
-      <c r="AN40" s="213"/>
-      <c r="AO40" s="213"/>
-      <c r="AP40" s="213"/>
-      <c r="AQ40" s="213"/>
-      <c r="AR40" s="213"/>
-      <c r="AS40" s="213"/>
-      <c r="AT40" s="215"/>
-      <c r="AU40" s="215"/>
-      <c r="AV40" s="215"/>
-      <c r="AW40" s="215"/>
-      <c r="AX40" s="214"/>
-      <c r="AY40" s="213"/>
-      <c r="AZ40" s="213"/>
-      <c r="BA40" s="213"/>
-      <c r="BF40" s="213"/>
-      <c r="BG40" s="213"/>
-      <c r="BH40" s="213"/>
-      <c r="BI40" s="214"/>
-      <c r="BJ40" s="213"/>
-      <c r="BK40" s="213"/>
-      <c r="BL40" s="213"/>
-      <c r="BM40" s="214"/>
-      <c r="BN40" s="213"/>
-      <c r="BO40" s="213"/>
-      <c r="BP40" s="212"/>
-      <c r="BQ40" s="214"/>
-      <c r="BR40" s="213"/>
-      <c r="BS40" s="213"/>
-      <c r="BT40" s="212"/>
-    </row>
-    <row r="41" spans="1:72" ht="12">
-      <c r="A41" s="230"/>
-      <c r="B41" s="217"/>
-      <c r="C41" s="226"/>
-      <c r="D41" s="226"/>
-      <c r="E41" s="218"/>
-      <c r="F41" s="217"/>
-      <c r="G41" s="226"/>
-      <c r="H41" s="226"/>
-      <c r="I41" s="208"/>
+      <c r="AM40" s="154"/>
+      <c r="AN40" s="154"/>
+      <c r="AO40" s="154"/>
+      <c r="AP40" s="154"/>
+      <c r="AQ40" s="154"/>
+      <c r="AR40" s="154"/>
+      <c r="AS40" s="154"/>
+      <c r="AT40" s="156"/>
+      <c r="AU40" s="156"/>
+      <c r="AV40" s="156"/>
+      <c r="AW40" s="156"/>
+      <c r="AX40" s="155"/>
+      <c r="AY40" s="154"/>
+      <c r="AZ40" s="154"/>
+      <c r="BA40" s="154"/>
+      <c r="BF40" s="154"/>
+      <c r="BG40" s="154"/>
+      <c r="BH40" s="154"/>
+      <c r="BI40" s="155"/>
+      <c r="BJ40" s="173"/>
+      <c r="BK40" s="173"/>
+      <c r="BL40" s="154"/>
+      <c r="BM40" s="155"/>
+      <c r="BN40" s="153"/>
+      <c r="BO40" s="155"/>
+      <c r="BP40" s="154"/>
+      <c r="BQ40" s="154"/>
+      <c r="BR40" s="153"/>
+    </row>
+    <row r="41" spans="1:70" ht="12">
+      <c r="A41" s="171"/>
+      <c r="B41" s="158"/>
+      <c r="C41" s="167"/>
+      <c r="D41" s="167"/>
+      <c r="E41" s="159"/>
+      <c r="F41" s="158"/>
+      <c r="G41" s="167"/>
+      <c r="H41" s="167"/>
+      <c r="I41" s="149"/>
       <c r="J41" s="24"/>
       <c r="K41" s="25"/>
-      <c r="L41" s="210"/>
-      <c r="M41" s="208"/>
-      <c r="N41" s="208"/>
-      <c r="O41" s="208"/>
-      <c r="P41" s="208"/>
-      <c r="Q41" s="211"/>
-      <c r="R41" s="210"/>
-      <c r="S41" s="226"/>
-      <c r="T41" s="226"/>
-      <c r="U41" s="226"/>
-      <c r="V41" s="226"/>
-      <c r="W41" s="226"/>
-      <c r="X41" s="217"/>
-      <c r="Y41" s="215"/>
-      <c r="Z41" s="216"/>
-      <c r="AA41" s="216"/>
-      <c r="AB41" s="216"/>
-      <c r="AC41" s="216"/>
-      <c r="AD41" s="215"/>
-      <c r="AE41" s="215"/>
-      <c r="AF41" s="215"/>
-      <c r="AG41" s="215"/>
-      <c r="AH41" s="215"/>
-      <c r="AI41" s="215"/>
-      <c r="AJ41" s="215"/>
-      <c r="AK41" s="213"/>
-      <c r="AL41" s="207"/>
-      <c r="AM41" s="213"/>
-      <c r="AN41" s="213"/>
-      <c r="AO41" s="213"/>
-      <c r="AP41" s="213"/>
-      <c r="AQ41" s="213"/>
-      <c r="AR41" s="213"/>
-      <c r="AS41" s="213"/>
-      <c r="AT41" s="215"/>
-      <c r="AU41" s="215"/>
-      <c r="AV41" s="215"/>
-      <c r="AW41" s="215"/>
-      <c r="AX41" s="214"/>
-      <c r="AY41" s="213"/>
-      <c r="AZ41" s="213"/>
+      <c r="L41" s="151"/>
+      <c r="M41" s="149"/>
+      <c r="N41" s="149"/>
+      <c r="O41" s="149"/>
+      <c r="P41" s="149"/>
+      <c r="Q41" s="152"/>
+      <c r="R41" s="151"/>
+      <c r="S41" s="167"/>
+      <c r="T41" s="167"/>
+      <c r="U41" s="167"/>
+      <c r="V41" s="167"/>
+      <c r="W41" s="167"/>
+      <c r="X41" s="158"/>
+      <c r="Y41" s="156"/>
+      <c r="Z41" s="157"/>
+      <c r="AA41" s="157"/>
+      <c r="AB41" s="157"/>
+      <c r="AC41" s="157"/>
+      <c r="AD41" s="156"/>
+      <c r="AE41" s="156"/>
+      <c r="AF41" s="156"/>
+      <c r="AG41" s="156"/>
+      <c r="AH41" s="156"/>
+      <c r="AI41" s="156"/>
+      <c r="AJ41" s="156"/>
+      <c r="AK41" s="154"/>
+      <c r="AL41" s="148"/>
+      <c r="AM41" s="154"/>
+      <c r="AN41" s="154"/>
+      <c r="AO41" s="154"/>
+      <c r="AP41" s="154"/>
+      <c r="AQ41" s="154"/>
+      <c r="AR41" s="154"/>
+      <c r="AS41" s="154"/>
+      <c r="AT41" s="156"/>
+      <c r="AU41" s="156"/>
+      <c r="AV41" s="156"/>
+      <c r="AW41" s="156"/>
+      <c r="AX41" s="155"/>
+      <c r="AY41" s="154"/>
+      <c r="AZ41" s="154"/>
       <c r="BA41" s="23"/>
       <c r="BB41" s="23"/>
       <c r="BC41" s="23"/>
       <c r="BD41" s="21"/>
       <c r="BE41" s="21"/>
-      <c r="BF41" s="213"/>
-      <c r="BG41" s="213"/>
-      <c r="BH41" s="213"/>
-      <c r="BI41" s="214"/>
-      <c r="BJ41" s="213"/>
-      <c r="BK41" s="213"/>
-      <c r="BL41" s="213"/>
-      <c r="BM41" s="214"/>
-      <c r="BN41" s="213"/>
-      <c r="BO41" s="213"/>
-      <c r="BP41" s="212"/>
-      <c r="BQ41" s="214"/>
-      <c r="BR41" s="213"/>
-      <c r="BS41" s="213"/>
-      <c r="BT41" s="212"/>
-    </row>
-    <row r="42" spans="1:72" ht="12">
-      <c r="A42" s="229" t="s">
+      <c r="BF41" s="154"/>
+      <c r="BG41" s="154"/>
+      <c r="BH41" s="154"/>
+      <c r="BI41" s="155"/>
+      <c r="BJ41" s="173"/>
+      <c r="BK41" s="173"/>
+      <c r="BL41" s="154"/>
+      <c r="BM41" s="155"/>
+      <c r="BN41" s="153"/>
+      <c r="BO41" s="155"/>
+      <c r="BP41" s="154"/>
+      <c r="BQ41" s="154"/>
+      <c r="BR41" s="153"/>
+    </row>
+    <row r="42" spans="1:70" ht="12">
+      <c r="A42" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="B42" s="224" t="s">
+      <c r="B42" s="165" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="222"/>
-      <c r="D42" s="222"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="224" t="s">
+      <c r="C42" s="163"/>
+      <c r="D42" s="163"/>
+      <c r="E42" s="166"/>
+      <c r="F42" s="165" t="s">
         <v>119</v>
       </c>
-      <c r="G42" s="222"/>
-      <c r="H42" s="222"/>
-      <c r="I42" s="226"/>
-      <c r="L42" s="217" t="s">
+      <c r="G42" s="163"/>
+      <c r="H42" s="163"/>
+      <c r="I42" s="167"/>
+      <c r="L42" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M42" s="226"/>
-      <c r="N42" s="226"/>
-      <c r="O42" s="226"/>
-      <c r="P42" s="226"/>
-      <c r="Q42" s="218"/>
-      <c r="R42" s="217" t="s">
+      <c r="M42" s="167"/>
+      <c r="N42" s="167"/>
+      <c r="O42" s="167"/>
+      <c r="P42" s="167"/>
+      <c r="Q42" s="159"/>
+      <c r="R42" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S42" s="222"/>
-      <c r="T42" s="222"/>
-      <c r="U42" s="222"/>
-      <c r="V42" s="222"/>
-      <c r="W42" s="222"/>
-      <c r="X42" s="233" t="s">
+      <c r="S42" s="163"/>
+      <c r="T42" s="163"/>
+      <c r="U42" s="163"/>
+      <c r="V42" s="163"/>
+      <c r="W42" s="163"/>
+      <c r="X42" s="174" t="s">
         <v>128</v>
       </c>
-      <c r="Y42" s="222"/>
-      <c r="Z42" s="223"/>
-      <c r="AA42" s="223"/>
-      <c r="AB42" s="223"/>
-      <c r="AC42" s="223"/>
-      <c r="AD42" s="222"/>
-      <c r="AE42" s="222"/>
-      <c r="AF42" s="222"/>
-      <c r="AG42" s="222"/>
-      <c r="AH42" s="222"/>
-      <c r="AI42" s="222"/>
-      <c r="AJ42" s="222"/>
-      <c r="AK42" s="220"/>
-      <c r="AL42" s="221" t="s">
+      <c r="Y42" s="163"/>
+      <c r="Z42" s="164"/>
+      <c r="AA42" s="164"/>
+      <c r="AB42" s="164"/>
+      <c r="AC42" s="164"/>
+      <c r="AD42" s="163"/>
+      <c r="AE42" s="163"/>
+      <c r="AF42" s="163"/>
+      <c r="AG42" s="163"/>
+      <c r="AH42" s="163"/>
+      <c r="AI42" s="163"/>
+      <c r="AJ42" s="163"/>
+      <c r="AK42" s="161"/>
+      <c r="AL42" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM42" s="220"/>
-      <c r="AN42" s="220"/>
-      <c r="AO42" s="220"/>
-      <c r="AP42" s="220"/>
-      <c r="AQ42" s="220"/>
-      <c r="AR42" s="220"/>
-      <c r="AS42" s="220"/>
-      <c r="AT42" s="222"/>
-      <c r="AU42" s="222"/>
-      <c r="AV42" s="222"/>
-      <c r="AW42" s="222"/>
-      <c r="AX42" s="221" t="s">
+      <c r="AM42" s="161"/>
+      <c r="AN42" s="161"/>
+      <c r="AO42" s="161"/>
+      <c r="AP42" s="161"/>
+      <c r="AQ42" s="161"/>
+      <c r="AR42" s="161"/>
+      <c r="AS42" s="161"/>
+      <c r="AT42" s="163"/>
+      <c r="AU42" s="163"/>
+      <c r="AV42" s="163"/>
+      <c r="AW42" s="163"/>
+      <c r="AX42" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY42" s="220"/>
-      <c r="AZ42" s="220"/>
-      <c r="BA42" s="220"/>
-      <c r="BF42" s="220"/>
-      <c r="BG42" s="220"/>
-      <c r="BH42" s="220"/>
-      <c r="BI42" s="221"/>
-      <c r="BJ42" s="220"/>
-      <c r="BK42" s="220"/>
-      <c r="BL42" s="220"/>
-      <c r="BM42" s="221"/>
-      <c r="BN42" s="220"/>
-      <c r="BO42" s="220"/>
-      <c r="BP42" s="219"/>
-      <c r="BQ42" s="221"/>
-      <c r="BR42" s="220"/>
-      <c r="BS42" s="220"/>
-      <c r="BT42" s="219"/>
-    </row>
-    <row r="43" spans="1:72" ht="12">
-      <c r="A43" s="230"/>
-      <c r="B43" s="217"/>
-      <c r="C43" s="226"/>
-      <c r="D43" s="226"/>
-      <c r="E43" s="218"/>
-      <c r="F43" s="217"/>
-      <c r="G43" s="226"/>
-      <c r="H43" s="226"/>
-      <c r="I43" s="226"/>
-      <c r="L43" s="217"/>
-      <c r="M43" s="226"/>
-      <c r="N43" s="226"/>
-      <c r="O43" s="226"/>
-      <c r="P43" s="226"/>
-      <c r="Q43" s="218"/>
-      <c r="R43" s="217"/>
-      <c r="S43" s="226"/>
-      <c r="T43" s="226"/>
-      <c r="U43" s="226"/>
-      <c r="V43" s="226"/>
-      <c r="W43" s="226"/>
-      <c r="X43" s="234" t="s">
+      <c r="AY42" s="161"/>
+      <c r="AZ42" s="161"/>
+      <c r="BA42" s="161"/>
+      <c r="BF42" s="161"/>
+      <c r="BG42" s="161"/>
+      <c r="BH42" s="161"/>
+      <c r="BI42" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ42" s="238"/>
+      <c r="BK42" s="238"/>
+      <c r="BL42" s="161"/>
+      <c r="BM42" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN42" s="160"/>
+      <c r="BO42" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP42" s="161"/>
+      <c r="BQ42" s="161"/>
+      <c r="BR42" s="160"/>
+    </row>
+    <row r="43" spans="1:70" ht="12">
+      <c r="A43" s="171"/>
+      <c r="B43" s="158"/>
+      <c r="C43" s="167"/>
+      <c r="D43" s="167"/>
+      <c r="E43" s="159"/>
+      <c r="F43" s="158"/>
+      <c r="G43" s="167"/>
+      <c r="H43" s="167"/>
+      <c r="I43" s="167"/>
+      <c r="L43" s="158"/>
+      <c r="M43" s="167"/>
+      <c r="N43" s="167"/>
+      <c r="O43" s="167"/>
+      <c r="P43" s="167"/>
+      <c r="Q43" s="159"/>
+      <c r="R43" s="158"/>
+      <c r="S43" s="167"/>
+      <c r="T43" s="167"/>
+      <c r="U43" s="167"/>
+      <c r="V43" s="167"/>
+      <c r="W43" s="167"/>
+      <c r="X43" s="175" t="s">
         <v>129</v>
       </c>
-      <c r="Y43" s="215"/>
-      <c r="Z43" s="216"/>
-      <c r="AA43" s="216"/>
-      <c r="AB43" s="216"/>
-      <c r="AC43" s="216"/>
-      <c r="AD43" s="215"/>
-      <c r="AE43" s="215"/>
-      <c r="AF43" s="215"/>
-      <c r="AG43" s="215"/>
-      <c r="AH43" s="215"/>
-      <c r="AI43" s="215"/>
-      <c r="AJ43" s="215"/>
-      <c r="AK43" s="213"/>
-      <c r="AL43" s="214" t="s">
+      <c r="Y43" s="156"/>
+      <c r="Z43" s="157"/>
+      <c r="AA43" s="157"/>
+      <c r="AB43" s="157"/>
+      <c r="AC43" s="157"/>
+      <c r="AD43" s="156"/>
+      <c r="AE43" s="156"/>
+      <c r="AF43" s="156"/>
+      <c r="AG43" s="156"/>
+      <c r="AH43" s="156"/>
+      <c r="AI43" s="156"/>
+      <c r="AJ43" s="156"/>
+      <c r="AK43" s="154"/>
+      <c r="AL43" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM43" s="213"/>
-      <c r="AN43" s="213"/>
-      <c r="AO43" s="213"/>
-      <c r="AP43" s="213"/>
-      <c r="AQ43" s="213"/>
-      <c r="AR43" s="213"/>
-      <c r="AS43" s="213"/>
-      <c r="AT43" s="215"/>
-      <c r="AU43" s="215"/>
-      <c r="AV43" s="215"/>
-      <c r="AW43" s="215"/>
-      <c r="AX43" s="214"/>
-      <c r="AY43" s="213"/>
-      <c r="AZ43" s="213"/>
-      <c r="BA43" s="213"/>
-      <c r="BF43" s="213"/>
-      <c r="BG43" s="213"/>
-      <c r="BH43" s="213"/>
-      <c r="BI43" s="214"/>
-      <c r="BJ43" s="213"/>
-      <c r="BK43" s="213"/>
-      <c r="BL43" s="213"/>
-      <c r="BM43" s="214"/>
-      <c r="BN43" s="213"/>
-      <c r="BO43" s="213"/>
-      <c r="BP43" s="212"/>
-      <c r="BQ43" s="214"/>
-      <c r="BR43" s="213"/>
-      <c r="BS43" s="213"/>
-      <c r="BT43" s="212"/>
-    </row>
-    <row r="44" spans="1:72" ht="12">
-      <c r="A44" s="231"/>
-      <c r="B44" s="210"/>
-      <c r="C44" s="208"/>
-      <c r="D44" s="208"/>
-      <c r="E44" s="211"/>
-      <c r="F44" s="210"/>
-      <c r="G44" s="208"/>
-      <c r="H44" s="208"/>
-      <c r="I44" s="208"/>
+      <c r="AM43" s="154"/>
+      <c r="AN43" s="154"/>
+      <c r="AO43" s="154"/>
+      <c r="AP43" s="154"/>
+      <c r="AQ43" s="154"/>
+      <c r="AR43" s="154"/>
+      <c r="AS43" s="154"/>
+      <c r="AT43" s="156"/>
+      <c r="AU43" s="156"/>
+      <c r="AV43" s="156"/>
+      <c r="AW43" s="156"/>
+      <c r="AX43" s="155"/>
+      <c r="AY43" s="154"/>
+      <c r="AZ43" s="154"/>
+      <c r="BA43" s="154"/>
+      <c r="BF43" s="154"/>
+      <c r="BG43" s="154"/>
+      <c r="BH43" s="154"/>
+      <c r="BI43" s="155"/>
+      <c r="BJ43" s="173"/>
+      <c r="BK43" s="173"/>
+      <c r="BL43" s="154"/>
+      <c r="BM43" s="155"/>
+      <c r="BN43" s="153"/>
+      <c r="BO43" s="155"/>
+      <c r="BP43" s="154"/>
+      <c r="BQ43" s="154"/>
+      <c r="BR43" s="153"/>
+    </row>
+    <row r="44" spans="1:70" ht="12">
+      <c r="A44" s="172"/>
+      <c r="B44" s="151"/>
+      <c r="C44" s="149"/>
+      <c r="D44" s="149"/>
+      <c r="E44" s="152"/>
+      <c r="F44" s="151"/>
+      <c r="G44" s="149"/>
+      <c r="H44" s="149"/>
+      <c r="I44" s="149"/>
       <c r="J44" s="24"/>
       <c r="K44" s="25"/>
-      <c r="L44" s="210"/>
-      <c r="M44" s="208"/>
-      <c r="N44" s="208"/>
-      <c r="O44" s="208"/>
-      <c r="P44" s="208"/>
-      <c r="Q44" s="211"/>
-      <c r="R44" s="210"/>
-      <c r="S44" s="208"/>
-      <c r="T44" s="208"/>
-      <c r="U44" s="208"/>
-      <c r="V44" s="208"/>
-      <c r="W44" s="208"/>
-      <c r="X44" s="235"/>
-      <c r="Y44" s="208"/>
-      <c r="Z44" s="209"/>
-      <c r="AA44" s="209"/>
-      <c r="AB44" s="209"/>
-      <c r="AC44" s="209"/>
-      <c r="AD44" s="208"/>
-      <c r="AE44" s="208"/>
-      <c r="AF44" s="208"/>
-      <c r="AG44" s="208"/>
-      <c r="AH44" s="208"/>
-      <c r="AI44" s="208"/>
-      <c r="AJ44" s="208"/>
-      <c r="AK44" s="206"/>
-      <c r="AL44" s="207"/>
-      <c r="AM44" s="206"/>
-      <c r="AN44" s="206"/>
-      <c r="AO44" s="206"/>
-      <c r="AP44" s="206"/>
-      <c r="AQ44" s="206"/>
-      <c r="AR44" s="206"/>
-      <c r="AS44" s="206"/>
-      <c r="AT44" s="208"/>
-      <c r="AU44" s="208"/>
-      <c r="AV44" s="208"/>
-      <c r="AW44" s="208"/>
-      <c r="AX44" s="207"/>
-      <c r="AY44" s="206"/>
-      <c r="AZ44" s="206"/>
-      <c r="BA44" s="206"/>
+      <c r="L44" s="151"/>
+      <c r="M44" s="149"/>
+      <c r="N44" s="149"/>
+      <c r="O44" s="149"/>
+      <c r="P44" s="149"/>
+      <c r="Q44" s="152"/>
+      <c r="R44" s="151"/>
+      <c r="S44" s="149"/>
+      <c r="T44" s="149"/>
+      <c r="U44" s="149"/>
+      <c r="V44" s="149"/>
+      <c r="W44" s="149"/>
+      <c r="X44" s="176"/>
+      <c r="Y44" s="149"/>
+      <c r="Z44" s="150"/>
+      <c r="AA44" s="150"/>
+      <c r="AB44" s="150"/>
+      <c r="AC44" s="150"/>
+      <c r="AD44" s="149"/>
+      <c r="AE44" s="149"/>
+      <c r="AF44" s="149"/>
+      <c r="AG44" s="149"/>
+      <c r="AH44" s="149"/>
+      <c r="AI44" s="149"/>
+      <c r="AJ44" s="149"/>
+      <c r="AK44" s="147"/>
+      <c r="AL44" s="148"/>
+      <c r="AM44" s="147"/>
+      <c r="AN44" s="147"/>
+      <c r="AO44" s="147"/>
+      <c r="AP44" s="147"/>
+      <c r="AQ44" s="147"/>
+      <c r="AR44" s="147"/>
+      <c r="AS44" s="147"/>
+      <c r="AT44" s="149"/>
+      <c r="AU44" s="149"/>
+      <c r="AV44" s="149"/>
+      <c r="AW44" s="149"/>
+      <c r="AX44" s="148"/>
+      <c r="AY44" s="147"/>
+      <c r="AZ44" s="147"/>
+      <c r="BA44" s="147"/>
       <c r="BB44" s="23"/>
       <c r="BC44" s="23"/>
       <c r="BD44" s="21"/>
       <c r="BE44" s="21"/>
-      <c r="BF44" s="206"/>
-      <c r="BG44" s="206"/>
-      <c r="BH44" s="206"/>
-      <c r="BI44" s="207"/>
-      <c r="BJ44" s="206"/>
-      <c r="BK44" s="206"/>
-      <c r="BL44" s="206"/>
-      <c r="BM44" s="207"/>
-      <c r="BN44" s="206"/>
-      <c r="BO44" s="206"/>
-      <c r="BP44" s="205"/>
-      <c r="BQ44" s="207"/>
-      <c r="BR44" s="206"/>
-      <c r="BS44" s="206"/>
-      <c r="BT44" s="205"/>
-    </row>
-    <row r="45" spans="1:72" ht="12">
-      <c r="A45" s="227" t="s">
+      <c r="BF44" s="147"/>
+      <c r="BG44" s="147"/>
+      <c r="BH44" s="147"/>
+      <c r="BI44" s="148"/>
+      <c r="BJ44" s="147"/>
+      <c r="BK44" s="147"/>
+      <c r="BL44" s="147"/>
+      <c r="BM44" s="148"/>
+      <c r="BN44" s="146"/>
+      <c r="BO44" s="148"/>
+      <c r="BP44" s="147"/>
+      <c r="BQ44" s="147"/>
+      <c r="BR44" s="146"/>
+    </row>
+    <row r="45" spans="1:70" ht="12">
+      <c r="A45" s="168" t="s">
         <v>130</v>
       </c>
-      <c r="B45" s="217" t="s">
+      <c r="B45" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C45" s="226"/>
-      <c r="D45" s="226"/>
-      <c r="E45" s="218"/>
-      <c r="F45" s="217" t="s">
+      <c r="C45" s="167"/>
+      <c r="D45" s="167"/>
+      <c r="E45" s="159"/>
+      <c r="F45" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G45" s="226"/>
-      <c r="H45" s="226"/>
-      <c r="I45" s="226"/>
-      <c r="L45" s="217" t="s">
+      <c r="G45" s="167"/>
+      <c r="H45" s="167"/>
+      <c r="I45" s="167"/>
+      <c r="L45" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M45" s="226"/>
-      <c r="N45" s="226"/>
-      <c r="O45" s="226"/>
-      <c r="P45" s="226"/>
-      <c r="Q45" s="218"/>
-      <c r="R45" s="217" t="s">
+      <c r="M45" s="167"/>
+      <c r="N45" s="167"/>
+      <c r="O45" s="167"/>
+      <c r="P45" s="167"/>
+      <c r="Q45" s="159"/>
+      <c r="R45" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S45" s="226"/>
-      <c r="T45" s="226"/>
-      <c r="U45" s="226"/>
-      <c r="V45" s="226"/>
-      <c r="W45" s="226"/>
-      <c r="X45" s="217" t="s">
+      <c r="S45" s="167"/>
+      <c r="T45" s="167"/>
+      <c r="U45" s="167"/>
+      <c r="V45" s="167"/>
+      <c r="W45" s="167"/>
+      <c r="X45" s="158" t="s">
         <v>131</v>
       </c>
-      <c r="Y45" s="215"/>
-      <c r="Z45" s="216"/>
-      <c r="AA45" s="216"/>
-      <c r="AB45" s="216"/>
-      <c r="AC45" s="216"/>
-      <c r="AD45" s="215"/>
-      <c r="AE45" s="215"/>
-      <c r="AF45" s="215"/>
-      <c r="AG45" s="215"/>
-      <c r="AH45" s="215"/>
-      <c r="AI45" s="215"/>
-      <c r="AJ45" s="215"/>
-      <c r="AK45" s="213"/>
-      <c r="AL45" s="221" t="s">
+      <c r="Y45" s="156"/>
+      <c r="Z45" s="157"/>
+      <c r="AA45" s="157"/>
+      <c r="AB45" s="157"/>
+      <c r="AC45" s="157"/>
+      <c r="AD45" s="156"/>
+      <c r="AE45" s="156"/>
+      <c r="AF45" s="156"/>
+      <c r="AG45" s="156"/>
+      <c r="AH45" s="156"/>
+      <c r="AI45" s="156"/>
+      <c r="AJ45" s="156"/>
+      <c r="AK45" s="154"/>
+      <c r="AL45" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM45" s="213"/>
-      <c r="AN45" s="213"/>
-      <c r="AO45" s="213"/>
-      <c r="AP45" s="213"/>
-      <c r="AQ45" s="213"/>
-      <c r="AR45" s="213"/>
-      <c r="AS45" s="213"/>
-      <c r="AT45" s="215"/>
-      <c r="AU45" s="215"/>
-      <c r="AV45" s="215"/>
-      <c r="AW45" s="215"/>
-      <c r="AX45" s="221" t="s">
+      <c r="AM45" s="154"/>
+      <c r="AN45" s="154"/>
+      <c r="AO45" s="154"/>
+      <c r="AP45" s="154"/>
+      <c r="AQ45" s="154"/>
+      <c r="AR45" s="154"/>
+      <c r="AS45" s="154"/>
+      <c r="AT45" s="156"/>
+      <c r="AU45" s="156"/>
+      <c r="AV45" s="156"/>
+      <c r="AW45" s="156"/>
+      <c r="AX45" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY45" s="213"/>
-      <c r="AZ45" s="213"/>
-      <c r="BA45" s="213"/>
-      <c r="BF45" s="213"/>
-      <c r="BG45" s="213"/>
-      <c r="BH45" s="213"/>
-      <c r="BI45" s="214"/>
-      <c r="BJ45" s="213"/>
-      <c r="BK45" s="213"/>
-      <c r="BL45" s="213"/>
-      <c r="BM45" s="214"/>
-      <c r="BN45" s="213"/>
-      <c r="BO45" s="213"/>
-      <c r="BP45" s="212"/>
-      <c r="BQ45" s="214"/>
-      <c r="BR45" s="213"/>
-      <c r="BS45" s="213"/>
-      <c r="BT45" s="212"/>
-    </row>
-    <row r="46" spans="1:72" ht="12">
-      <c r="A46" s="227"/>
-      <c r="B46" s="217"/>
-      <c r="C46" s="226"/>
-      <c r="D46" s="226"/>
-      <c r="E46" s="218"/>
-      <c r="F46" s="217"/>
-      <c r="G46" s="226"/>
-      <c r="H46" s="226"/>
-      <c r="I46" s="226"/>
-      <c r="L46" s="217"/>
-      <c r="M46" s="226"/>
-      <c r="N46" s="226"/>
-      <c r="O46" s="226"/>
-      <c r="P46" s="226"/>
-      <c r="Q46" s="218"/>
-      <c r="R46" s="217"/>
-      <c r="S46" s="226"/>
-      <c r="T46" s="226"/>
-      <c r="U46" s="226"/>
-      <c r="V46" s="226"/>
-      <c r="W46" s="226"/>
-      <c r="X46" s="217" t="s">
+      <c r="AY45" s="154"/>
+      <c r="AZ45" s="154"/>
+      <c r="BA45" s="154"/>
+      <c r="BF45" s="154"/>
+      <c r="BG45" s="154"/>
+      <c r="BH45" s="154"/>
+      <c r="BI45" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ45" s="239"/>
+      <c r="BK45" s="239"/>
+      <c r="BL45" s="154"/>
+      <c r="BM45" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN45" s="153"/>
+      <c r="BO45" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP45" s="154"/>
+      <c r="BQ45" s="154"/>
+      <c r="BR45" s="153"/>
+    </row>
+    <row r="46" spans="1:70" ht="12">
+      <c r="A46" s="168"/>
+      <c r="B46" s="158"/>
+      <c r="C46" s="167"/>
+      <c r="D46" s="167"/>
+      <c r="E46" s="159"/>
+      <c r="F46" s="158"/>
+      <c r="G46" s="167"/>
+      <c r="H46" s="167"/>
+      <c r="I46" s="167"/>
+      <c r="L46" s="158"/>
+      <c r="M46" s="167"/>
+      <c r="N46" s="167"/>
+      <c r="O46" s="167"/>
+      <c r="P46" s="167"/>
+      <c r="Q46" s="159"/>
+      <c r="R46" s="158"/>
+      <c r="S46" s="167"/>
+      <c r="T46" s="167"/>
+      <c r="U46" s="167"/>
+      <c r="V46" s="167"/>
+      <c r="W46" s="167"/>
+      <c r="X46" s="158" t="s">
         <v>132</v>
       </c>
-      <c r="Y46" s="215"/>
-      <c r="Z46" s="216"/>
-      <c r="AA46" s="216"/>
-      <c r="AB46" s="216"/>
-      <c r="AC46" s="216"/>
-      <c r="AD46" s="215"/>
-      <c r="AE46" s="215"/>
-      <c r="AF46" s="215"/>
-      <c r="AG46" s="215"/>
-      <c r="AH46" s="215"/>
-      <c r="AI46" s="215"/>
-      <c r="AJ46" s="215"/>
-      <c r="AK46" s="213"/>
-      <c r="AL46" s="214" t="s">
+      <c r="Y46" s="156"/>
+      <c r="Z46" s="157"/>
+      <c r="AA46" s="157"/>
+      <c r="AB46" s="157"/>
+      <c r="AC46" s="157"/>
+      <c r="AD46" s="156"/>
+      <c r="AE46" s="156"/>
+      <c r="AF46" s="156"/>
+      <c r="AG46" s="156"/>
+      <c r="AH46" s="156"/>
+      <c r="AI46" s="156"/>
+      <c r="AJ46" s="156"/>
+      <c r="AK46" s="154"/>
+      <c r="AL46" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM46" s="213"/>
-      <c r="AN46" s="213"/>
-      <c r="AO46" s="213"/>
-      <c r="AP46" s="213"/>
-      <c r="AQ46" s="213"/>
-      <c r="AR46" s="213"/>
-      <c r="AS46" s="213"/>
-      <c r="AT46" s="215"/>
-      <c r="AU46" s="215"/>
-      <c r="AV46" s="215"/>
-      <c r="AW46" s="215"/>
-      <c r="AX46" s="214"/>
-      <c r="AY46" s="213"/>
-      <c r="AZ46" s="213"/>
-      <c r="BA46" s="213"/>
-      <c r="BF46" s="213"/>
-      <c r="BG46" s="213"/>
-      <c r="BH46" s="213"/>
-      <c r="BI46" s="214"/>
-      <c r="BJ46" s="213"/>
-      <c r="BK46" s="213"/>
-      <c r="BL46" s="213"/>
-      <c r="BM46" s="214"/>
-      <c r="BN46" s="213"/>
-      <c r="BO46" s="213"/>
-      <c r="BP46" s="212"/>
-      <c r="BQ46" s="214"/>
-      <c r="BR46" s="213"/>
-      <c r="BS46" s="213"/>
-      <c r="BT46" s="212"/>
-    </row>
-    <row r="47" spans="1:72" ht="12">
-      <c r="A47" s="228"/>
-      <c r="B47" s="210"/>
-      <c r="C47" s="208"/>
-      <c r="D47" s="208"/>
-      <c r="E47" s="211"/>
-      <c r="F47" s="210"/>
-      <c r="G47" s="208"/>
-      <c r="H47" s="208"/>
-      <c r="I47" s="208"/>
+      <c r="AM46" s="154"/>
+      <c r="AN46" s="154"/>
+      <c r="AO46" s="154"/>
+      <c r="AP46" s="154"/>
+      <c r="AQ46" s="154"/>
+      <c r="AR46" s="154"/>
+      <c r="AS46" s="154"/>
+      <c r="AT46" s="156"/>
+      <c r="AU46" s="156"/>
+      <c r="AV46" s="156"/>
+      <c r="AW46" s="156"/>
+      <c r="AX46" s="155"/>
+      <c r="AY46" s="154"/>
+      <c r="AZ46" s="154"/>
+      <c r="BA46" s="154"/>
+      <c r="BF46" s="154"/>
+      <c r="BG46" s="154"/>
+      <c r="BH46" s="154"/>
+      <c r="BI46" s="155"/>
+      <c r="BJ46" s="173"/>
+      <c r="BK46" s="173"/>
+      <c r="BL46" s="154"/>
+      <c r="BM46" s="155"/>
+      <c r="BN46" s="153"/>
+      <c r="BO46" s="155"/>
+      <c r="BP46" s="154"/>
+      <c r="BQ46" s="154"/>
+      <c r="BR46" s="153"/>
+    </row>
+    <row r="47" spans="1:70" ht="12">
+      <c r="A47" s="169"/>
+      <c r="B47" s="151"/>
+      <c r="C47" s="149"/>
+      <c r="D47" s="149"/>
+      <c r="E47" s="152"/>
+      <c r="F47" s="151"/>
+      <c r="G47" s="149"/>
+      <c r="H47" s="149"/>
+      <c r="I47" s="149"/>
       <c r="J47" s="24"/>
       <c r="K47" s="25"/>
-      <c r="L47" s="210"/>
-      <c r="M47" s="208"/>
-      <c r="N47" s="208"/>
-      <c r="O47" s="208"/>
-      <c r="P47" s="208"/>
-      <c r="Q47" s="211"/>
-      <c r="R47" s="210"/>
-      <c r="S47" s="208"/>
-      <c r="T47" s="208"/>
-      <c r="U47" s="208"/>
-      <c r="V47" s="208"/>
-      <c r="W47" s="208"/>
-      <c r="X47" s="210" t="s">
+      <c r="L47" s="151"/>
+      <c r="M47" s="149"/>
+      <c r="N47" s="149"/>
+      <c r="O47" s="149"/>
+      <c r="P47" s="149"/>
+      <c r="Q47" s="152"/>
+      <c r="R47" s="151"/>
+      <c r="S47" s="149"/>
+      <c r="T47" s="149"/>
+      <c r="U47" s="149"/>
+      <c r="V47" s="149"/>
+      <c r="W47" s="149"/>
+      <c r="X47" s="151" t="s">
         <v>133</v>
       </c>
-      <c r="Y47" s="208"/>
-      <c r="Z47" s="209"/>
-      <c r="AA47" s="209"/>
-      <c r="AB47" s="209"/>
-      <c r="AC47" s="209"/>
-      <c r="AD47" s="208"/>
-      <c r="AE47" s="208"/>
-      <c r="AF47" s="208"/>
-      <c r="AG47" s="208"/>
-      <c r="AH47" s="208"/>
-      <c r="AI47" s="208"/>
-      <c r="AJ47" s="208"/>
-      <c r="AK47" s="206"/>
-      <c r="AL47" s="207"/>
-      <c r="AM47" s="206"/>
-      <c r="AN47" s="206"/>
-      <c r="AO47" s="206"/>
-      <c r="AP47" s="206"/>
-      <c r="AQ47" s="206"/>
-      <c r="AR47" s="206"/>
-      <c r="AS47" s="206"/>
-      <c r="AT47" s="208"/>
-      <c r="AU47" s="208"/>
-      <c r="AV47" s="208"/>
-      <c r="AW47" s="208"/>
-      <c r="AX47" s="207"/>
-      <c r="AY47" s="206"/>
-      <c r="AZ47" s="206"/>
-      <c r="BA47" s="206"/>
+      <c r="Y47" s="149"/>
+      <c r="Z47" s="150"/>
+      <c r="AA47" s="150"/>
+      <c r="AB47" s="150"/>
+      <c r="AC47" s="150"/>
+      <c r="AD47" s="149"/>
+      <c r="AE47" s="149"/>
+      <c r="AF47" s="149"/>
+      <c r="AG47" s="149"/>
+      <c r="AH47" s="149"/>
+      <c r="AI47" s="149"/>
+      <c r="AJ47" s="149"/>
+      <c r="AK47" s="147"/>
+      <c r="AL47" s="148"/>
+      <c r="AM47" s="147"/>
+      <c r="AN47" s="147"/>
+      <c r="AO47" s="147"/>
+      <c r="AP47" s="147"/>
+      <c r="AQ47" s="147"/>
+      <c r="AR47" s="147"/>
+      <c r="AS47" s="147"/>
+      <c r="AT47" s="149"/>
+      <c r="AU47" s="149"/>
+      <c r="AV47" s="149"/>
+      <c r="AW47" s="149"/>
+      <c r="AX47" s="148"/>
+      <c r="AY47" s="147"/>
+      <c r="AZ47" s="147"/>
+      <c r="BA47" s="147"/>
       <c r="BB47" s="23"/>
       <c r="BC47" s="23"/>
       <c r="BD47" s="21"/>
       <c r="BE47" s="21"/>
-      <c r="BF47" s="206"/>
-      <c r="BG47" s="206"/>
-      <c r="BH47" s="206"/>
-      <c r="BI47" s="207"/>
-      <c r="BJ47" s="206"/>
-      <c r="BK47" s="206"/>
-      <c r="BL47" s="206"/>
-      <c r="BM47" s="207"/>
-      <c r="BN47" s="206"/>
-      <c r="BO47" s="206"/>
-      <c r="BP47" s="205"/>
-      <c r="BQ47" s="207"/>
-      <c r="BR47" s="206"/>
-      <c r="BS47" s="206"/>
-      <c r="BT47" s="205"/>
-    </row>
-    <row r="48" spans="1:72" ht="12">
-      <c r="A48" s="227" t="s">
+      <c r="BF47" s="147"/>
+      <c r="BG47" s="147"/>
+      <c r="BH47" s="147"/>
+      <c r="BI47" s="148"/>
+      <c r="BJ47" s="147"/>
+      <c r="BK47" s="147"/>
+      <c r="BL47" s="147"/>
+      <c r="BM47" s="148"/>
+      <c r="BN47" s="146"/>
+      <c r="BO47" s="148"/>
+      <c r="BP47" s="147"/>
+      <c r="BQ47" s="147"/>
+      <c r="BR47" s="146"/>
+    </row>
+    <row r="48" spans="1:70" ht="12">
+      <c r="A48" s="168" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="217" t="s">
+      <c r="B48" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="226"/>
-      <c r="D48" s="226"/>
-      <c r="E48" s="218"/>
-      <c r="F48" s="217" t="s">
+      <c r="C48" s="167"/>
+      <c r="D48" s="167"/>
+      <c r="E48" s="159"/>
+      <c r="F48" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G48" s="226"/>
-      <c r="H48" s="226"/>
-      <c r="I48" s="226"/>
-      <c r="L48" s="217" t="s">
+      <c r="G48" s="167"/>
+      <c r="H48" s="167"/>
+      <c r="I48" s="167"/>
+      <c r="L48" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M48" s="226"/>
-      <c r="N48" s="226"/>
-      <c r="O48" s="226"/>
-      <c r="P48" s="226"/>
-      <c r="Q48" s="218"/>
-      <c r="R48" s="217" t="s">
+      <c r="M48" s="167"/>
+      <c r="N48" s="167"/>
+      <c r="O48" s="167"/>
+      <c r="P48" s="167"/>
+      <c r="Q48" s="159"/>
+      <c r="R48" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S48" s="226"/>
-      <c r="T48" s="226"/>
-      <c r="U48" s="226"/>
-      <c r="V48" s="226"/>
-      <c r="W48" s="226"/>
-      <c r="X48" s="217" t="s">
+      <c r="S48" s="167"/>
+      <c r="T48" s="167"/>
+      <c r="U48" s="167"/>
+      <c r="V48" s="167"/>
+      <c r="W48" s="167"/>
+      <c r="X48" s="158" t="s">
         <v>135</v>
       </c>
-      <c r="Y48" s="215"/>
-      <c r="Z48" s="216"/>
-      <c r="AA48" s="216"/>
-      <c r="AB48" s="216"/>
-      <c r="AC48" s="216"/>
-      <c r="AD48" s="215"/>
-      <c r="AE48" s="215"/>
-      <c r="AF48" s="215"/>
-      <c r="AG48" s="215"/>
-      <c r="AH48" s="215"/>
-      <c r="AI48" s="215"/>
-      <c r="AJ48" s="215"/>
-      <c r="AK48" s="213"/>
-      <c r="AL48" s="221" t="s">
+      <c r="Y48" s="156"/>
+      <c r="Z48" s="157"/>
+      <c r="AA48" s="157"/>
+      <c r="AB48" s="157"/>
+      <c r="AC48" s="157"/>
+      <c r="AD48" s="156"/>
+      <c r="AE48" s="156"/>
+      <c r="AF48" s="156"/>
+      <c r="AG48" s="156"/>
+      <c r="AH48" s="156"/>
+      <c r="AI48" s="156"/>
+      <c r="AJ48" s="156"/>
+      <c r="AK48" s="154"/>
+      <c r="AL48" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM48" s="213"/>
-      <c r="AN48" s="213"/>
-      <c r="AO48" s="213"/>
-      <c r="AP48" s="213"/>
-      <c r="AQ48" s="213"/>
-      <c r="AR48" s="213"/>
-      <c r="AS48" s="213"/>
-      <c r="AT48" s="215"/>
-      <c r="AU48" s="215"/>
-      <c r="AV48" s="215"/>
-      <c r="AW48" s="215"/>
-      <c r="AX48" s="221" t="s">
+      <c r="AM48" s="154"/>
+      <c r="AN48" s="154"/>
+      <c r="AO48" s="154"/>
+      <c r="AP48" s="154"/>
+      <c r="AQ48" s="154"/>
+      <c r="AR48" s="154"/>
+      <c r="AS48" s="154"/>
+      <c r="AT48" s="156"/>
+      <c r="AU48" s="156"/>
+      <c r="AV48" s="156"/>
+      <c r="AW48" s="156"/>
+      <c r="AX48" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY48" s="213"/>
-      <c r="AZ48" s="213"/>
-      <c r="BA48" s="213"/>
-      <c r="BF48" s="213"/>
-      <c r="BG48" s="213"/>
-      <c r="BH48" s="213"/>
-      <c r="BI48" s="214"/>
-      <c r="BJ48" s="213"/>
-      <c r="BK48" s="213"/>
-      <c r="BL48" s="213"/>
-      <c r="BM48" s="214"/>
-      <c r="BN48" s="213"/>
-      <c r="BO48" s="213"/>
-      <c r="BP48" s="212"/>
-      <c r="BQ48" s="214"/>
-      <c r="BR48" s="213"/>
-      <c r="BS48" s="213"/>
-      <c r="BT48" s="212"/>
-    </row>
-    <row r="49" spans="1:72" ht="12">
-      <c r="A49" s="227"/>
-      <c r="B49" s="217"/>
-      <c r="C49" s="226"/>
-      <c r="D49" s="226"/>
-      <c r="E49" s="218"/>
-      <c r="F49" s="217"/>
-      <c r="G49" s="226"/>
-      <c r="H49" s="226"/>
-      <c r="I49" s="226"/>
-      <c r="L49" s="217"/>
-      <c r="M49" s="226"/>
-      <c r="N49" s="226"/>
-      <c r="O49" s="226"/>
-      <c r="P49" s="226"/>
-      <c r="Q49" s="218"/>
-      <c r="R49" s="217"/>
-      <c r="S49" s="226"/>
-      <c r="T49" s="226"/>
-      <c r="U49" s="226"/>
-      <c r="V49" s="226"/>
-      <c r="W49" s="226"/>
-      <c r="X49" s="217" t="s">
+      <c r="AY48" s="154"/>
+      <c r="AZ48" s="154"/>
+      <c r="BA48" s="154"/>
+      <c r="BF48" s="154"/>
+      <c r="BG48" s="154"/>
+      <c r="BH48" s="154"/>
+      <c r="BI48" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ48" s="239"/>
+      <c r="BK48" s="239"/>
+      <c r="BL48" s="154"/>
+      <c r="BM48" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN48" s="153"/>
+      <c r="BO48" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP48" s="154"/>
+      <c r="BQ48" s="154"/>
+      <c r="BR48" s="153"/>
+    </row>
+    <row r="49" spans="1:70" ht="12">
+      <c r="A49" s="168"/>
+      <c r="B49" s="158"/>
+      <c r="C49" s="167"/>
+      <c r="D49" s="167"/>
+      <c r="E49" s="159"/>
+      <c r="F49" s="158"/>
+      <c r="G49" s="167"/>
+      <c r="H49" s="167"/>
+      <c r="I49" s="167"/>
+      <c r="L49" s="158"/>
+      <c r="M49" s="167"/>
+      <c r="N49" s="167"/>
+      <c r="O49" s="167"/>
+      <c r="P49" s="167"/>
+      <c r="Q49" s="159"/>
+      <c r="R49" s="158"/>
+      <c r="S49" s="167"/>
+      <c r="T49" s="167"/>
+      <c r="U49" s="167"/>
+      <c r="V49" s="167"/>
+      <c r="W49" s="167"/>
+      <c r="X49" s="158" t="s">
         <v>136</v>
       </c>
-      <c r="Y49" s="215"/>
-      <c r="Z49" s="216"/>
-      <c r="AA49" s="216"/>
-      <c r="AB49" s="216"/>
-      <c r="AC49" s="216"/>
-      <c r="AD49" s="215"/>
-      <c r="AE49" s="215"/>
-      <c r="AF49" s="215"/>
-      <c r="AG49" s="215"/>
-      <c r="AH49" s="215"/>
-      <c r="AI49" s="215"/>
-      <c r="AJ49" s="215"/>
-      <c r="AK49" s="213"/>
-      <c r="AL49" s="214" t="s">
+      <c r="Y49" s="156"/>
+      <c r="Z49" s="157"/>
+      <c r="AA49" s="157"/>
+      <c r="AB49" s="157"/>
+      <c r="AC49" s="157"/>
+      <c r="AD49" s="156"/>
+      <c r="AE49" s="156"/>
+      <c r="AF49" s="156"/>
+      <c r="AG49" s="156"/>
+      <c r="AH49" s="156"/>
+      <c r="AI49" s="156"/>
+      <c r="AJ49" s="156"/>
+      <c r="AK49" s="154"/>
+      <c r="AL49" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM49" s="213"/>
-      <c r="AN49" s="213"/>
-      <c r="AO49" s="213"/>
-      <c r="AP49" s="213"/>
-      <c r="AQ49" s="213"/>
-      <c r="AR49" s="213"/>
-      <c r="AS49" s="213"/>
-      <c r="AT49" s="215"/>
-      <c r="AU49" s="215"/>
-      <c r="AV49" s="215"/>
-      <c r="AW49" s="215"/>
-      <c r="AX49" s="214"/>
-      <c r="AY49" s="213"/>
-      <c r="AZ49" s="213"/>
-      <c r="BA49" s="213"/>
-      <c r="BF49" s="213"/>
-      <c r="BG49" s="213"/>
-      <c r="BH49" s="213"/>
-      <c r="BI49" s="214"/>
-      <c r="BJ49" s="213"/>
-      <c r="BK49" s="213"/>
-      <c r="BL49" s="213"/>
-      <c r="BM49" s="214"/>
-      <c r="BN49" s="213"/>
-      <c r="BO49" s="213"/>
-      <c r="BP49" s="212"/>
-      <c r="BQ49" s="214"/>
-      <c r="BR49" s="213"/>
-      <c r="BS49" s="213"/>
-      <c r="BT49" s="212"/>
-    </row>
-    <row r="50" spans="1:72" ht="12">
-      <c r="A50" s="228"/>
-      <c r="B50" s="210"/>
-      <c r="C50" s="208"/>
-      <c r="D50" s="208"/>
-      <c r="E50" s="211"/>
-      <c r="F50" s="210"/>
-      <c r="G50" s="208"/>
-      <c r="H50" s="208"/>
-      <c r="I50" s="208"/>
+      <c r="AM49" s="154"/>
+      <c r="AN49" s="154"/>
+      <c r="AO49" s="154"/>
+      <c r="AP49" s="154"/>
+      <c r="AQ49" s="154"/>
+      <c r="AR49" s="154"/>
+      <c r="AS49" s="154"/>
+      <c r="AT49" s="156"/>
+      <c r="AU49" s="156"/>
+      <c r="AV49" s="156"/>
+      <c r="AW49" s="156"/>
+      <c r="AX49" s="155"/>
+      <c r="AY49" s="154"/>
+      <c r="AZ49" s="154"/>
+      <c r="BA49" s="154"/>
+      <c r="BF49" s="154"/>
+      <c r="BG49" s="154"/>
+      <c r="BH49" s="154"/>
+      <c r="BI49" s="155"/>
+      <c r="BJ49" s="173"/>
+      <c r="BK49" s="173"/>
+      <c r="BL49" s="154"/>
+      <c r="BM49" s="155"/>
+      <c r="BN49" s="153"/>
+      <c r="BO49" s="155"/>
+      <c r="BP49" s="154"/>
+      <c r="BQ49" s="154"/>
+      <c r="BR49" s="153"/>
+    </row>
+    <row r="50" spans="1:70" ht="12">
+      <c r="A50" s="169"/>
+      <c r="B50" s="151"/>
+      <c r="C50" s="149"/>
+      <c r="D50" s="149"/>
+      <c r="E50" s="152"/>
+      <c r="F50" s="151"/>
+      <c r="G50" s="149"/>
+      <c r="H50" s="149"/>
+      <c r="I50" s="149"/>
       <c r="J50" s="24"/>
       <c r="K50" s="25"/>
-      <c r="L50" s="210"/>
-      <c r="M50" s="208"/>
-      <c r="N50" s="208"/>
-      <c r="O50" s="208"/>
-      <c r="P50" s="208"/>
-      <c r="Q50" s="211"/>
-      <c r="R50" s="210"/>
-      <c r="S50" s="208"/>
-      <c r="T50" s="208"/>
-      <c r="U50" s="208"/>
-      <c r="V50" s="208"/>
-      <c r="W50" s="208"/>
-      <c r="X50" s="210" t="s">
+      <c r="L50" s="151"/>
+      <c r="M50" s="149"/>
+      <c r="N50" s="149"/>
+      <c r="O50" s="149"/>
+      <c r="P50" s="149"/>
+      <c r="Q50" s="152"/>
+      <c r="R50" s="151"/>
+      <c r="S50" s="149"/>
+      <c r="T50" s="149"/>
+      <c r="U50" s="149"/>
+      <c r="V50" s="149"/>
+      <c r="W50" s="149"/>
+      <c r="X50" s="151" t="s">
         <v>137</v>
       </c>
-      <c r="Y50" s="208"/>
-      <c r="Z50" s="209"/>
-      <c r="AA50" s="209"/>
-      <c r="AB50" s="209"/>
-      <c r="AC50" s="209"/>
-      <c r="AD50" s="208"/>
-      <c r="AE50" s="208"/>
-      <c r="AF50" s="208"/>
-      <c r="AG50" s="208"/>
-      <c r="AH50" s="208"/>
-      <c r="AI50" s="208"/>
-      <c r="AJ50" s="208"/>
-      <c r="AK50" s="206"/>
-      <c r="AL50" s="207"/>
-      <c r="AM50" s="206"/>
-      <c r="AN50" s="206"/>
-      <c r="AO50" s="206"/>
-      <c r="AP50" s="206"/>
-      <c r="AQ50" s="206"/>
-      <c r="AR50" s="206"/>
-      <c r="AS50" s="206"/>
-      <c r="AT50" s="208"/>
-      <c r="AU50" s="208"/>
-      <c r="AV50" s="208"/>
-      <c r="AW50" s="208"/>
-      <c r="AX50" s="207"/>
-      <c r="AY50" s="206"/>
-      <c r="AZ50" s="206"/>
-      <c r="BA50" s="206"/>
+      <c r="Y50" s="149"/>
+      <c r="Z50" s="150"/>
+      <c r="AA50" s="150"/>
+      <c r="AB50" s="150"/>
+      <c r="AC50" s="150"/>
+      <c r="AD50" s="149"/>
+      <c r="AE50" s="149"/>
+      <c r="AF50" s="149"/>
+      <c r="AG50" s="149"/>
+      <c r="AH50" s="149"/>
+      <c r="AI50" s="149"/>
+      <c r="AJ50" s="149"/>
+      <c r="AK50" s="147"/>
+      <c r="AL50" s="148"/>
+      <c r="AM50" s="147"/>
+      <c r="AN50" s="147"/>
+      <c r="AO50" s="147"/>
+      <c r="AP50" s="147"/>
+      <c r="AQ50" s="147"/>
+      <c r="AR50" s="147"/>
+      <c r="AS50" s="147"/>
+      <c r="AT50" s="149"/>
+      <c r="AU50" s="149"/>
+      <c r="AV50" s="149"/>
+      <c r="AW50" s="149"/>
+      <c r="AX50" s="148"/>
+      <c r="AY50" s="147"/>
+      <c r="AZ50" s="147"/>
+      <c r="BA50" s="147"/>
       <c r="BB50" s="23"/>
       <c r="BC50" s="23"/>
       <c r="BD50" s="21"/>
       <c r="BE50" s="21"/>
-      <c r="BF50" s="206"/>
-      <c r="BG50" s="206"/>
-      <c r="BH50" s="206"/>
-      <c r="BI50" s="207"/>
-      <c r="BJ50" s="206"/>
-      <c r="BK50" s="206"/>
-      <c r="BL50" s="206"/>
-      <c r="BM50" s="207"/>
-      <c r="BN50" s="206"/>
-      <c r="BO50" s="206"/>
-      <c r="BP50" s="205"/>
-      <c r="BQ50" s="207"/>
-      <c r="BR50" s="206"/>
-      <c r="BS50" s="206"/>
-      <c r="BT50" s="205"/>
-    </row>
-    <row r="51" spans="1:72" ht="12">
-      <c r="A51" s="227" t="s">
+      <c r="BF50" s="147"/>
+      <c r="BG50" s="147"/>
+      <c r="BH50" s="147"/>
+      <c r="BI50" s="148"/>
+      <c r="BJ50" s="147"/>
+      <c r="BK50" s="147"/>
+      <c r="BL50" s="147"/>
+      <c r="BM50" s="148"/>
+      <c r="BN50" s="146"/>
+      <c r="BO50" s="148"/>
+      <c r="BP50" s="147"/>
+      <c r="BQ50" s="147"/>
+      <c r="BR50" s="146"/>
+    </row>
+    <row r="51" spans="1:70" ht="12">
+      <c r="A51" s="168" t="s">
         <v>138</v>
       </c>
-      <c r="B51" s="217" t="s">
+      <c r="B51" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C51" s="215"/>
-      <c r="D51" s="215"/>
-      <c r="E51" s="218"/>
-      <c r="F51" s="217" t="s">
+      <c r="C51" s="156"/>
+      <c r="D51" s="156"/>
+      <c r="E51" s="159"/>
+      <c r="F51" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G51" s="215"/>
-      <c r="H51" s="215"/>
-      <c r="I51" s="215"/>
-      <c r="L51" s="217" t="s">
+      <c r="G51" s="156"/>
+      <c r="H51" s="156"/>
+      <c r="I51" s="156"/>
+      <c r="L51" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M51" s="215"/>
-      <c r="N51" s="215"/>
-      <c r="O51" s="215"/>
-      <c r="P51" s="215"/>
-      <c r="Q51" s="218"/>
-      <c r="R51" s="217" t="s">
+      <c r="M51" s="156"/>
+      <c r="N51" s="156"/>
+      <c r="O51" s="156"/>
+      <c r="P51" s="156"/>
+      <c r="Q51" s="159"/>
+      <c r="R51" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S51" s="215"/>
-      <c r="T51" s="215"/>
-      <c r="U51" s="215"/>
-      <c r="V51" s="215"/>
-      <c r="W51" s="215"/>
-      <c r="X51" s="217" t="s">
+      <c r="S51" s="156"/>
+      <c r="T51" s="156"/>
+      <c r="U51" s="156"/>
+      <c r="V51" s="156"/>
+      <c r="W51" s="156"/>
+      <c r="X51" s="158" t="s">
         <v>139</v>
       </c>
-      <c r="Y51" s="215"/>
-      <c r="Z51" s="216"/>
-      <c r="AA51" s="216"/>
-      <c r="AB51" s="216"/>
-      <c r="AC51" s="216"/>
-      <c r="AD51" s="215"/>
-      <c r="AE51" s="215"/>
-      <c r="AF51" s="215"/>
-      <c r="AG51" s="215"/>
-      <c r="AH51" s="215"/>
-      <c r="AI51" s="215"/>
-      <c r="AJ51" s="215"/>
-      <c r="AK51" s="213"/>
-      <c r="AL51" s="221" t="s">
+      <c r="Y51" s="156"/>
+      <c r="Z51" s="157"/>
+      <c r="AA51" s="157"/>
+      <c r="AB51" s="157"/>
+      <c r="AC51" s="157"/>
+      <c r="AD51" s="156"/>
+      <c r="AE51" s="156"/>
+      <c r="AF51" s="156"/>
+      <c r="AG51" s="156"/>
+      <c r="AH51" s="156"/>
+      <c r="AI51" s="156"/>
+      <c r="AJ51" s="156"/>
+      <c r="AK51" s="154"/>
+      <c r="AL51" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM51" s="213"/>
-      <c r="AN51" s="213"/>
-      <c r="AO51" s="213"/>
-      <c r="AP51" s="213"/>
-      <c r="AQ51" s="213"/>
-      <c r="AR51" s="213"/>
-      <c r="AS51" s="213"/>
-      <c r="AT51" s="215"/>
-      <c r="AU51" s="215"/>
-      <c r="AV51" s="215"/>
-      <c r="AW51" s="215"/>
-      <c r="AX51" s="221" t="s">
+      <c r="AM51" s="154"/>
+      <c r="AN51" s="154"/>
+      <c r="AO51" s="154"/>
+      <c r="AP51" s="154"/>
+      <c r="AQ51" s="154"/>
+      <c r="AR51" s="154"/>
+      <c r="AS51" s="154"/>
+      <c r="AT51" s="156"/>
+      <c r="AU51" s="156"/>
+      <c r="AV51" s="156"/>
+      <c r="AW51" s="156"/>
+      <c r="AX51" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY51" s="213"/>
-      <c r="AZ51" s="213"/>
-      <c r="BA51" s="213"/>
-      <c r="BF51" s="213"/>
-      <c r="BG51" s="213"/>
-      <c r="BH51" s="213"/>
-      <c r="BI51" s="214"/>
-      <c r="BJ51" s="213"/>
-      <c r="BK51" s="213"/>
-      <c r="BL51" s="213"/>
-      <c r="BM51" s="214"/>
-      <c r="BN51" s="213"/>
-      <c r="BO51" s="213"/>
-      <c r="BP51" s="212"/>
-      <c r="BQ51" s="214"/>
-      <c r="BR51" s="213"/>
-      <c r="BS51" s="213"/>
-      <c r="BT51" s="212"/>
-    </row>
-    <row r="52" spans="1:72" ht="13.2">
-      <c r="A52" s="204"/>
-      <c r="B52" s="217"/>
-      <c r="C52" s="215"/>
-      <c r="D52" s="215"/>
-      <c r="E52" s="218"/>
-      <c r="F52" s="217"/>
-      <c r="G52" s="215"/>
-      <c r="H52" s="215"/>
-      <c r="I52" s="215"/>
-      <c r="L52" s="217"/>
-      <c r="M52" s="215"/>
-      <c r="N52" s="215"/>
-      <c r="O52" s="215"/>
-      <c r="P52" s="215"/>
-      <c r="Q52" s="218"/>
-      <c r="R52" s="217"/>
-      <c r="S52" s="215"/>
-      <c r="T52" s="215"/>
-      <c r="U52" s="215"/>
-      <c r="V52" s="215"/>
-      <c r="W52" s="215"/>
-      <c r="X52" s="217" t="s">
+      <c r="AY51" s="154"/>
+      <c r="AZ51" s="154"/>
+      <c r="BA51" s="154"/>
+      <c r="BF51" s="154"/>
+      <c r="BG51" s="154"/>
+      <c r="BH51" s="154"/>
+      <c r="BI51" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ51" s="239"/>
+      <c r="BK51" s="239"/>
+      <c r="BL51" s="154"/>
+      <c r="BM51" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN51" s="153"/>
+      <c r="BO51" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP51" s="154"/>
+      <c r="BQ51" s="154"/>
+      <c r="BR51" s="153"/>
+    </row>
+    <row r="52" spans="1:70" ht="13.2">
+      <c r="A52" s="145"/>
+      <c r="B52" s="158"/>
+      <c r="C52" s="156"/>
+      <c r="D52" s="156"/>
+      <c r="E52" s="159"/>
+      <c r="F52" s="158"/>
+      <c r="G52" s="156"/>
+      <c r="H52" s="156"/>
+      <c r="I52" s="156"/>
+      <c r="L52" s="158"/>
+      <c r="M52" s="156"/>
+      <c r="N52" s="156"/>
+      <c r="O52" s="156"/>
+      <c r="P52" s="156"/>
+      <c r="Q52" s="159"/>
+      <c r="R52" s="158"/>
+      <c r="S52" s="156"/>
+      <c r="T52" s="156"/>
+      <c r="U52" s="156"/>
+      <c r="V52" s="156"/>
+      <c r="W52" s="156"/>
+      <c r="X52" s="158" t="s">
         <v>140</v>
       </c>
-      <c r="Y52" s="215"/>
-      <c r="Z52" s="216"/>
-      <c r="AA52" s="216"/>
-      <c r="AB52" s="216"/>
-      <c r="AC52" s="216"/>
-      <c r="AD52" s="215"/>
-      <c r="AE52" s="215"/>
-      <c r="AF52" s="215"/>
-      <c r="AG52" s="215"/>
-      <c r="AH52" s="215"/>
-      <c r="AI52" s="215"/>
-      <c r="AJ52" s="215"/>
-      <c r="AK52" s="213"/>
-      <c r="AL52" s="214" t="s">
+      <c r="Y52" s="156"/>
+      <c r="Z52" s="157"/>
+      <c r="AA52" s="157"/>
+      <c r="AB52" s="157"/>
+      <c r="AC52" s="157"/>
+      <c r="AD52" s="156"/>
+      <c r="AE52" s="156"/>
+      <c r="AF52" s="156"/>
+      <c r="AG52" s="156"/>
+      <c r="AH52" s="156"/>
+      <c r="AI52" s="156"/>
+      <c r="AJ52" s="156"/>
+      <c r="AK52" s="154"/>
+      <c r="AL52" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM52" s="213"/>
-      <c r="AN52" s="213"/>
-      <c r="AO52" s="213"/>
-      <c r="AP52" s="213"/>
-      <c r="AQ52" s="213"/>
-      <c r="AR52" s="213"/>
-      <c r="AS52" s="213"/>
-      <c r="AT52" s="215"/>
-      <c r="AU52" s="215"/>
-      <c r="AV52" s="215"/>
-      <c r="AW52" s="215"/>
-      <c r="AX52" s="214"/>
-      <c r="AY52" s="213"/>
-      <c r="AZ52" s="213"/>
-      <c r="BA52" s="213"/>
-      <c r="BF52" s="213"/>
-      <c r="BG52" s="213"/>
-      <c r="BH52" s="213"/>
-      <c r="BI52" s="214"/>
-      <c r="BJ52" s="213"/>
-      <c r="BK52" s="213"/>
-      <c r="BL52" s="213"/>
-      <c r="BM52" s="214"/>
-      <c r="BN52" s="213"/>
-      <c r="BO52" s="213"/>
-      <c r="BP52" s="212"/>
-      <c r="BQ52" s="214"/>
-      <c r="BR52" s="213"/>
-      <c r="BS52" s="213"/>
-      <c r="BT52" s="212"/>
-    </row>
-    <row r="53" spans="1:72" ht="12">
-      <c r="A53" s="228"/>
-      <c r="B53" s="210"/>
-      <c r="C53" s="208"/>
-      <c r="D53" s="208"/>
-      <c r="E53" s="211"/>
-      <c r="F53" s="210"/>
-      <c r="G53" s="208"/>
-      <c r="H53" s="208"/>
-      <c r="I53" s="208"/>
+      <c r="AM52" s="154"/>
+      <c r="AN52" s="154"/>
+      <c r="AO52" s="154"/>
+      <c r="AP52" s="154"/>
+      <c r="AQ52" s="154"/>
+      <c r="AR52" s="154"/>
+      <c r="AS52" s="154"/>
+      <c r="AT52" s="156"/>
+      <c r="AU52" s="156"/>
+      <c r="AV52" s="156"/>
+      <c r="AW52" s="156"/>
+      <c r="AX52" s="155"/>
+      <c r="AY52" s="154"/>
+      <c r="AZ52" s="154"/>
+      <c r="BA52" s="154"/>
+      <c r="BF52" s="154"/>
+      <c r="BG52" s="154"/>
+      <c r="BH52" s="154"/>
+      <c r="BI52" s="155"/>
+      <c r="BJ52" s="173"/>
+      <c r="BK52" s="173"/>
+      <c r="BL52" s="154"/>
+      <c r="BM52" s="155"/>
+      <c r="BN52" s="153"/>
+      <c r="BO52" s="155"/>
+      <c r="BP52" s="154"/>
+      <c r="BQ52" s="154"/>
+      <c r="BR52" s="153"/>
+    </row>
+    <row r="53" spans="1:70" ht="12">
+      <c r="A53" s="169"/>
+      <c r="B53" s="151"/>
+      <c r="C53" s="149"/>
+      <c r="D53" s="149"/>
+      <c r="E53" s="152"/>
+      <c r="F53" s="151"/>
+      <c r="G53" s="149"/>
+      <c r="H53" s="149"/>
+      <c r="I53" s="149"/>
       <c r="J53" s="24"/>
       <c r="K53" s="25"/>
-      <c r="L53" s="210"/>
-      <c r="M53" s="208"/>
-      <c r="N53" s="208"/>
-      <c r="O53" s="208"/>
-      <c r="P53" s="208"/>
-      <c r="Q53" s="211"/>
-      <c r="R53" s="210"/>
-      <c r="S53" s="208"/>
-      <c r="T53" s="208"/>
-      <c r="U53" s="208"/>
-      <c r="V53" s="208"/>
-      <c r="W53" s="208"/>
-      <c r="X53" s="210"/>
-      <c r="Y53" s="208"/>
-      <c r="Z53" s="209"/>
-      <c r="AA53" s="209"/>
-      <c r="AB53" s="209"/>
-      <c r="AC53" s="209"/>
-      <c r="AD53" s="208"/>
-      <c r="AE53" s="208"/>
-      <c r="AF53" s="208"/>
-      <c r="AG53" s="208"/>
-      <c r="AH53" s="208"/>
-      <c r="AI53" s="208"/>
-      <c r="AJ53" s="208"/>
-      <c r="AK53" s="206"/>
-      <c r="AL53" s="207"/>
-      <c r="AM53" s="206"/>
-      <c r="AN53" s="206"/>
-      <c r="AO53" s="206"/>
-      <c r="AP53" s="206"/>
-      <c r="AQ53" s="206"/>
-      <c r="AR53" s="206"/>
-      <c r="AS53" s="206"/>
-      <c r="AT53" s="208"/>
-      <c r="AU53" s="208"/>
-      <c r="AV53" s="208"/>
-      <c r="AW53" s="208"/>
-      <c r="AX53" s="207"/>
-      <c r="AY53" s="206"/>
-      <c r="AZ53" s="206"/>
-      <c r="BA53" s="206"/>
+      <c r="L53" s="151"/>
+      <c r="M53" s="149"/>
+      <c r="N53" s="149"/>
+      <c r="O53" s="149"/>
+      <c r="P53" s="149"/>
+      <c r="Q53" s="152"/>
+      <c r="R53" s="151"/>
+      <c r="S53" s="149"/>
+      <c r="T53" s="149"/>
+      <c r="U53" s="149"/>
+      <c r="V53" s="149"/>
+      <c r="W53" s="149"/>
+      <c r="X53" s="151"/>
+      <c r="Y53" s="149"/>
+      <c r="Z53" s="150"/>
+      <c r="AA53" s="150"/>
+      <c r="AB53" s="150"/>
+      <c r="AC53" s="150"/>
+      <c r="AD53" s="149"/>
+      <c r="AE53" s="149"/>
+      <c r="AF53" s="149"/>
+      <c r="AG53" s="149"/>
+      <c r="AH53" s="149"/>
+      <c r="AI53" s="149"/>
+      <c r="AJ53" s="149"/>
+      <c r="AK53" s="147"/>
+      <c r="AL53" s="148"/>
+      <c r="AM53" s="147"/>
+      <c r="AN53" s="147"/>
+      <c r="AO53" s="147"/>
+      <c r="AP53" s="147"/>
+      <c r="AQ53" s="147"/>
+      <c r="AR53" s="147"/>
+      <c r="AS53" s="147"/>
+      <c r="AT53" s="149"/>
+      <c r="AU53" s="149"/>
+      <c r="AV53" s="149"/>
+      <c r="AW53" s="149"/>
+      <c r="AX53" s="148"/>
+      <c r="AY53" s="147"/>
+      <c r="AZ53" s="147"/>
+      <c r="BA53" s="147"/>
       <c r="BB53" s="23"/>
       <c r="BC53" s="23"/>
       <c r="BD53" s="21"/>
       <c r="BE53" s="21"/>
-      <c r="BF53" s="206"/>
-      <c r="BG53" s="206"/>
-      <c r="BH53" s="206"/>
-      <c r="BI53" s="207"/>
-      <c r="BJ53" s="206"/>
-      <c r="BK53" s="206"/>
-      <c r="BL53" s="206"/>
-      <c r="BM53" s="207"/>
-      <c r="BN53" s="206"/>
-      <c r="BO53" s="206"/>
-      <c r="BP53" s="205"/>
-      <c r="BQ53" s="207"/>
-      <c r="BR53" s="206"/>
-      <c r="BS53" s="206"/>
-      <c r="BT53" s="205"/>
-    </row>
-    <row r="54" spans="1:72" ht="12">
-      <c r="A54" s="227" t="s">
+      <c r="BF53" s="147"/>
+      <c r="BG53" s="147"/>
+      <c r="BH53" s="147"/>
+      <c r="BI53" s="148"/>
+      <c r="BJ53" s="147"/>
+      <c r="BK53" s="147"/>
+      <c r="BL53" s="147"/>
+      <c r="BM53" s="148"/>
+      <c r="BN53" s="146"/>
+      <c r="BO53" s="148"/>
+      <c r="BP53" s="147"/>
+      <c r="BQ53" s="147"/>
+      <c r="BR53" s="146"/>
+    </row>
+    <row r="54" spans="1:70" ht="12">
+      <c r="A54" s="168" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="217" t="s">
+      <c r="B54" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C54" s="215"/>
-      <c r="D54" s="215"/>
-      <c r="E54" s="218"/>
-      <c r="F54" s="217" t="s">
+      <c r="C54" s="156"/>
+      <c r="D54" s="156"/>
+      <c r="E54" s="159"/>
+      <c r="F54" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G54" s="215"/>
-      <c r="H54" s="215"/>
-      <c r="I54" s="215"/>
-      <c r="L54" s="217" t="s">
+      <c r="G54" s="156"/>
+      <c r="H54" s="156"/>
+      <c r="I54" s="156"/>
+      <c r="L54" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M54" s="215"/>
-      <c r="N54" s="215"/>
-      <c r="O54" s="215"/>
-      <c r="P54" s="215"/>
-      <c r="Q54" s="218"/>
-      <c r="R54" s="217" t="s">
+      <c r="M54" s="156"/>
+      <c r="N54" s="156"/>
+      <c r="O54" s="156"/>
+      <c r="P54" s="156"/>
+      <c r="Q54" s="159"/>
+      <c r="R54" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S54" s="215"/>
-      <c r="T54" s="215"/>
-      <c r="U54" s="215"/>
-      <c r="V54" s="215"/>
-      <c r="W54" s="215"/>
-      <c r="X54" s="217" t="s">
+      <c r="S54" s="156"/>
+      <c r="T54" s="156"/>
+      <c r="U54" s="156"/>
+      <c r="V54" s="156"/>
+      <c r="W54" s="156"/>
+      <c r="X54" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="Y54" s="215"/>
-      <c r="Z54" s="216"/>
-      <c r="AA54" s="216"/>
-      <c r="AB54" s="216"/>
-      <c r="AC54" s="216"/>
-      <c r="AD54" s="215"/>
-      <c r="AE54" s="215"/>
-      <c r="AF54" s="215"/>
-      <c r="AG54" s="215"/>
-      <c r="AH54" s="215"/>
-      <c r="AI54" s="215"/>
-      <c r="AJ54" s="215"/>
-      <c r="AK54" s="213"/>
-      <c r="AL54" s="221" t="s">
+      <c r="Y54" s="156"/>
+      <c r="Z54" s="157"/>
+      <c r="AA54" s="157"/>
+      <c r="AB54" s="157"/>
+      <c r="AC54" s="157"/>
+      <c r="AD54" s="156"/>
+      <c r="AE54" s="156"/>
+      <c r="AF54" s="156"/>
+      <c r="AG54" s="156"/>
+      <c r="AH54" s="156"/>
+      <c r="AI54" s="156"/>
+      <c r="AJ54" s="156"/>
+      <c r="AK54" s="154"/>
+      <c r="AL54" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM54" s="213"/>
-      <c r="AN54" s="213"/>
-      <c r="AO54" s="213"/>
-      <c r="AP54" s="213"/>
-      <c r="AQ54" s="213"/>
-      <c r="AR54" s="213"/>
-      <c r="AS54" s="213"/>
-      <c r="AT54" s="215"/>
-      <c r="AU54" s="215"/>
-      <c r="AV54" s="215"/>
-      <c r="AW54" s="215"/>
-      <c r="AX54" s="221" t="s">
+      <c r="AM54" s="154"/>
+      <c r="AN54" s="154"/>
+      <c r="AO54" s="154"/>
+      <c r="AP54" s="154"/>
+      <c r="AQ54" s="154"/>
+      <c r="AR54" s="154"/>
+      <c r="AS54" s="154"/>
+      <c r="AT54" s="156"/>
+      <c r="AU54" s="156"/>
+      <c r="AV54" s="156"/>
+      <c r="AW54" s="156"/>
+      <c r="AX54" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY54" s="213"/>
-      <c r="AZ54" s="213"/>
-      <c r="BA54" s="213"/>
-      <c r="BF54" s="213"/>
-      <c r="BG54" s="213"/>
-      <c r="BH54" s="213"/>
-      <c r="BI54" s="214"/>
-      <c r="BJ54" s="213"/>
-      <c r="BK54" s="213"/>
-      <c r="BL54" s="213"/>
-      <c r="BM54" s="214"/>
-      <c r="BN54" s="213"/>
-      <c r="BO54" s="213"/>
-      <c r="BP54" s="212"/>
-      <c r="BQ54" s="214"/>
-      <c r="BR54" s="213"/>
-      <c r="BS54" s="213"/>
-      <c r="BT54" s="212"/>
-    </row>
-    <row r="55" spans="1:72" ht="13.2">
-      <c r="A55" s="204"/>
-      <c r="B55" s="217"/>
-      <c r="C55" s="215"/>
-      <c r="D55" s="215"/>
-      <c r="E55" s="218"/>
-      <c r="F55" s="217"/>
-      <c r="G55" s="215"/>
-      <c r="H55" s="215"/>
-      <c r="I55" s="215"/>
-      <c r="L55" s="217"/>
-      <c r="M55" s="215"/>
-      <c r="N55" s="215"/>
-      <c r="O55" s="215"/>
-      <c r="P55" s="215"/>
-      <c r="Q55" s="218"/>
-      <c r="R55" s="217"/>
-      <c r="S55" s="215"/>
-      <c r="T55" s="215"/>
-      <c r="U55" s="215"/>
-      <c r="V55" s="215"/>
-      <c r="W55" s="215"/>
-      <c r="X55" s="217" t="s">
+      <c r="AY54" s="154"/>
+      <c r="AZ54" s="154"/>
+      <c r="BA54" s="154"/>
+      <c r="BF54" s="154"/>
+      <c r="BG54" s="154"/>
+      <c r="BH54" s="154"/>
+      <c r="BI54" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ54" s="239"/>
+      <c r="BK54" s="239"/>
+      <c r="BL54" s="154"/>
+      <c r="BM54" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN54" s="153"/>
+      <c r="BO54" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP54" s="154"/>
+      <c r="BQ54" s="154"/>
+      <c r="BR54" s="153"/>
+    </row>
+    <row r="55" spans="1:70" ht="13.2">
+      <c r="A55" s="145"/>
+      <c r="B55" s="158"/>
+      <c r="C55" s="156"/>
+      <c r="D55" s="156"/>
+      <c r="E55" s="159"/>
+      <c r="F55" s="158"/>
+      <c r="G55" s="156"/>
+      <c r="H55" s="156"/>
+      <c r="I55" s="156"/>
+      <c r="L55" s="158"/>
+      <c r="M55" s="156"/>
+      <c r="N55" s="156"/>
+      <c r="O55" s="156"/>
+      <c r="P55" s="156"/>
+      <c r="Q55" s="159"/>
+      <c r="R55" s="158"/>
+      <c r="S55" s="156"/>
+      <c r="T55" s="156"/>
+      <c r="U55" s="156"/>
+      <c r="V55" s="156"/>
+      <c r="W55" s="156"/>
+      <c r="X55" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="Y55" s="215"/>
-      <c r="Z55" s="216"/>
-      <c r="AA55" s="216"/>
-      <c r="AB55" s="216"/>
-      <c r="AC55" s="216"/>
-      <c r="AD55" s="215"/>
-      <c r="AE55" s="215"/>
-      <c r="AF55" s="215"/>
-      <c r="AG55" s="215"/>
-      <c r="AH55" s="215"/>
-      <c r="AI55" s="215"/>
-      <c r="AJ55" s="215"/>
-      <c r="AK55" s="213"/>
-      <c r="AL55" s="214" t="s">
+      <c r="Y55" s="156"/>
+      <c r="Z55" s="157"/>
+      <c r="AA55" s="157"/>
+      <c r="AB55" s="157"/>
+      <c r="AC55" s="157"/>
+      <c r="AD55" s="156"/>
+      <c r="AE55" s="156"/>
+      <c r="AF55" s="156"/>
+      <c r="AG55" s="156"/>
+      <c r="AH55" s="156"/>
+      <c r="AI55" s="156"/>
+      <c r="AJ55" s="156"/>
+      <c r="AK55" s="154"/>
+      <c r="AL55" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM55" s="213"/>
-      <c r="AN55" s="213"/>
-      <c r="AO55" s="213"/>
-      <c r="AP55" s="213"/>
-      <c r="AQ55" s="213"/>
-      <c r="AR55" s="213"/>
-      <c r="AS55" s="213"/>
-      <c r="AT55" s="215"/>
-      <c r="AU55" s="215"/>
-      <c r="AV55" s="215"/>
-      <c r="AW55" s="215"/>
-      <c r="AX55" s="214"/>
-      <c r="AY55" s="213"/>
-      <c r="AZ55" s="213"/>
-      <c r="BA55" s="213"/>
-      <c r="BF55" s="213"/>
-      <c r="BG55" s="213"/>
-      <c r="BH55" s="213"/>
-      <c r="BI55" s="214"/>
-      <c r="BJ55" s="213"/>
-      <c r="BK55" s="213"/>
-      <c r="BL55" s="213"/>
-      <c r="BM55" s="214"/>
-      <c r="BN55" s="213"/>
-      <c r="BO55" s="213"/>
-      <c r="BP55" s="212"/>
-      <c r="BQ55" s="214"/>
-      <c r="BR55" s="213"/>
-      <c r="BS55" s="213"/>
-      <c r="BT55" s="212"/>
-    </row>
-    <row r="56" spans="1:72" ht="12">
-      <c r="A56" s="228"/>
-      <c r="B56" s="210"/>
-      <c r="C56" s="208"/>
-      <c r="D56" s="208"/>
-      <c r="E56" s="211"/>
-      <c r="F56" s="210"/>
-      <c r="G56" s="208"/>
-      <c r="H56" s="208"/>
-      <c r="I56" s="208"/>
+      <c r="AM55" s="154"/>
+      <c r="AN55" s="154"/>
+      <c r="AO55" s="154"/>
+      <c r="AP55" s="154"/>
+      <c r="AQ55" s="154"/>
+      <c r="AR55" s="154"/>
+      <c r="AS55" s="154"/>
+      <c r="AT55" s="156"/>
+      <c r="AU55" s="156"/>
+      <c r="AV55" s="156"/>
+      <c r="AW55" s="156"/>
+      <c r="AX55" s="155"/>
+      <c r="AY55" s="154"/>
+      <c r="AZ55" s="154"/>
+      <c r="BA55" s="154"/>
+      <c r="BF55" s="154"/>
+      <c r="BG55" s="154"/>
+      <c r="BH55" s="154"/>
+      <c r="BI55" s="155"/>
+      <c r="BJ55" s="173"/>
+      <c r="BK55" s="173"/>
+      <c r="BL55" s="154"/>
+      <c r="BM55" s="155"/>
+      <c r="BN55" s="153"/>
+      <c r="BO55" s="155"/>
+      <c r="BP55" s="154"/>
+      <c r="BQ55" s="154"/>
+      <c r="BR55" s="153"/>
+    </row>
+    <row r="56" spans="1:70" ht="12">
+      <c r="A56" s="169"/>
+      <c r="B56" s="151"/>
+      <c r="C56" s="149"/>
+      <c r="D56" s="149"/>
+      <c r="E56" s="152"/>
+      <c r="F56" s="151"/>
+      <c r="G56" s="149"/>
+      <c r="H56" s="149"/>
+      <c r="I56" s="149"/>
       <c r="J56" s="24"/>
       <c r="K56" s="25"/>
-      <c r="L56" s="210"/>
-      <c r="M56" s="208"/>
-      <c r="N56" s="208"/>
-      <c r="O56" s="208"/>
-      <c r="P56" s="208"/>
-      <c r="Q56" s="211"/>
-      <c r="R56" s="210"/>
-      <c r="S56" s="208"/>
-      <c r="T56" s="208"/>
-      <c r="U56" s="208"/>
-      <c r="V56" s="208"/>
-      <c r="W56" s="211"/>
-      <c r="X56" s="210" t="s">
+      <c r="L56" s="151"/>
+      <c r="M56" s="149"/>
+      <c r="N56" s="149"/>
+      <c r="O56" s="149"/>
+      <c r="P56" s="149"/>
+      <c r="Q56" s="152"/>
+      <c r="R56" s="151"/>
+      <c r="S56" s="149"/>
+      <c r="T56" s="149"/>
+      <c r="U56" s="149"/>
+      <c r="V56" s="149"/>
+      <c r="W56" s="152"/>
+      <c r="X56" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="Y56" s="208"/>
-      <c r="Z56" s="209"/>
-      <c r="AA56" s="209"/>
-      <c r="AB56" s="209"/>
-      <c r="AC56" s="209"/>
-      <c r="AD56" s="208"/>
-      <c r="AE56" s="208"/>
-      <c r="AF56" s="208"/>
-      <c r="AG56" s="208"/>
-      <c r="AH56" s="208"/>
-      <c r="AI56" s="208"/>
-      <c r="AJ56" s="208"/>
-      <c r="AK56" s="206"/>
-      <c r="AL56" s="207"/>
-      <c r="AM56" s="206"/>
-      <c r="AN56" s="206"/>
-      <c r="AO56" s="206"/>
-      <c r="AP56" s="206"/>
-      <c r="AQ56" s="206"/>
-      <c r="AR56" s="206"/>
-      <c r="AS56" s="206"/>
-      <c r="AT56" s="208"/>
-      <c r="AU56" s="208"/>
-      <c r="AV56" s="208"/>
-      <c r="AW56" s="208"/>
-      <c r="AX56" s="207"/>
-      <c r="AY56" s="206"/>
-      <c r="AZ56" s="206"/>
-      <c r="BA56" s="206"/>
+      <c r="Y56" s="149"/>
+      <c r="Z56" s="150"/>
+      <c r="AA56" s="150"/>
+      <c r="AB56" s="150"/>
+      <c r="AC56" s="150"/>
+      <c r="AD56" s="149"/>
+      <c r="AE56" s="149"/>
+      <c r="AF56" s="149"/>
+      <c r="AG56" s="149"/>
+      <c r="AH56" s="149"/>
+      <c r="AI56" s="149"/>
+      <c r="AJ56" s="149"/>
+      <c r="AK56" s="147"/>
+      <c r="AL56" s="148"/>
+      <c r="AM56" s="147"/>
+      <c r="AN56" s="147"/>
+      <c r="AO56" s="147"/>
+      <c r="AP56" s="147"/>
+      <c r="AQ56" s="147"/>
+      <c r="AR56" s="147"/>
+      <c r="AS56" s="147"/>
+      <c r="AT56" s="149"/>
+      <c r="AU56" s="149"/>
+      <c r="AV56" s="149"/>
+      <c r="AW56" s="149"/>
+      <c r="AX56" s="148"/>
+      <c r="AY56" s="147"/>
+      <c r="AZ56" s="147"/>
+      <c r="BA56" s="147"/>
       <c r="BB56" s="23"/>
       <c r="BC56" s="23"/>
       <c r="BD56" s="21"/>
       <c r="BE56" s="21"/>
-      <c r="BF56" s="206"/>
-      <c r="BG56" s="206"/>
-      <c r="BH56" s="206"/>
-      <c r="BI56" s="207"/>
-      <c r="BJ56" s="206"/>
-      <c r="BK56" s="206"/>
-      <c r="BL56" s="206"/>
-      <c r="BM56" s="207"/>
-      <c r="BN56" s="206"/>
-      <c r="BO56" s="206"/>
-      <c r="BP56" s="205"/>
-      <c r="BQ56" s="207"/>
-      <c r="BR56" s="206"/>
-      <c r="BS56" s="206"/>
-      <c r="BT56" s="205"/>
-    </row>
-    <row r="57" spans="1:72" ht="12">
-      <c r="A57" s="227" t="s">
+      <c r="BF56" s="147"/>
+      <c r="BG56" s="147"/>
+      <c r="BH56" s="147"/>
+      <c r="BI56" s="148"/>
+      <c r="BJ56" s="147"/>
+      <c r="BK56" s="147"/>
+      <c r="BL56" s="147"/>
+      <c r="BM56" s="148"/>
+      <c r="BN56" s="146"/>
+      <c r="BO56" s="148"/>
+      <c r="BP56" s="147"/>
+      <c r="BQ56" s="147"/>
+      <c r="BR56" s="146"/>
+    </row>
+    <row r="57" spans="1:70" ht="12">
+      <c r="A57" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="B57" s="217" t="s">
+      <c r="B57" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="215"/>
-      <c r="D57" s="215"/>
-      <c r="E57" s="218"/>
-      <c r="F57" s="217" t="s">
+      <c r="C57" s="156"/>
+      <c r="D57" s="156"/>
+      <c r="E57" s="159"/>
+      <c r="F57" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G57" s="215"/>
-      <c r="H57" s="215"/>
-      <c r="I57" s="215"/>
-      <c r="L57" s="217" t="s">
+      <c r="G57" s="156"/>
+      <c r="H57" s="156"/>
+      <c r="I57" s="156"/>
+      <c r="L57" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M57" s="215"/>
-      <c r="N57" s="215"/>
-      <c r="O57" s="215"/>
-      <c r="P57" s="215"/>
-      <c r="Q57" s="218"/>
-      <c r="R57" s="217" t="s">
+      <c r="M57" s="156"/>
+      <c r="N57" s="156"/>
+      <c r="O57" s="156"/>
+      <c r="P57" s="156"/>
+      <c r="Q57" s="159"/>
+      <c r="R57" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S57" s="215"/>
-      <c r="T57" s="215"/>
-      <c r="U57" s="215"/>
-      <c r="V57" s="215"/>
-      <c r="W57" s="215"/>
-      <c r="X57" s="217" t="s">
+      <c r="S57" s="156"/>
+      <c r="T57" s="156"/>
+      <c r="U57" s="156"/>
+      <c r="V57" s="156"/>
+      <c r="W57" s="156"/>
+      <c r="X57" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="Y57" s="215"/>
-      <c r="Z57" s="216"/>
-      <c r="AA57" s="216"/>
-      <c r="AB57" s="216"/>
-      <c r="AC57" s="216"/>
-      <c r="AD57" s="215"/>
-      <c r="AE57" s="215"/>
-      <c r="AF57" s="215"/>
-      <c r="AG57" s="215"/>
-      <c r="AH57" s="215"/>
-      <c r="AI57" s="215"/>
-      <c r="AJ57" s="215"/>
-      <c r="AK57" s="213"/>
-      <c r="AL57" s="221" t="s">
+      <c r="Y57" s="156"/>
+      <c r="Z57" s="157"/>
+      <c r="AA57" s="157"/>
+      <c r="AB57" s="157"/>
+      <c r="AC57" s="157"/>
+      <c r="AD57" s="156"/>
+      <c r="AE57" s="156"/>
+      <c r="AF57" s="156"/>
+      <c r="AG57" s="156"/>
+      <c r="AH57" s="156"/>
+      <c r="AI57" s="156"/>
+      <c r="AJ57" s="156"/>
+      <c r="AK57" s="154"/>
+      <c r="AL57" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM57" s="213"/>
-      <c r="AN57" s="213"/>
-      <c r="AO57" s="213"/>
-      <c r="AP57" s="213"/>
-      <c r="AQ57" s="213"/>
-      <c r="AR57" s="213"/>
-      <c r="AS57" s="213"/>
-      <c r="AT57" s="215"/>
-      <c r="AU57" s="215"/>
-      <c r="AV57" s="215"/>
-      <c r="AW57" s="215"/>
-      <c r="AX57" s="221" t="s">
+      <c r="AM57" s="154"/>
+      <c r="AN57" s="154"/>
+      <c r="AO57" s="154"/>
+      <c r="AP57" s="154"/>
+      <c r="AQ57" s="154"/>
+      <c r="AR57" s="154"/>
+      <c r="AS57" s="154"/>
+      <c r="AT57" s="156"/>
+      <c r="AU57" s="156"/>
+      <c r="AV57" s="156"/>
+      <c r="AW57" s="156"/>
+      <c r="AX57" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY57" s="213"/>
-      <c r="AZ57" s="213"/>
-      <c r="BA57" s="213"/>
-      <c r="BF57" s="213"/>
-      <c r="BG57" s="213"/>
-      <c r="BH57" s="213"/>
-      <c r="BI57" s="214"/>
-      <c r="BJ57" s="213"/>
-      <c r="BK57" s="213"/>
-      <c r="BL57" s="213"/>
-      <c r="BM57" s="214"/>
-      <c r="BN57" s="213"/>
-      <c r="BO57" s="213"/>
-      <c r="BP57" s="212"/>
-      <c r="BQ57" s="214"/>
-      <c r="BR57" s="213"/>
-      <c r="BS57" s="213"/>
-      <c r="BT57" s="212"/>
-    </row>
-    <row r="58" spans="1:72" ht="13.2">
-      <c r="A58" s="204"/>
-      <c r="B58" s="217"/>
-      <c r="C58" s="215"/>
-      <c r="D58" s="215"/>
-      <c r="E58" s="218"/>
-      <c r="F58" s="217"/>
-      <c r="G58" s="215"/>
-      <c r="H58" s="215"/>
-      <c r="I58" s="215"/>
-      <c r="L58" s="217"/>
-      <c r="M58" s="215"/>
-      <c r="N58" s="215"/>
-      <c r="O58" s="215"/>
-      <c r="P58" s="215"/>
-      <c r="Q58" s="218"/>
-      <c r="R58" s="217"/>
-      <c r="S58" s="215"/>
-      <c r="T58" s="215"/>
-      <c r="U58" s="215"/>
-      <c r="V58" s="215"/>
-      <c r="W58" s="215"/>
-      <c r="X58" s="217" t="s">
+      <c r="AY57" s="154"/>
+      <c r="AZ57" s="154"/>
+      <c r="BA57" s="154"/>
+      <c r="BF57" s="154"/>
+      <c r="BG57" s="154"/>
+      <c r="BH57" s="154"/>
+      <c r="BI57" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ57" s="239"/>
+      <c r="BK57" s="239"/>
+      <c r="BL57" s="154"/>
+      <c r="BM57" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN57" s="153"/>
+      <c r="BO57" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP57" s="154"/>
+      <c r="BQ57" s="154"/>
+      <c r="BR57" s="153"/>
+    </row>
+    <row r="58" spans="1:70" ht="13.2">
+      <c r="A58" s="145"/>
+      <c r="B58" s="158"/>
+      <c r="C58" s="156"/>
+      <c r="D58" s="156"/>
+      <c r="E58" s="159"/>
+      <c r="F58" s="158"/>
+      <c r="G58" s="156"/>
+      <c r="H58" s="156"/>
+      <c r="I58" s="156"/>
+      <c r="L58" s="158"/>
+      <c r="M58" s="156"/>
+      <c r="N58" s="156"/>
+      <c r="O58" s="156"/>
+      <c r="P58" s="156"/>
+      <c r="Q58" s="159"/>
+      <c r="R58" s="158"/>
+      <c r="S58" s="156"/>
+      <c r="T58" s="156"/>
+      <c r="U58" s="156"/>
+      <c r="V58" s="156"/>
+      <c r="W58" s="156"/>
+      <c r="X58" s="158" t="s">
         <v>146</v>
       </c>
-      <c r="Y58" s="215"/>
-      <c r="Z58" s="216"/>
-      <c r="AA58" s="216"/>
-      <c r="AB58" s="216"/>
-      <c r="AC58" s="216"/>
-      <c r="AD58" s="215"/>
-      <c r="AE58" s="215"/>
-      <c r="AF58" s="215"/>
-      <c r="AG58" s="215"/>
-      <c r="AH58" s="215"/>
-      <c r="AI58" s="215"/>
-      <c r="AJ58" s="215"/>
-      <c r="AK58" s="213"/>
-      <c r="AL58" s="214" t="s">
+      <c r="Y58" s="156"/>
+      <c r="Z58" s="157"/>
+      <c r="AA58" s="157"/>
+      <c r="AB58" s="157"/>
+      <c r="AC58" s="157"/>
+      <c r="AD58" s="156"/>
+      <c r="AE58" s="156"/>
+      <c r="AF58" s="156"/>
+      <c r="AG58" s="156"/>
+      <c r="AH58" s="156"/>
+      <c r="AI58" s="156"/>
+      <c r="AJ58" s="156"/>
+      <c r="AK58" s="154"/>
+      <c r="AL58" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM58" s="213"/>
-      <c r="AN58" s="213"/>
-      <c r="AO58" s="213"/>
-      <c r="AP58" s="213"/>
-      <c r="AQ58" s="213"/>
-      <c r="AR58" s="213"/>
-      <c r="AS58" s="213"/>
-      <c r="AT58" s="215"/>
-      <c r="AU58" s="215"/>
-      <c r="AV58" s="215"/>
-      <c r="AW58" s="215"/>
-      <c r="AX58" s="214"/>
-      <c r="AY58" s="213"/>
-      <c r="AZ58" s="213"/>
-      <c r="BA58" s="213"/>
-      <c r="BF58" s="213"/>
-      <c r="BG58" s="213"/>
-      <c r="BH58" s="213"/>
-      <c r="BI58" s="214"/>
-      <c r="BJ58" s="213"/>
-      <c r="BK58" s="213"/>
-      <c r="BL58" s="213"/>
-      <c r="BM58" s="214"/>
-      <c r="BN58" s="213"/>
-      <c r="BO58" s="213"/>
-      <c r="BP58" s="212"/>
-      <c r="BQ58" s="214"/>
-      <c r="BR58" s="213"/>
-      <c r="BS58" s="213"/>
-      <c r="BT58" s="212"/>
-    </row>
-    <row r="59" spans="1:72" ht="12">
-      <c r="A59" s="228"/>
-      <c r="B59" s="210"/>
-      <c r="C59" s="208"/>
-      <c r="D59" s="208"/>
-      <c r="E59" s="211"/>
-      <c r="F59" s="210"/>
-      <c r="G59" s="208"/>
-      <c r="H59" s="208"/>
-      <c r="I59" s="208"/>
+      <c r="AM58" s="154"/>
+      <c r="AN58" s="154"/>
+      <c r="AO58" s="154"/>
+      <c r="AP58" s="154"/>
+      <c r="AQ58" s="154"/>
+      <c r="AR58" s="154"/>
+      <c r="AS58" s="154"/>
+      <c r="AT58" s="156"/>
+      <c r="AU58" s="156"/>
+      <c r="AV58" s="156"/>
+      <c r="AW58" s="156"/>
+      <c r="AX58" s="155"/>
+      <c r="AY58" s="154"/>
+      <c r="AZ58" s="154"/>
+      <c r="BA58" s="154"/>
+      <c r="BF58" s="154"/>
+      <c r="BG58" s="154"/>
+      <c r="BH58" s="154"/>
+      <c r="BI58" s="155"/>
+      <c r="BJ58" s="173"/>
+      <c r="BK58" s="173"/>
+      <c r="BL58" s="154"/>
+      <c r="BM58" s="155"/>
+      <c r="BN58" s="153"/>
+      <c r="BO58" s="155"/>
+      <c r="BP58" s="154"/>
+      <c r="BQ58" s="154"/>
+      <c r="BR58" s="153"/>
+    </row>
+    <row r="59" spans="1:70" ht="12">
+      <c r="A59" s="169"/>
+      <c r="B59" s="151"/>
+      <c r="C59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="152"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
       <c r="J59" s="24"/>
       <c r="K59" s="25"/>
-      <c r="L59" s="210"/>
-      <c r="M59" s="208"/>
-      <c r="N59" s="208"/>
-      <c r="O59" s="208"/>
-      <c r="P59" s="208"/>
-      <c r="Q59" s="211"/>
-      <c r="R59" s="210"/>
-      <c r="S59" s="208"/>
-      <c r="T59" s="208"/>
-      <c r="U59" s="208"/>
-      <c r="V59" s="208"/>
-      <c r="W59" s="211"/>
-      <c r="X59" s="210" t="s">
+      <c r="L59" s="151"/>
+      <c r="M59" s="149"/>
+      <c r="N59" s="149"/>
+      <c r="O59" s="149"/>
+      <c r="P59" s="149"/>
+      <c r="Q59" s="152"/>
+      <c r="R59" s="151"/>
+      <c r="S59" s="149"/>
+      <c r="T59" s="149"/>
+      <c r="U59" s="149"/>
+      <c r="V59" s="149"/>
+      <c r="W59" s="152"/>
+      <c r="X59" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="Y59" s="208"/>
-      <c r="Z59" s="209"/>
-      <c r="AA59" s="209"/>
-      <c r="AB59" s="209"/>
-      <c r="AC59" s="209"/>
-      <c r="AD59" s="208"/>
-      <c r="AE59" s="208"/>
-      <c r="AF59" s="208"/>
-      <c r="AG59" s="208"/>
-      <c r="AH59" s="208"/>
-      <c r="AI59" s="208"/>
-      <c r="AJ59" s="208"/>
-      <c r="AK59" s="206"/>
-      <c r="AL59" s="207"/>
-      <c r="AM59" s="206"/>
-      <c r="AN59" s="206"/>
-      <c r="AO59" s="206"/>
-      <c r="AP59" s="206"/>
-      <c r="AQ59" s="206"/>
-      <c r="AR59" s="206"/>
-      <c r="AS59" s="206"/>
-      <c r="AT59" s="208"/>
-      <c r="AU59" s="208"/>
-      <c r="AV59" s="208"/>
-      <c r="AW59" s="208"/>
-      <c r="AX59" s="207"/>
-      <c r="AY59" s="206"/>
-      <c r="AZ59" s="206"/>
-      <c r="BA59" s="206"/>
+      <c r="Y59" s="149"/>
+      <c r="Z59" s="150"/>
+      <c r="AA59" s="150"/>
+      <c r="AB59" s="150"/>
+      <c r="AC59" s="150"/>
+      <c r="AD59" s="149"/>
+      <c r="AE59" s="149"/>
+      <c r="AF59" s="149"/>
+      <c r="AG59" s="149"/>
+      <c r="AH59" s="149"/>
+      <c r="AI59" s="149"/>
+      <c r="AJ59" s="149"/>
+      <c r="AK59" s="147"/>
+      <c r="AL59" s="148"/>
+      <c r="AM59" s="147"/>
+      <c r="AN59" s="147"/>
+      <c r="AO59" s="147"/>
+      <c r="AP59" s="147"/>
+      <c r="AQ59" s="147"/>
+      <c r="AR59" s="147"/>
+      <c r="AS59" s="147"/>
+      <c r="AT59" s="149"/>
+      <c r="AU59" s="149"/>
+      <c r="AV59" s="149"/>
+      <c r="AW59" s="149"/>
+      <c r="AX59" s="148"/>
+      <c r="AY59" s="147"/>
+      <c r="AZ59" s="147"/>
+      <c r="BA59" s="147"/>
       <c r="BB59" s="23"/>
       <c r="BC59" s="23"/>
       <c r="BD59" s="21"/>
       <c r="BE59" s="21"/>
-      <c r="BF59" s="206"/>
-      <c r="BG59" s="206"/>
-      <c r="BH59" s="206"/>
-      <c r="BI59" s="207"/>
-      <c r="BJ59" s="206"/>
-      <c r="BK59" s="206"/>
-      <c r="BL59" s="206"/>
-      <c r="BM59" s="207"/>
-      <c r="BN59" s="206"/>
-      <c r="BO59" s="206"/>
-      <c r="BP59" s="205"/>
-      <c r="BQ59" s="207"/>
-      <c r="BR59" s="206"/>
-      <c r="BS59" s="206"/>
-      <c r="BT59" s="205"/>
-    </row>
-    <row r="60" spans="1:72" ht="12">
-      <c r="A60" s="227" t="s">
+      <c r="BF59" s="147"/>
+      <c r="BG59" s="147"/>
+      <c r="BH59" s="147"/>
+      <c r="BI59" s="148"/>
+      <c r="BJ59" s="147"/>
+      <c r="BK59" s="147"/>
+      <c r="BL59" s="147"/>
+      <c r="BM59" s="148"/>
+      <c r="BN59" s="146"/>
+      <c r="BO59" s="148"/>
+      <c r="BP59" s="147"/>
+      <c r="BQ59" s="147"/>
+      <c r="BR59" s="146"/>
+    </row>
+    <row r="60" spans="1:70" ht="12">
+      <c r="A60" s="168" t="s">
         <v>147</v>
       </c>
-      <c r="B60" s="217" t="s">
+      <c r="B60" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="215"/>
-      <c r="D60" s="215"/>
-      <c r="E60" s="218"/>
-      <c r="F60" s="217" t="s">
+      <c r="C60" s="156"/>
+      <c r="D60" s="156"/>
+      <c r="E60" s="159"/>
+      <c r="F60" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G60" s="215"/>
-      <c r="H60" s="215"/>
-      <c r="I60" s="215"/>
-      <c r="L60" s="217" t="s">
+      <c r="G60" s="156"/>
+      <c r="H60" s="156"/>
+      <c r="I60" s="156"/>
+      <c r="L60" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M60" s="215"/>
-      <c r="N60" s="215"/>
-      <c r="O60" s="215"/>
-      <c r="P60" s="215"/>
-      <c r="Q60" s="218"/>
-      <c r="R60" s="217" t="s">
+      <c r="M60" s="156"/>
+      <c r="N60" s="156"/>
+      <c r="O60" s="156"/>
+      <c r="P60" s="156"/>
+      <c r="Q60" s="159"/>
+      <c r="R60" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S60" s="215"/>
-      <c r="T60" s="215"/>
-      <c r="U60" s="215"/>
-      <c r="V60" s="215"/>
-      <c r="W60" s="215"/>
-      <c r="X60" s="217" t="s">
+      <c r="S60" s="156"/>
+      <c r="T60" s="156"/>
+      <c r="U60" s="156"/>
+      <c r="V60" s="156"/>
+      <c r="W60" s="156"/>
+      <c r="X60" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="Y60" s="215"/>
-      <c r="Z60" s="216"/>
-      <c r="AA60" s="216"/>
-      <c r="AB60" s="216"/>
-      <c r="AC60" s="216"/>
-      <c r="AD60" s="215"/>
-      <c r="AE60" s="215"/>
-      <c r="AF60" s="215"/>
-      <c r="AG60" s="215"/>
-      <c r="AH60" s="215"/>
-      <c r="AI60" s="215"/>
-      <c r="AJ60" s="215"/>
-      <c r="AK60" s="213"/>
-      <c r="AL60" s="221" t="s">
+      <c r="Y60" s="156"/>
+      <c r="Z60" s="157"/>
+      <c r="AA60" s="157"/>
+      <c r="AB60" s="157"/>
+      <c r="AC60" s="157"/>
+      <c r="AD60" s="156"/>
+      <c r="AE60" s="156"/>
+      <c r="AF60" s="156"/>
+      <c r="AG60" s="156"/>
+      <c r="AH60" s="156"/>
+      <c r="AI60" s="156"/>
+      <c r="AJ60" s="156"/>
+      <c r="AK60" s="154"/>
+      <c r="AL60" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM60" s="213"/>
-      <c r="AN60" s="213"/>
-      <c r="AO60" s="213"/>
-      <c r="AP60" s="213"/>
-      <c r="AQ60" s="213"/>
-      <c r="AR60" s="213"/>
-      <c r="AS60" s="213"/>
-      <c r="AT60" s="215"/>
-      <c r="AU60" s="215"/>
-      <c r="AV60" s="215"/>
-      <c r="AW60" s="215"/>
-      <c r="AX60" s="221" t="s">
+      <c r="AM60" s="154"/>
+      <c r="AN60" s="154"/>
+      <c r="AO60" s="154"/>
+      <c r="AP60" s="154"/>
+      <c r="AQ60" s="154"/>
+      <c r="AR60" s="154"/>
+      <c r="AS60" s="154"/>
+      <c r="AT60" s="156"/>
+      <c r="AU60" s="156"/>
+      <c r="AV60" s="156"/>
+      <c r="AW60" s="156"/>
+      <c r="AX60" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY60" s="213"/>
-      <c r="AZ60" s="213"/>
-      <c r="BA60" s="213"/>
-      <c r="BF60" s="213"/>
-      <c r="BG60" s="213"/>
-      <c r="BH60" s="213"/>
-      <c r="BI60" s="214"/>
-      <c r="BJ60" s="213"/>
-      <c r="BK60" s="213"/>
-      <c r="BL60" s="213"/>
-      <c r="BM60" s="214"/>
-      <c r="BN60" s="213"/>
-      <c r="BO60" s="213"/>
-      <c r="BP60" s="212"/>
-      <c r="BQ60" s="214"/>
-      <c r="BR60" s="213"/>
-      <c r="BS60" s="213"/>
-      <c r="BT60" s="212"/>
-    </row>
-    <row r="61" spans="1:72" ht="13.2">
-      <c r="A61" s="204"/>
-      <c r="B61" s="217"/>
-      <c r="C61" s="215"/>
-      <c r="D61" s="215"/>
-      <c r="E61" s="218"/>
-      <c r="F61" s="217"/>
-      <c r="G61" s="215"/>
-      <c r="H61" s="215"/>
-      <c r="I61" s="215"/>
-      <c r="L61" s="217"/>
-      <c r="M61" s="215"/>
-      <c r="N61" s="215"/>
-      <c r="O61" s="215"/>
-      <c r="P61" s="215"/>
-      <c r="Q61" s="218"/>
-      <c r="R61" s="217"/>
-      <c r="S61" s="215"/>
-      <c r="T61" s="215"/>
-      <c r="U61" s="215"/>
-      <c r="V61" s="215"/>
-      <c r="W61" s="215"/>
-      <c r="X61" s="217" t="s">
+      <c r="AY60" s="154"/>
+      <c r="AZ60" s="154"/>
+      <c r="BA60" s="154"/>
+      <c r="BF60" s="154"/>
+      <c r="BG60" s="154"/>
+      <c r="BH60" s="154"/>
+      <c r="BI60" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ60" s="239"/>
+      <c r="BK60" s="239"/>
+      <c r="BL60" s="154"/>
+      <c r="BM60" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN60" s="153"/>
+      <c r="BO60" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP60" s="154"/>
+      <c r="BQ60" s="154"/>
+      <c r="BR60" s="153"/>
+    </row>
+    <row r="61" spans="1:70" ht="13.2">
+      <c r="A61" s="145"/>
+      <c r="B61" s="158"/>
+      <c r="C61" s="156"/>
+      <c r="D61" s="156"/>
+      <c r="E61" s="159"/>
+      <c r="F61" s="158"/>
+      <c r="G61" s="156"/>
+      <c r="H61" s="156"/>
+      <c r="I61" s="156"/>
+      <c r="L61" s="158"/>
+      <c r="M61" s="156"/>
+      <c r="N61" s="156"/>
+      <c r="O61" s="156"/>
+      <c r="P61" s="156"/>
+      <c r="Q61" s="159"/>
+      <c r="R61" s="158"/>
+      <c r="S61" s="156"/>
+      <c r="T61" s="156"/>
+      <c r="U61" s="156"/>
+      <c r="V61" s="156"/>
+      <c r="W61" s="156"/>
+      <c r="X61" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="Y61" s="215"/>
-      <c r="Z61" s="216"/>
-      <c r="AA61" s="216"/>
-      <c r="AB61" s="216"/>
-      <c r="AC61" s="216"/>
-      <c r="AD61" s="215"/>
-      <c r="AE61" s="215"/>
-      <c r="AF61" s="215"/>
-      <c r="AG61" s="215"/>
-      <c r="AH61" s="215"/>
-      <c r="AI61" s="215"/>
-      <c r="AJ61" s="215"/>
-      <c r="AK61" s="213"/>
-      <c r="AL61" s="214" t="s">
+      <c r="Y61" s="156"/>
+      <c r="Z61" s="157"/>
+      <c r="AA61" s="157"/>
+      <c r="AB61" s="157"/>
+      <c r="AC61" s="157"/>
+      <c r="AD61" s="156"/>
+      <c r="AE61" s="156"/>
+      <c r="AF61" s="156"/>
+      <c r="AG61" s="156"/>
+      <c r="AH61" s="156"/>
+      <c r="AI61" s="156"/>
+      <c r="AJ61" s="156"/>
+      <c r="AK61" s="154"/>
+      <c r="AL61" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM61" s="213"/>
-      <c r="AN61" s="213"/>
-      <c r="AO61" s="213"/>
-      <c r="AP61" s="213"/>
-      <c r="AQ61" s="213"/>
-      <c r="AR61" s="213"/>
-      <c r="AS61" s="213"/>
-      <c r="AT61" s="215"/>
-      <c r="AU61" s="215"/>
-      <c r="AV61" s="215"/>
-      <c r="AW61" s="215"/>
-      <c r="AX61" s="214"/>
-      <c r="AY61" s="213"/>
-      <c r="AZ61" s="213"/>
-      <c r="BA61" s="213"/>
-      <c r="BF61" s="213"/>
-      <c r="BG61" s="213"/>
-      <c r="BH61" s="213"/>
-      <c r="BI61" s="214"/>
-      <c r="BJ61" s="213"/>
-      <c r="BK61" s="213"/>
-      <c r="BL61" s="213"/>
-      <c r="BM61" s="214"/>
-      <c r="BN61" s="213"/>
-      <c r="BO61" s="213"/>
-      <c r="BP61" s="212"/>
-      <c r="BQ61" s="214"/>
-      <c r="BR61" s="213"/>
-      <c r="BS61" s="213"/>
-      <c r="BT61" s="212"/>
-    </row>
-    <row r="62" spans="1:72" ht="12">
-      <c r="A62" s="228"/>
-      <c r="B62" s="210"/>
-      <c r="C62" s="208"/>
-      <c r="D62" s="208"/>
-      <c r="E62" s="211"/>
-      <c r="F62" s="210"/>
-      <c r="G62" s="208"/>
-      <c r="H62" s="208"/>
-      <c r="I62" s="208"/>
+      <c r="AM61" s="154"/>
+      <c r="AN61" s="154"/>
+      <c r="AO61" s="154"/>
+      <c r="AP61" s="154"/>
+      <c r="AQ61" s="154"/>
+      <c r="AR61" s="154"/>
+      <c r="AS61" s="154"/>
+      <c r="AT61" s="156"/>
+      <c r="AU61" s="156"/>
+      <c r="AV61" s="156"/>
+      <c r="AW61" s="156"/>
+      <c r="AX61" s="155"/>
+      <c r="AY61" s="154"/>
+      <c r="AZ61" s="154"/>
+      <c r="BA61" s="154"/>
+      <c r="BF61" s="154"/>
+      <c r="BG61" s="154"/>
+      <c r="BH61" s="154"/>
+      <c r="BI61" s="155"/>
+      <c r="BJ61" s="173"/>
+      <c r="BK61" s="173"/>
+      <c r="BL61" s="154"/>
+      <c r="BM61" s="155"/>
+      <c r="BN61" s="153"/>
+      <c r="BO61" s="155"/>
+      <c r="BP61" s="154"/>
+      <c r="BQ61" s="154"/>
+      <c r="BR61" s="153"/>
+    </row>
+    <row r="62" spans="1:70" ht="12">
+      <c r="A62" s="169"/>
+      <c r="B62" s="151"/>
+      <c r="C62" s="149"/>
+      <c r="D62" s="149"/>
+      <c r="E62" s="152"/>
+      <c r="F62" s="151"/>
+      <c r="G62" s="149"/>
+      <c r="H62" s="149"/>
+      <c r="I62" s="149"/>
       <c r="J62" s="24"/>
       <c r="K62" s="25"/>
-      <c r="L62" s="210"/>
-      <c r="M62" s="208"/>
-      <c r="N62" s="208"/>
-      <c r="O62" s="208"/>
-      <c r="P62" s="208"/>
-      <c r="Q62" s="211"/>
-      <c r="R62" s="210"/>
-      <c r="S62" s="208"/>
-      <c r="T62" s="208"/>
-      <c r="U62" s="208"/>
-      <c r="V62" s="208"/>
-      <c r="W62" s="211"/>
-      <c r="X62" s="210" t="s">
+      <c r="L62" s="151"/>
+      <c r="M62" s="149"/>
+      <c r="N62" s="149"/>
+      <c r="O62" s="149"/>
+      <c r="P62" s="149"/>
+      <c r="Q62" s="152"/>
+      <c r="R62" s="151"/>
+      <c r="S62" s="149"/>
+      <c r="T62" s="149"/>
+      <c r="U62" s="149"/>
+      <c r="V62" s="149"/>
+      <c r="W62" s="152"/>
+      <c r="X62" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="Y62" s="208"/>
-      <c r="Z62" s="209"/>
-      <c r="AA62" s="209"/>
-      <c r="AB62" s="209"/>
-      <c r="AC62" s="209"/>
-      <c r="AD62" s="208"/>
-      <c r="AE62" s="208"/>
-      <c r="AF62" s="208"/>
-      <c r="AG62" s="208"/>
-      <c r="AH62" s="208"/>
-      <c r="AI62" s="208"/>
-      <c r="AJ62" s="208"/>
-      <c r="AK62" s="206"/>
-      <c r="AL62" s="207"/>
-      <c r="AM62" s="206"/>
-      <c r="AN62" s="206"/>
-      <c r="AO62" s="206"/>
-      <c r="AP62" s="206"/>
-      <c r="AQ62" s="206"/>
-      <c r="AR62" s="206"/>
-      <c r="AS62" s="206"/>
-      <c r="AT62" s="208"/>
-      <c r="AU62" s="208"/>
-      <c r="AV62" s="208"/>
-      <c r="AW62" s="208"/>
-      <c r="AX62" s="207"/>
-      <c r="AY62" s="206"/>
-      <c r="AZ62" s="206"/>
-      <c r="BA62" s="206"/>
+      <c r="Y62" s="149"/>
+      <c r="Z62" s="150"/>
+      <c r="AA62" s="150"/>
+      <c r="AB62" s="150"/>
+      <c r="AC62" s="150"/>
+      <c r="AD62" s="149"/>
+      <c r="AE62" s="149"/>
+      <c r="AF62" s="149"/>
+      <c r="AG62" s="149"/>
+      <c r="AH62" s="149"/>
+      <c r="AI62" s="149"/>
+      <c r="AJ62" s="149"/>
+      <c r="AK62" s="147"/>
+      <c r="AL62" s="148"/>
+      <c r="AM62" s="147"/>
+      <c r="AN62" s="147"/>
+      <c r="AO62" s="147"/>
+      <c r="AP62" s="147"/>
+      <c r="AQ62" s="147"/>
+      <c r="AR62" s="147"/>
+      <c r="AS62" s="147"/>
+      <c r="AT62" s="149"/>
+      <c r="AU62" s="149"/>
+      <c r="AV62" s="149"/>
+      <c r="AW62" s="149"/>
+      <c r="AX62" s="148"/>
+      <c r="AY62" s="147"/>
+      <c r="AZ62" s="147"/>
+      <c r="BA62" s="147"/>
       <c r="BB62" s="23"/>
       <c r="BC62" s="23"/>
       <c r="BD62" s="21"/>
       <c r="BE62" s="21"/>
-      <c r="BF62" s="206"/>
-      <c r="BG62" s="206"/>
-      <c r="BH62" s="206"/>
-      <c r="BI62" s="207"/>
-      <c r="BJ62" s="206"/>
-      <c r="BK62" s="206"/>
-      <c r="BL62" s="206"/>
-      <c r="BM62" s="207"/>
-      <c r="BN62" s="206"/>
-      <c r="BO62" s="206"/>
-      <c r="BP62" s="205"/>
-      <c r="BQ62" s="207"/>
-      <c r="BR62" s="206"/>
-      <c r="BS62" s="206"/>
-      <c r="BT62" s="205"/>
-    </row>
-    <row r="63" spans="1:72" ht="12">
-      <c r="A63" s="227" t="s">
+      <c r="BF62" s="147"/>
+      <c r="BG62" s="147"/>
+      <c r="BH62" s="147"/>
+      <c r="BI62" s="148"/>
+      <c r="BJ62" s="147"/>
+      <c r="BK62" s="147"/>
+      <c r="BL62" s="147"/>
+      <c r="BM62" s="148"/>
+      <c r="BN62" s="146"/>
+      <c r="BO62" s="148"/>
+      <c r="BP62" s="147"/>
+      <c r="BQ62" s="147"/>
+      <c r="BR62" s="146"/>
+    </row>
+    <row r="63" spans="1:70" ht="12">
+      <c r="A63" s="168" t="s">
         <v>150</v>
       </c>
-      <c r="B63" s="217" t="s">
+      <c r="B63" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C63" s="215"/>
-      <c r="D63" s="215"/>
-      <c r="E63" s="218"/>
-      <c r="F63" s="217" t="s">
+      <c r="C63" s="156"/>
+      <c r="D63" s="156"/>
+      <c r="E63" s="159"/>
+      <c r="F63" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G63" s="215"/>
-      <c r="H63" s="215"/>
-      <c r="I63" s="215"/>
-      <c r="L63" s="217" t="s">
+      <c r="G63" s="156"/>
+      <c r="H63" s="156"/>
+      <c r="I63" s="156"/>
+      <c r="L63" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="M63" s="215"/>
-      <c r="N63" s="215"/>
-      <c r="O63" s="215"/>
-      <c r="P63" s="215"/>
-      <c r="Q63" s="218"/>
-      <c r="R63" s="217" t="s">
+      <c r="M63" s="156"/>
+      <c r="N63" s="156"/>
+      <c r="O63" s="156"/>
+      <c r="P63" s="156"/>
+      <c r="Q63" s="159"/>
+      <c r="R63" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S63" s="215"/>
-      <c r="T63" s="215"/>
-      <c r="U63" s="215"/>
-      <c r="V63" s="215"/>
-      <c r="W63" s="215"/>
-      <c r="X63" s="217" t="s">
+      <c r="S63" s="156"/>
+      <c r="T63" s="156"/>
+      <c r="U63" s="156"/>
+      <c r="V63" s="156"/>
+      <c r="W63" s="156"/>
+      <c r="X63" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="Y63" s="215"/>
-      <c r="Z63" s="216"/>
-      <c r="AA63" s="216"/>
-      <c r="AB63" s="216"/>
-      <c r="AC63" s="216"/>
-      <c r="AD63" s="215"/>
-      <c r="AE63" s="215"/>
-      <c r="AF63" s="215"/>
-      <c r="AG63" s="215"/>
-      <c r="AH63" s="215"/>
-      <c r="AI63" s="215"/>
-      <c r="AJ63" s="215"/>
-      <c r="AK63" s="213"/>
-      <c r="AL63" s="221" t="s">
+      <c r="Y63" s="156"/>
+      <c r="Z63" s="157"/>
+      <c r="AA63" s="157"/>
+      <c r="AB63" s="157"/>
+      <c r="AC63" s="157"/>
+      <c r="AD63" s="156"/>
+      <c r="AE63" s="156"/>
+      <c r="AF63" s="156"/>
+      <c r="AG63" s="156"/>
+      <c r="AH63" s="156"/>
+      <c r="AI63" s="156"/>
+      <c r="AJ63" s="156"/>
+      <c r="AK63" s="154"/>
+      <c r="AL63" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM63" s="213"/>
-      <c r="AN63" s="213"/>
-      <c r="AO63" s="213"/>
-      <c r="AP63" s="213"/>
-      <c r="AQ63" s="213"/>
-      <c r="AR63" s="213"/>
-      <c r="AS63" s="213"/>
-      <c r="AT63" s="215"/>
-      <c r="AU63" s="215"/>
-      <c r="AV63" s="215"/>
-      <c r="AW63" s="215"/>
-      <c r="AX63" s="221" t="s">
+      <c r="AM63" s="154"/>
+      <c r="AN63" s="154"/>
+      <c r="AO63" s="154"/>
+      <c r="AP63" s="154"/>
+      <c r="AQ63" s="154"/>
+      <c r="AR63" s="154"/>
+      <c r="AS63" s="154"/>
+      <c r="AT63" s="156"/>
+      <c r="AU63" s="156"/>
+      <c r="AV63" s="156"/>
+      <c r="AW63" s="156"/>
+      <c r="AX63" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY63" s="213"/>
-      <c r="AZ63" s="213"/>
-      <c r="BA63" s="213"/>
-      <c r="BF63" s="213"/>
-      <c r="BG63" s="213"/>
-      <c r="BH63" s="213"/>
-      <c r="BI63" s="214"/>
-      <c r="BJ63" s="213"/>
-      <c r="BK63" s="213"/>
-      <c r="BL63" s="213"/>
-      <c r="BM63" s="214"/>
-      <c r="BN63" s="213"/>
-      <c r="BO63" s="213"/>
-      <c r="BP63" s="212"/>
-      <c r="BQ63" s="214"/>
-      <c r="BR63" s="213"/>
-      <c r="BS63" s="213"/>
-      <c r="BT63" s="212"/>
-    </row>
-    <row r="64" spans="1:72" ht="13.2">
-      <c r="A64" s="204"/>
-      <c r="B64" s="217"/>
-      <c r="C64" s="215"/>
-      <c r="D64" s="215"/>
-      <c r="E64" s="218"/>
-      <c r="F64" s="217"/>
-      <c r="G64" s="215"/>
-      <c r="H64" s="215"/>
-      <c r="I64" s="215"/>
-      <c r="L64" s="217"/>
-      <c r="M64" s="215"/>
-      <c r="N64" s="215"/>
-      <c r="O64" s="215"/>
-      <c r="P64" s="215"/>
-      <c r="Q64" s="218"/>
-      <c r="R64" s="217"/>
-      <c r="S64" s="215"/>
-      <c r="T64" s="215"/>
-      <c r="U64" s="215"/>
-      <c r="V64" s="215"/>
-      <c r="W64" s="215"/>
-      <c r="X64" s="217" t="s">
+      <c r="AY63" s="154"/>
+      <c r="AZ63" s="154"/>
+      <c r="BA63" s="154"/>
+      <c r="BF63" s="154"/>
+      <c r="BG63" s="154"/>
+      <c r="BH63" s="154"/>
+      <c r="BI63" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ63" s="239"/>
+      <c r="BK63" s="239"/>
+      <c r="BL63" s="154"/>
+      <c r="BM63" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN63" s="153"/>
+      <c r="BO63" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP63" s="154"/>
+      <c r="BQ63" s="154"/>
+      <c r="BR63" s="153"/>
+    </row>
+    <row r="64" spans="1:70" ht="13.2">
+      <c r="A64" s="145"/>
+      <c r="B64" s="158"/>
+      <c r="C64" s="156"/>
+      <c r="D64" s="156"/>
+      <c r="E64" s="159"/>
+      <c r="F64" s="158"/>
+      <c r="G64" s="156"/>
+      <c r="H64" s="156"/>
+      <c r="I64" s="156"/>
+      <c r="L64" s="158"/>
+      <c r="M64" s="156"/>
+      <c r="N64" s="156"/>
+      <c r="O64" s="156"/>
+      <c r="P64" s="156"/>
+      <c r="Q64" s="159"/>
+      <c r="R64" s="158"/>
+      <c r="S64" s="156"/>
+      <c r="T64" s="156"/>
+      <c r="U64" s="156"/>
+      <c r="V64" s="156"/>
+      <c r="W64" s="156"/>
+      <c r="X64" s="158" t="s">
         <v>151</v>
       </c>
-      <c r="Y64" s="215"/>
-      <c r="Z64" s="216"/>
-      <c r="AA64" s="216"/>
-      <c r="AB64" s="216"/>
-      <c r="AC64" s="216"/>
-      <c r="AD64" s="215"/>
-      <c r="AE64" s="215"/>
-      <c r="AF64" s="215"/>
-      <c r="AG64" s="215"/>
-      <c r="AH64" s="215"/>
-      <c r="AI64" s="215"/>
-      <c r="AJ64" s="215"/>
-      <c r="AK64" s="213"/>
-      <c r="AL64" s="214" t="s">
+      <c r="Y64" s="156"/>
+      <c r="Z64" s="157"/>
+      <c r="AA64" s="157"/>
+      <c r="AB64" s="157"/>
+      <c r="AC64" s="157"/>
+      <c r="AD64" s="156"/>
+      <c r="AE64" s="156"/>
+      <c r="AF64" s="156"/>
+      <c r="AG64" s="156"/>
+      <c r="AH64" s="156"/>
+      <c r="AI64" s="156"/>
+      <c r="AJ64" s="156"/>
+      <c r="AK64" s="154"/>
+      <c r="AL64" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM64" s="213"/>
-      <c r="AN64" s="213"/>
-      <c r="AO64" s="213"/>
-      <c r="AP64" s="213"/>
-      <c r="AQ64" s="213"/>
-      <c r="AR64" s="213"/>
-      <c r="AS64" s="213"/>
-      <c r="AT64" s="215"/>
-      <c r="AU64" s="215"/>
-      <c r="AV64" s="215"/>
-      <c r="AW64" s="215"/>
-      <c r="AX64" s="214"/>
-      <c r="AY64" s="213"/>
-      <c r="AZ64" s="213"/>
-      <c r="BA64" s="213"/>
-      <c r="BF64" s="213"/>
-      <c r="BG64" s="213"/>
-      <c r="BH64" s="213"/>
-      <c r="BI64" s="214"/>
-      <c r="BJ64" s="213"/>
-      <c r="BK64" s="213"/>
-      <c r="BL64" s="213"/>
-      <c r="BM64" s="214"/>
-      <c r="BN64" s="213"/>
-      <c r="BO64" s="213"/>
-      <c r="BP64" s="212"/>
-      <c r="BQ64" s="214"/>
-      <c r="BR64" s="213"/>
-      <c r="BS64" s="213"/>
-      <c r="BT64" s="212"/>
-    </row>
-    <row r="65" spans="1:72" ht="12">
-      <c r="A65" s="227"/>
-      <c r="B65" s="217"/>
-      <c r="C65" s="226"/>
-      <c r="D65" s="226"/>
-      <c r="E65" s="218"/>
-      <c r="F65" s="217"/>
-      <c r="G65" s="226"/>
-      <c r="H65" s="226"/>
-      <c r="I65" s="226"/>
-      <c r="L65" s="217"/>
-      <c r="M65" s="226"/>
-      <c r="N65" s="226"/>
-      <c r="O65" s="226"/>
-      <c r="P65" s="226"/>
-      <c r="Q65" s="218"/>
-      <c r="R65" s="217"/>
-      <c r="S65" s="226"/>
-      <c r="T65" s="226"/>
-      <c r="U65" s="226"/>
-      <c r="V65" s="226"/>
-      <c r="W65" s="218"/>
-      <c r="X65" s="217" t="s">
+      <c r="AM64" s="154"/>
+      <c r="AN64" s="154"/>
+      <c r="AO64" s="154"/>
+      <c r="AP64" s="154"/>
+      <c r="AQ64" s="154"/>
+      <c r="AR64" s="154"/>
+      <c r="AS64" s="154"/>
+      <c r="AT64" s="156"/>
+      <c r="AU64" s="156"/>
+      <c r="AV64" s="156"/>
+      <c r="AW64" s="156"/>
+      <c r="AX64" s="155"/>
+      <c r="AY64" s="154"/>
+      <c r="AZ64" s="154"/>
+      <c r="BA64" s="154"/>
+      <c r="BF64" s="154"/>
+      <c r="BG64" s="154"/>
+      <c r="BH64" s="154"/>
+      <c r="BI64" s="155"/>
+      <c r="BJ64" s="173"/>
+      <c r="BK64" s="173"/>
+      <c r="BL64" s="154"/>
+      <c r="BM64" s="155"/>
+      <c r="BN64" s="153"/>
+      <c r="BO64" s="155"/>
+      <c r="BP64" s="154"/>
+      <c r="BQ64" s="154"/>
+      <c r="BR64" s="153"/>
+    </row>
+    <row r="65" spans="1:70" ht="12">
+      <c r="A65" s="168"/>
+      <c r="B65" s="158"/>
+      <c r="C65" s="167"/>
+      <c r="D65" s="167"/>
+      <c r="E65" s="159"/>
+      <c r="F65" s="158"/>
+      <c r="G65" s="167"/>
+      <c r="H65" s="167"/>
+      <c r="I65" s="167"/>
+      <c r="L65" s="158"/>
+      <c r="M65" s="167"/>
+      <c r="N65" s="167"/>
+      <c r="O65" s="167"/>
+      <c r="P65" s="167"/>
+      <c r="Q65" s="159"/>
+      <c r="R65" s="158"/>
+      <c r="S65" s="167"/>
+      <c r="T65" s="167"/>
+      <c r="U65" s="167"/>
+      <c r="V65" s="167"/>
+      <c r="W65" s="159"/>
+      <c r="X65" s="158" t="s">
         <v>152</v>
       </c>
-      <c r="Y65" s="226"/>
-      <c r="Z65" s="236"/>
-      <c r="AA65" s="236"/>
-      <c r="AB65" s="236"/>
-      <c r="AC65" s="236"/>
-      <c r="AD65" s="226"/>
-      <c r="AE65" s="226"/>
-      <c r="AF65" s="226"/>
-      <c r="AG65" s="226"/>
-      <c r="AH65" s="226"/>
-      <c r="AI65" s="226"/>
-      <c r="AJ65" s="226"/>
-      <c r="AK65" s="232"/>
-      <c r="AL65" s="214"/>
-      <c r="AM65" s="232"/>
-      <c r="AN65" s="232"/>
-      <c r="AO65" s="232"/>
-      <c r="AP65" s="232"/>
-      <c r="AQ65" s="232"/>
-      <c r="AR65" s="232"/>
-      <c r="AS65" s="232"/>
-      <c r="AT65" s="226"/>
-      <c r="AU65" s="226"/>
-      <c r="AV65" s="226"/>
-      <c r="AW65" s="226"/>
-      <c r="AX65" s="214"/>
-      <c r="AY65" s="232"/>
-      <c r="AZ65" s="232"/>
-      <c r="BA65" s="232"/>
-      <c r="BF65" s="232"/>
-      <c r="BG65" s="232"/>
-      <c r="BH65" s="232"/>
-      <c r="BI65" s="214"/>
-      <c r="BJ65" s="232"/>
-      <c r="BK65" s="232"/>
-      <c r="BL65" s="232"/>
-      <c r="BM65" s="214"/>
-      <c r="BN65" s="232"/>
-      <c r="BO65" s="232"/>
-      <c r="BP65" s="212"/>
-      <c r="BQ65" s="214"/>
-      <c r="BR65" s="232"/>
-      <c r="BS65" s="232"/>
-      <c r="BT65" s="212"/>
-    </row>
-    <row r="66" spans="1:72" ht="12">
-      <c r="A66" s="228"/>
-      <c r="B66" s="210"/>
-      <c r="C66" s="208"/>
-      <c r="D66" s="208"/>
-      <c r="E66" s="211"/>
-      <c r="F66" s="210"/>
-      <c r="G66" s="208"/>
-      <c r="H66" s="208"/>
-      <c r="I66" s="208"/>
+      <c r="Y65" s="167"/>
+      <c r="Z65" s="177"/>
+      <c r="AA65" s="177"/>
+      <c r="AB65" s="177"/>
+      <c r="AC65" s="177"/>
+      <c r="AD65" s="167"/>
+      <c r="AE65" s="167"/>
+      <c r="AF65" s="167"/>
+      <c r="AG65" s="167"/>
+      <c r="AH65" s="167"/>
+      <c r="AI65" s="167"/>
+      <c r="AJ65" s="167"/>
+      <c r="AK65" s="173"/>
+      <c r="AL65" s="155"/>
+      <c r="AM65" s="173"/>
+      <c r="AN65" s="173"/>
+      <c r="AO65" s="173"/>
+      <c r="AP65" s="173"/>
+      <c r="AQ65" s="173"/>
+      <c r="AR65" s="173"/>
+      <c r="AS65" s="173"/>
+      <c r="AT65" s="167"/>
+      <c r="AU65" s="167"/>
+      <c r="AV65" s="167"/>
+      <c r="AW65" s="167"/>
+      <c r="AX65" s="155"/>
+      <c r="AY65" s="173"/>
+      <c r="AZ65" s="173"/>
+      <c r="BA65" s="173"/>
+      <c r="BF65" s="173"/>
+      <c r="BG65" s="173"/>
+      <c r="BH65" s="173"/>
+      <c r="BI65" s="155"/>
+      <c r="BJ65" s="173"/>
+      <c r="BK65" s="173"/>
+      <c r="BL65" s="173"/>
+      <c r="BM65" s="155"/>
+      <c r="BN65" s="153"/>
+      <c r="BO65" s="155"/>
+      <c r="BP65" s="173"/>
+      <c r="BQ65" s="173"/>
+      <c r="BR65" s="153"/>
+    </row>
+    <row r="66" spans="1:70" ht="12">
+      <c r="A66" s="169"/>
+      <c r="B66" s="151"/>
+      <c r="C66" s="149"/>
+      <c r="D66" s="149"/>
+      <c r="E66" s="152"/>
+      <c r="F66" s="151"/>
+      <c r="G66" s="149"/>
+      <c r="H66" s="149"/>
+      <c r="I66" s="149"/>
       <c r="J66" s="24"/>
       <c r="K66" s="25"/>
-      <c r="L66" s="210"/>
-      <c r="M66" s="208"/>
-      <c r="N66" s="208"/>
-      <c r="O66" s="208"/>
-      <c r="P66" s="208"/>
-      <c r="Q66" s="211"/>
-      <c r="R66" s="210"/>
-      <c r="S66" s="208"/>
-      <c r="T66" s="208"/>
-      <c r="U66" s="208"/>
-      <c r="V66" s="208"/>
-      <c r="W66" s="208"/>
-      <c r="X66" s="210" t="s">
+      <c r="L66" s="151"/>
+      <c r="M66" s="149"/>
+      <c r="N66" s="149"/>
+      <c r="O66" s="149"/>
+      <c r="P66" s="149"/>
+      <c r="Q66" s="152"/>
+      <c r="R66" s="151"/>
+      <c r="S66" s="149"/>
+      <c r="T66" s="149"/>
+      <c r="U66" s="149"/>
+      <c r="V66" s="149"/>
+      <c r="W66" s="149"/>
+      <c r="X66" s="151" t="s">
         <v>153</v>
       </c>
-      <c r="Y66" s="208"/>
-      <c r="Z66" s="209"/>
-      <c r="AA66" s="209"/>
-      <c r="AB66" s="209"/>
-      <c r="AC66" s="209"/>
-      <c r="AD66" s="208"/>
-      <c r="AE66" s="208"/>
-      <c r="AF66" s="208"/>
-      <c r="AG66" s="208"/>
-      <c r="AH66" s="208"/>
-      <c r="AI66" s="208"/>
-      <c r="AJ66" s="208"/>
-      <c r="AK66" s="206"/>
-      <c r="AL66" s="207"/>
-      <c r="AM66" s="206"/>
-      <c r="AN66" s="206"/>
-      <c r="AO66" s="206"/>
-      <c r="AP66" s="206"/>
-      <c r="AQ66" s="206"/>
-      <c r="AR66" s="206"/>
-      <c r="AS66" s="206"/>
-      <c r="AT66" s="208"/>
-      <c r="AU66" s="208"/>
-      <c r="AV66" s="208"/>
-      <c r="AW66" s="208"/>
-      <c r="AX66" s="207"/>
-      <c r="AY66" s="206"/>
-      <c r="AZ66" s="206"/>
-      <c r="BA66" s="206"/>
+      <c r="Y66" s="149"/>
+      <c r="Z66" s="150"/>
+      <c r="AA66" s="150"/>
+      <c r="AB66" s="150"/>
+      <c r="AC66" s="150"/>
+      <c r="AD66" s="149"/>
+      <c r="AE66" s="149"/>
+      <c r="AF66" s="149"/>
+      <c r="AG66" s="149"/>
+      <c r="AH66" s="149"/>
+      <c r="AI66" s="149"/>
+      <c r="AJ66" s="149"/>
+      <c r="AK66" s="147"/>
+      <c r="AL66" s="148"/>
+      <c r="AM66" s="147"/>
+      <c r="AN66" s="147"/>
+      <c r="AO66" s="147"/>
+      <c r="AP66" s="147"/>
+      <c r="AQ66" s="147"/>
+      <c r="AR66" s="147"/>
+      <c r="AS66" s="147"/>
+      <c r="AT66" s="149"/>
+      <c r="AU66" s="149"/>
+      <c r="AV66" s="149"/>
+      <c r="AW66" s="149"/>
+      <c r="AX66" s="148"/>
+      <c r="AY66" s="147"/>
+      <c r="AZ66" s="147"/>
+      <c r="BA66" s="147"/>
       <c r="BB66" s="23"/>
       <c r="BC66" s="23"/>
       <c r="BD66" s="21"/>
       <c r="BE66" s="21"/>
-      <c r="BF66" s="206"/>
-      <c r="BG66" s="206"/>
-      <c r="BH66" s="206"/>
-      <c r="BI66" s="207"/>
-      <c r="BJ66" s="206"/>
-      <c r="BK66" s="206"/>
-      <c r="BL66" s="206"/>
-      <c r="BM66" s="207"/>
-      <c r="BN66" s="206"/>
-      <c r="BO66" s="206"/>
-      <c r="BP66" s="205"/>
-      <c r="BQ66" s="207"/>
-      <c r="BR66" s="206"/>
-      <c r="BS66" s="206"/>
-      <c r="BT66" s="205"/>
-    </row>
-    <row r="67" spans="1:72" ht="12">
-      <c r="A67" s="227" t="s">
+      <c r="BF66" s="147"/>
+      <c r="BG66" s="147"/>
+      <c r="BH66" s="147"/>
+      <c r="BI66" s="148"/>
+      <c r="BJ66" s="147"/>
+      <c r="BK66" s="147"/>
+      <c r="BL66" s="147"/>
+      <c r="BM66" s="148"/>
+      <c r="BN66" s="146"/>
+      <c r="BO66" s="148"/>
+      <c r="BP66" s="147"/>
+      <c r="BQ66" s="147"/>
+      <c r="BR66" s="146"/>
+    </row>
+    <row r="67" spans="1:70" ht="12">
+      <c r="A67" s="168" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="217" t="s">
+      <c r="B67" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C67" s="215"/>
-      <c r="D67" s="215"/>
-      <c r="E67" s="218"/>
-      <c r="F67" s="217" t="s">
+      <c r="C67" s="156"/>
+      <c r="D67" s="156"/>
+      <c r="E67" s="159"/>
+      <c r="F67" s="158" t="s">
         <v>119</v>
       </c>
-      <c r="G67" s="215"/>
-      <c r="H67" s="215"/>
-      <c r="I67" s="215"/>
-      <c r="L67" s="217" t="s">
+      <c r="G67" s="156"/>
+      <c r="H67" s="156"/>
+      <c r="I67" s="156"/>
+      <c r="L67" s="158" t="s">
         <v>155</v>
       </c>
-      <c r="M67" s="215"/>
-      <c r="N67" s="215"/>
-      <c r="O67" s="215"/>
-      <c r="P67" s="215"/>
-      <c r="Q67" s="218"/>
-      <c r="R67" s="217" t="s">
+      <c r="M67" s="156"/>
+      <c r="N67" s="156"/>
+      <c r="O67" s="156"/>
+      <c r="P67" s="156"/>
+      <c r="Q67" s="159"/>
+      <c r="R67" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="S67" s="215"/>
-      <c r="T67" s="215"/>
-      <c r="U67" s="215"/>
-      <c r="V67" s="215"/>
-      <c r="W67" s="215"/>
-      <c r="X67" s="217" t="s">
+      <c r="S67" s="156"/>
+      <c r="T67" s="156"/>
+      <c r="U67" s="156"/>
+      <c r="V67" s="156"/>
+      <c r="W67" s="156"/>
+      <c r="X67" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="Y67" s="215"/>
-      <c r="Z67" s="216"/>
-      <c r="AA67" s="216"/>
-      <c r="AB67" s="216"/>
-      <c r="AC67" s="216"/>
-      <c r="AD67" s="215"/>
-      <c r="AE67" s="215"/>
-      <c r="AF67" s="215"/>
-      <c r="AG67" s="215"/>
-      <c r="AH67" s="215"/>
-      <c r="AI67" s="215"/>
-      <c r="AJ67" s="215"/>
-      <c r="AK67" s="213"/>
-      <c r="AL67" s="221" t="s">
+      <c r="Y67" s="156"/>
+      <c r="Z67" s="157"/>
+      <c r="AA67" s="157"/>
+      <c r="AB67" s="157"/>
+      <c r="AC67" s="157"/>
+      <c r="AD67" s="156"/>
+      <c r="AE67" s="156"/>
+      <c r="AF67" s="156"/>
+      <c r="AG67" s="156"/>
+      <c r="AH67" s="156"/>
+      <c r="AI67" s="156"/>
+      <c r="AJ67" s="156"/>
+      <c r="AK67" s="154"/>
+      <c r="AL67" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="AM67" s="213"/>
-      <c r="AN67" s="213"/>
-      <c r="AO67" s="213"/>
-      <c r="AP67" s="213"/>
-      <c r="AQ67" s="213"/>
-      <c r="AR67" s="213"/>
-      <c r="AS67" s="213"/>
-      <c r="AT67" s="215"/>
-      <c r="AU67" s="215"/>
-      <c r="AV67" s="215"/>
-      <c r="AW67" s="215"/>
-      <c r="AX67" s="221" t="s">
+      <c r="AM67" s="154"/>
+      <c r="AN67" s="154"/>
+      <c r="AO67" s="154"/>
+      <c r="AP67" s="154"/>
+      <c r="AQ67" s="154"/>
+      <c r="AR67" s="154"/>
+      <c r="AS67" s="154"/>
+      <c r="AT67" s="156"/>
+      <c r="AU67" s="156"/>
+      <c r="AV67" s="156"/>
+      <c r="AW67" s="156"/>
+      <c r="AX67" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="AY67" s="213"/>
-      <c r="AZ67" s="213"/>
-      <c r="BA67" s="213"/>
-      <c r="BF67" s="213"/>
-      <c r="BG67" s="213"/>
-      <c r="BH67" s="213"/>
-      <c r="BI67" s="214"/>
-      <c r="BJ67" s="213"/>
-      <c r="BK67" s="213"/>
-      <c r="BL67" s="213"/>
-      <c r="BM67" s="214"/>
-      <c r="BN67" s="213"/>
-      <c r="BO67" s="213"/>
-      <c r="BP67" s="212"/>
-      <c r="BQ67" s="214"/>
-      <c r="BR67" s="213"/>
-      <c r="BS67" s="213"/>
-      <c r="BT67" s="212"/>
-    </row>
-    <row r="68" spans="1:72" ht="12">
-      <c r="A68" s="227"/>
-      <c r="B68" s="217"/>
-      <c r="C68" s="215"/>
-      <c r="D68" s="215"/>
-      <c r="E68" s="218"/>
-      <c r="F68" s="217"/>
-      <c r="G68" s="215"/>
-      <c r="H68" s="215"/>
-      <c r="I68" s="215"/>
-      <c r="L68" s="217"/>
-      <c r="M68" s="215"/>
-      <c r="N68" s="215"/>
-      <c r="O68" s="215"/>
-      <c r="P68" s="215"/>
-      <c r="Q68" s="218"/>
-      <c r="R68" s="217"/>
-      <c r="S68" s="215"/>
-      <c r="T68" s="215"/>
-      <c r="U68" s="215"/>
-      <c r="V68" s="215"/>
-      <c r="W68" s="215"/>
-      <c r="X68" s="217" t="s">
+      <c r="AY67" s="154"/>
+      <c r="AZ67" s="154"/>
+      <c r="BA67" s="154"/>
+      <c r="BF67" s="154"/>
+      <c r="BG67" s="154"/>
+      <c r="BH67" s="154"/>
+      <c r="BI67" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ67" s="239"/>
+      <c r="BK67" s="239"/>
+      <c r="BL67" s="154"/>
+      <c r="BM67" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN67" s="153"/>
+      <c r="BO67" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP67" s="154"/>
+      <c r="BQ67" s="154"/>
+      <c r="BR67" s="153"/>
+    </row>
+    <row r="68" spans="1:70" ht="12">
+      <c r="A68" s="168"/>
+      <c r="B68" s="158"/>
+      <c r="C68" s="156"/>
+      <c r="D68" s="156"/>
+      <c r="E68" s="159"/>
+      <c r="F68" s="158"/>
+      <c r="G68" s="156"/>
+      <c r="H68" s="156"/>
+      <c r="I68" s="156"/>
+      <c r="L68" s="158"/>
+      <c r="M68" s="156"/>
+      <c r="N68" s="156"/>
+      <c r="O68" s="156"/>
+      <c r="P68" s="156"/>
+      <c r="Q68" s="159"/>
+      <c r="R68" s="158"/>
+      <c r="S68" s="156"/>
+      <c r="T68" s="156"/>
+      <c r="U68" s="156"/>
+      <c r="V68" s="156"/>
+      <c r="W68" s="156"/>
+      <c r="X68" s="158" t="s">
         <v>156</v>
       </c>
-      <c r="Y68" s="215"/>
-      <c r="Z68" s="216"/>
-      <c r="AA68" s="216"/>
-      <c r="AB68" s="216"/>
-      <c r="AC68" s="216"/>
-      <c r="AD68" s="215"/>
-      <c r="AE68" s="215"/>
-      <c r="AF68" s="215"/>
-      <c r="AG68" s="215"/>
-      <c r="AH68" s="215"/>
-      <c r="AI68" s="215"/>
-      <c r="AJ68" s="215"/>
-      <c r="AK68" s="213"/>
-      <c r="AL68" s="214" t="s">
+      <c r="Y68" s="156"/>
+      <c r="Z68" s="157"/>
+      <c r="AA68" s="157"/>
+      <c r="AB68" s="157"/>
+      <c r="AC68" s="157"/>
+      <c r="AD68" s="156"/>
+      <c r="AE68" s="156"/>
+      <c r="AF68" s="156"/>
+      <c r="AG68" s="156"/>
+      <c r="AH68" s="156"/>
+      <c r="AI68" s="156"/>
+      <c r="AJ68" s="156"/>
+      <c r="AK68" s="154"/>
+      <c r="AL68" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="AM68" s="213"/>
-      <c r="AN68" s="213"/>
-      <c r="AO68" s="213"/>
-      <c r="AP68" s="213"/>
-      <c r="AQ68" s="213"/>
-      <c r="AR68" s="213"/>
-      <c r="AS68" s="213"/>
-      <c r="AT68" s="215"/>
-      <c r="AU68" s="215"/>
-      <c r="AV68" s="215"/>
-      <c r="AW68" s="215"/>
-      <c r="AX68" s="214"/>
-      <c r="AY68" s="213"/>
-      <c r="AZ68" s="213"/>
-      <c r="BA68" s="213"/>
-      <c r="BF68" s="213"/>
-      <c r="BG68" s="213"/>
-      <c r="BH68" s="213"/>
-      <c r="BI68" s="214"/>
-      <c r="BJ68" s="213"/>
-      <c r="BK68" s="213"/>
-      <c r="BL68" s="213"/>
-      <c r="BM68" s="214"/>
-      <c r="BN68" s="213"/>
-      <c r="BO68" s="213"/>
-      <c r="BP68" s="212"/>
-      <c r="BQ68" s="214"/>
-      <c r="BR68" s="213"/>
-      <c r="BS68" s="213"/>
-      <c r="BT68" s="212"/>
-    </row>
-    <row r="69" spans="1:72" ht="12">
-      <c r="A69" s="227"/>
-      <c r="B69" s="217"/>
-      <c r="C69" s="215"/>
-      <c r="D69" s="215"/>
-      <c r="E69" s="218"/>
-      <c r="F69" s="217"/>
-      <c r="G69" s="215"/>
-      <c r="H69" s="215"/>
-      <c r="I69" s="215"/>
-      <c r="L69" s="217"/>
-      <c r="M69" s="215"/>
-      <c r="N69" s="215"/>
-      <c r="O69" s="215"/>
-      <c r="P69" s="215"/>
-      <c r="Q69" s="218"/>
-      <c r="R69" s="217"/>
-      <c r="S69" s="215"/>
-      <c r="T69" s="215"/>
-      <c r="U69" s="215"/>
-      <c r="V69" s="215"/>
-      <c r="W69" s="215"/>
-      <c r="X69" s="217" t="s">
+      <c r="AM68" s="154"/>
+      <c r="AN68" s="154"/>
+      <c r="AO68" s="154"/>
+      <c r="AP68" s="154"/>
+      <c r="AQ68" s="154"/>
+      <c r="AR68" s="154"/>
+      <c r="AS68" s="154"/>
+      <c r="AT68" s="156"/>
+      <c r="AU68" s="156"/>
+      <c r="AV68" s="156"/>
+      <c r="AW68" s="156"/>
+      <c r="AX68" s="155"/>
+      <c r="AY68" s="154"/>
+      <c r="AZ68" s="154"/>
+      <c r="BA68" s="154"/>
+      <c r="BF68" s="154"/>
+      <c r="BG68" s="154"/>
+      <c r="BH68" s="154"/>
+      <c r="BI68" s="155"/>
+      <c r="BJ68" s="173"/>
+      <c r="BK68" s="173"/>
+      <c r="BL68" s="154"/>
+      <c r="BM68" s="155"/>
+      <c r="BN68" s="153"/>
+      <c r="BO68" s="155"/>
+      <c r="BP68" s="154"/>
+      <c r="BQ68" s="154"/>
+      <c r="BR68" s="153"/>
+    </row>
+    <row r="69" spans="1:70" ht="12">
+      <c r="A69" s="168"/>
+      <c r="B69" s="158"/>
+      <c r="C69" s="156"/>
+      <c r="D69" s="156"/>
+      <c r="E69" s="159"/>
+      <c r="F69" s="158"/>
+      <c r="G69" s="156"/>
+      <c r="H69" s="156"/>
+      <c r="I69" s="156"/>
+      <c r="L69" s="158"/>
+      <c r="M69" s="156"/>
+      <c r="N69" s="156"/>
+      <c r="O69" s="156"/>
+      <c r="P69" s="156"/>
+      <c r="Q69" s="159"/>
+      <c r="R69" s="158"/>
+      <c r="S69" s="156"/>
+      <c r="T69" s="156"/>
+      <c r="U69" s="156"/>
+      <c r="V69" s="156"/>
+      <c r="W69" s="156"/>
+      <c r="X69" s="158" t="s">
         <v>157</v>
       </c>
-      <c r="Y69" s="215"/>
-      <c r="Z69" s="216"/>
-      <c r="AA69" s="216"/>
-      <c r="AB69" s="216"/>
-      <c r="AC69" s="216"/>
-      <c r="AD69" s="215"/>
-      <c r="AE69" s="215"/>
-      <c r="AF69" s="215"/>
-      <c r="AG69" s="215"/>
-      <c r="AH69" s="215"/>
-      <c r="AI69" s="215"/>
-      <c r="AJ69" s="215"/>
-      <c r="AK69" s="213"/>
-      <c r="AL69" s="214"/>
-      <c r="AM69" s="213"/>
-      <c r="AN69" s="213"/>
-      <c r="AO69" s="213"/>
-      <c r="AP69" s="213"/>
-      <c r="AQ69" s="213"/>
-      <c r="AR69" s="213"/>
-      <c r="AS69" s="213"/>
-      <c r="AT69" s="215"/>
-      <c r="AU69" s="215"/>
-      <c r="AV69" s="215"/>
-      <c r="AW69" s="215"/>
-      <c r="AX69" s="214"/>
-      <c r="AY69" s="213"/>
-      <c r="AZ69" s="213"/>
-      <c r="BA69" s="213"/>
-      <c r="BF69" s="213"/>
-      <c r="BG69" s="213"/>
-      <c r="BH69" s="213"/>
-      <c r="BI69" s="214"/>
-      <c r="BJ69" s="213"/>
-      <c r="BK69" s="213"/>
-      <c r="BL69" s="213"/>
-      <c r="BM69" s="214"/>
-      <c r="BN69" s="213"/>
-      <c r="BO69" s="213"/>
-      <c r="BP69" s="212"/>
-      <c r="BQ69" s="214"/>
-      <c r="BR69" s="213"/>
-      <c r="BS69" s="213"/>
-      <c r="BT69" s="212"/>
-    </row>
-    <row r="70" spans="1:72" ht="12">
-      <c r="A70" s="228"/>
-      <c r="B70" s="210"/>
-      <c r="C70" s="208"/>
-      <c r="D70" s="208"/>
-      <c r="E70" s="211"/>
-      <c r="F70" s="210"/>
-      <c r="G70" s="208"/>
-      <c r="H70" s="208"/>
-      <c r="I70" s="208"/>
+      <c r="Y69" s="156"/>
+      <c r="Z69" s="157"/>
+      <c r="AA69" s="157"/>
+      <c r="AB69" s="157"/>
+      <c r="AC69" s="157"/>
+      <c r="AD69" s="156"/>
+      <c r="AE69" s="156"/>
+      <c r="AF69" s="156"/>
+      <c r="AG69" s="156"/>
+      <c r="AH69" s="156"/>
+      <c r="AI69" s="156"/>
+      <c r="AJ69" s="156"/>
+      <c r="AK69" s="154"/>
+      <c r="AL69" s="155"/>
+      <c r="AM69" s="154"/>
+      <c r="AN69" s="154"/>
+      <c r="AO69" s="154"/>
+      <c r="AP69" s="154"/>
+      <c r="AQ69" s="154"/>
+      <c r="AR69" s="154"/>
+      <c r="AS69" s="154"/>
+      <c r="AT69" s="156"/>
+      <c r="AU69" s="156"/>
+      <c r="AV69" s="156"/>
+      <c r="AW69" s="156"/>
+      <c r="AX69" s="155"/>
+      <c r="AY69" s="154"/>
+      <c r="AZ69" s="154"/>
+      <c r="BA69" s="154"/>
+      <c r="BF69" s="154"/>
+      <c r="BG69" s="154"/>
+      <c r="BH69" s="154"/>
+      <c r="BI69" s="155"/>
+      <c r="BJ69" s="173"/>
+      <c r="BK69" s="173"/>
+      <c r="BL69" s="154"/>
+      <c r="BM69" s="155"/>
+      <c r="BN69" s="153"/>
+      <c r="BO69" s="155"/>
+      <c r="BP69" s="154"/>
+      <c r="BQ69" s="154"/>
+      <c r="BR69" s="153"/>
+    </row>
+    <row r="70" spans="1:70" ht="12">
+      <c r="A70" s="169"/>
+      <c r="B70" s="151"/>
+      <c r="C70" s="149"/>
+      <c r="D70" s="149"/>
+      <c r="E70" s="152"/>
+      <c r="F70" s="151"/>
+      <c r="G70" s="149"/>
+      <c r="H70" s="149"/>
+      <c r="I70" s="149"/>
       <c r="J70" s="24"/>
       <c r="K70" s="25"/>
-      <c r="L70" s="210"/>
-      <c r="M70" s="208"/>
-      <c r="N70" s="208"/>
-      <c r="O70" s="208"/>
-      <c r="P70" s="208"/>
-      <c r="Q70" s="211"/>
-      <c r="R70" s="210"/>
-      <c r="S70" s="208"/>
-      <c r="T70" s="208"/>
-      <c r="U70" s="208"/>
-      <c r="V70" s="208"/>
-      <c r="W70" s="208"/>
-      <c r="X70" s="210" t="s">
+      <c r="L70" s="151"/>
+      <c r="M70" s="149"/>
+      <c r="N70" s="149"/>
+      <c r="O70" s="149"/>
+      <c r="P70" s="149"/>
+      <c r="Q70" s="152"/>
+      <c r="R70" s="151"/>
+      <c r="S70" s="149"/>
+      <c r="T70" s="149"/>
+      <c r="U70" s="149"/>
+      <c r="V70" s="149"/>
+      <c r="W70" s="149"/>
+      <c r="X70" s="151" t="s">
         <v>153</v>
       </c>
-      <c r="Y70" s="208"/>
-      <c r="Z70" s="209"/>
-      <c r="AA70" s="209"/>
-      <c r="AB70" s="209"/>
-      <c r="AC70" s="209"/>
-      <c r="AD70" s="208"/>
-      <c r="AE70" s="208"/>
-      <c r="AF70" s="208"/>
-      <c r="AG70" s="208"/>
-      <c r="AH70" s="208"/>
-      <c r="AI70" s="208"/>
-      <c r="AJ70" s="208"/>
-      <c r="AK70" s="206"/>
-      <c r="AL70" s="207"/>
-      <c r="AM70" s="206"/>
-      <c r="AN70" s="206"/>
-      <c r="AO70" s="206"/>
-      <c r="AP70" s="206"/>
-      <c r="AQ70" s="206"/>
-      <c r="AR70" s="206"/>
-      <c r="AS70" s="206"/>
-      <c r="AT70" s="208"/>
-      <c r="AU70" s="208"/>
-      <c r="AV70" s="208"/>
-      <c r="AW70" s="208"/>
-      <c r="AX70" s="207"/>
-      <c r="AY70" s="206"/>
-      <c r="AZ70" s="206"/>
-      <c r="BA70" s="206"/>
+      <c r="Y70" s="149"/>
+      <c r="Z70" s="150"/>
+      <c r="AA70" s="150"/>
+      <c r="AB70" s="150"/>
+      <c r="AC70" s="150"/>
+      <c r="AD70" s="149"/>
+      <c r="AE70" s="149"/>
+      <c r="AF70" s="149"/>
+      <c r="AG70" s="149"/>
+      <c r="AH70" s="149"/>
+      <c r="AI70" s="149"/>
+      <c r="AJ70" s="149"/>
+      <c r="AK70" s="147"/>
+      <c r="AL70" s="148"/>
+      <c r="AM70" s="147"/>
+      <c r="AN70" s="147"/>
+      <c r="AO70" s="147"/>
+      <c r="AP70" s="147"/>
+      <c r="AQ70" s="147"/>
+      <c r="AR70" s="147"/>
+      <c r="AS70" s="147"/>
+      <c r="AT70" s="149"/>
+      <c r="AU70" s="149"/>
+      <c r="AV70" s="149"/>
+      <c r="AW70" s="149"/>
+      <c r="AX70" s="148"/>
+      <c r="AY70" s="147"/>
+      <c r="AZ70" s="147"/>
+      <c r="BA70" s="147"/>
       <c r="BB70" s="23"/>
       <c r="BC70" s="23"/>
       <c r="BD70" s="21"/>
       <c r="BE70" s="21"/>
-      <c r="BF70" s="206"/>
-      <c r="BG70" s="206"/>
-      <c r="BH70" s="206"/>
-      <c r="BI70" s="207"/>
-      <c r="BJ70" s="206"/>
-      <c r="BK70" s="206"/>
-      <c r="BL70" s="206"/>
-      <c r="BM70" s="207"/>
-      <c r="BN70" s="206"/>
-      <c r="BO70" s="206"/>
-      <c r="BP70" s="205"/>
-      <c r="BQ70" s="207"/>
-      <c r="BR70" s="206"/>
-      <c r="BS70" s="206"/>
-      <c r="BT70" s="205"/>
-    </row>
-    <row r="71" spans="1:72" ht="12">
-      <c r="A71" s="227" t="s">
+      <c r="BF70" s="147"/>
+      <c r="BG70" s="147"/>
+      <c r="BH70" s="147"/>
+      <c r="BI70" s="148"/>
+      <c r="BJ70" s="147"/>
+      <c r="BK70" s="147"/>
+      <c r="BL70" s="147"/>
+      <c r="BM70" s="148"/>
+      <c r="BN70" s="146"/>
+      <c r="BO70" s="148"/>
+      <c r="BP70" s="147"/>
+      <c r="BQ70" s="147"/>
+      <c r="BR70" s="146"/>
+    </row>
+    <row r="71" spans="1:70" ht="12">
+      <c r="A71" s="168" t="s">
         <v>158</v>
       </c>
-      <c r="B71" s="217" t="s">
+      <c r="B71" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="C71" s="215"/>
-      <c r="D71" s="215"/>
-      <c r="E71" s="218"/>
-      <c r="F71" s="217" t="s">
+      <c r="C71" s="156"/>
+      <c r="D71" s="156"/>
+      <c r="E71" s="159"/>
+      <c r="F71" s="158" t="s">
         <v>159</v>
       </c>
-      <c r="G71" s="215"/>
-      <c r="H71" s="215"/>
-      <c r="I71" s="215"/>
-      <c r="L71" s="217" t="s">
+      <c r="G71" s="156"/>
+      <c r="H71" s="156"/>
+      <c r="I71" s="156"/>
+      <c r="L71" s="158" t="s">
         <v>160</v>
       </c>
-      <c r="M71" s="215"/>
-      <c r="N71" s="215"/>
-      <c r="O71" s="215"/>
-      <c r="P71" s="215"/>
-      <c r="Q71" s="218"/>
-      <c r="R71" s="217" t="s">
+      <c r="M71" s="156"/>
+      <c r="N71" s="156"/>
+      <c r="O71" s="156"/>
+      <c r="P71" s="156"/>
+      <c r="Q71" s="159"/>
+      <c r="R71" s="158" t="s">
         <v>99</v>
       </c>
-      <c r="S71" s="215"/>
-      <c r="T71" s="215"/>
-      <c r="U71" s="215"/>
-      <c r="V71" s="215"/>
-      <c r="W71" s="215"/>
-      <c r="X71" s="217" t="s">
+      <c r="S71" s="156"/>
+      <c r="T71" s="156"/>
+      <c r="U71" s="156"/>
+      <c r="V71" s="156"/>
+      <c r="W71" s="156"/>
+      <c r="X71" s="158" t="s">
         <v>84</v>
       </c>
-      <c r="Y71" s="215"/>
-      <c r="Z71" s="216"/>
-      <c r="AA71" s="216"/>
-      <c r="AB71" s="216"/>
-      <c r="AC71" s="216"/>
-      <c r="AD71" s="215"/>
-      <c r="AE71" s="215"/>
-      <c r="AF71" s="215"/>
-      <c r="AG71" s="215"/>
-      <c r="AH71" s="215"/>
-      <c r="AI71" s="215"/>
-      <c r="AJ71" s="215"/>
-      <c r="AK71" s="213"/>
-      <c r="AL71" s="214" t="s">
+      <c r="Y71" s="156"/>
+      <c r="Z71" s="157"/>
+      <c r="AA71" s="157"/>
+      <c r="AB71" s="157"/>
+      <c r="AC71" s="157"/>
+      <c r="AD71" s="156"/>
+      <c r="AE71" s="156"/>
+      <c r="AF71" s="156"/>
+      <c r="AG71" s="156"/>
+      <c r="AH71" s="156"/>
+      <c r="AI71" s="156"/>
+      <c r="AJ71" s="156"/>
+      <c r="AK71" s="154"/>
+      <c r="AL71" s="155" t="s">
         <v>99</v>
       </c>
-      <c r="AM71" s="213"/>
-      <c r="AN71" s="213"/>
-      <c r="AO71" s="213"/>
-      <c r="AP71" s="213"/>
-      <c r="AQ71" s="213"/>
-      <c r="AR71" s="213"/>
-      <c r="AS71" s="213"/>
-      <c r="AT71" s="215"/>
-      <c r="AU71" s="215"/>
-      <c r="AV71" s="215"/>
-      <c r="AW71" s="215"/>
-      <c r="AX71" s="214" t="s">
+      <c r="AM71" s="154"/>
+      <c r="AN71" s="154"/>
+      <c r="AO71" s="154"/>
+      <c r="AP71" s="154"/>
+      <c r="AQ71" s="154"/>
+      <c r="AR71" s="154"/>
+      <c r="AS71" s="154"/>
+      <c r="AT71" s="156"/>
+      <c r="AU71" s="156"/>
+      <c r="AV71" s="156"/>
+      <c r="AW71" s="156"/>
+      <c r="AX71" s="155" t="s">
         <v>99</v>
       </c>
-      <c r="AY71" s="213"/>
-      <c r="AZ71" s="213"/>
-      <c r="BA71" s="213"/>
-      <c r="BF71" s="213"/>
-      <c r="BG71" s="213"/>
-      <c r="BH71" s="213"/>
-      <c r="BI71" s="214"/>
-      <c r="BJ71" s="213"/>
-      <c r="BK71" s="213"/>
-      <c r="BL71" s="213"/>
-      <c r="BM71" s="214"/>
-      <c r="BN71" s="213"/>
-      <c r="BO71" s="213"/>
-      <c r="BP71" s="212"/>
-      <c r="BQ71" s="214"/>
-      <c r="BR71" s="213"/>
-      <c r="BS71" s="213"/>
-      <c r="BT71" s="212"/>
-    </row>
-    <row r="72" spans="1:72" ht="12">
-      <c r="A72" s="228"/>
-      <c r="B72" s="210"/>
-      <c r="C72" s="208"/>
-      <c r="D72" s="208"/>
-      <c r="E72" s="211"/>
-      <c r="F72" s="210"/>
-      <c r="G72" s="208"/>
-      <c r="H72" s="208"/>
-      <c r="I72" s="208"/>
+      <c r="AY71" s="154"/>
+      <c r="AZ71" s="154"/>
+      <c r="BA71" s="154"/>
+      <c r="BF71" s="154"/>
+      <c r="BG71" s="154"/>
+      <c r="BH71" s="154"/>
+      <c r="BI71" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ71" s="239"/>
+      <c r="BK71" s="239"/>
+      <c r="BL71" s="154"/>
+      <c r="BM71" s="237">
+        <v>45594</v>
+      </c>
+      <c r="BN71" s="153"/>
+      <c r="BO71" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP71" s="154"/>
+      <c r="BQ71" s="154"/>
+      <c r="BR71" s="153"/>
+    </row>
+    <row r="72" spans="1:70" ht="12">
+      <c r="A72" s="169"/>
+      <c r="B72" s="151"/>
+      <c r="C72" s="149"/>
+      <c r="D72" s="149"/>
+      <c r="E72" s="152"/>
+      <c r="F72" s="151"/>
+      <c r="G72" s="149"/>
+      <c r="H72" s="149"/>
+      <c r="I72" s="149"/>
       <c r="J72" s="24"/>
       <c r="K72" s="25"/>
-      <c r="L72" s="210"/>
-      <c r="M72" s="208"/>
-      <c r="N72" s="208"/>
-      <c r="O72" s="208"/>
-      <c r="P72" s="208"/>
-      <c r="Q72" s="211"/>
-      <c r="R72" s="210"/>
-      <c r="S72" s="208"/>
-      <c r="T72" s="208"/>
-      <c r="U72" s="208"/>
-      <c r="V72" s="208"/>
-      <c r="W72" s="208"/>
-      <c r="X72" s="210" t="s">
+      <c r="L72" s="151"/>
+      <c r="M72" s="149"/>
+      <c r="N72" s="149"/>
+      <c r="O72" s="149"/>
+      <c r="P72" s="149"/>
+      <c r="Q72" s="152"/>
+      <c r="R72" s="151"/>
+      <c r="S72" s="149"/>
+      <c r="T72" s="149"/>
+      <c r="U72" s="149"/>
+      <c r="V72" s="149"/>
+      <c r="W72" s="149"/>
+      <c r="X72" s="151" t="s">
         <v>85</v>
       </c>
-      <c r="Y72" s="208"/>
-      <c r="Z72" s="209"/>
-      <c r="AA72" s="209"/>
-      <c r="AB72" s="209"/>
-      <c r="AC72" s="209"/>
-      <c r="AD72" s="208"/>
-      <c r="AE72" s="208"/>
-      <c r="AF72" s="208"/>
-      <c r="AG72" s="208"/>
-      <c r="AH72" s="208"/>
-      <c r="AI72" s="208"/>
-      <c r="AJ72" s="208"/>
-      <c r="AK72" s="206"/>
-      <c r="AL72" s="207"/>
-      <c r="AM72" s="206"/>
-      <c r="AN72" s="206"/>
-      <c r="AO72" s="206"/>
-      <c r="AP72" s="206"/>
-      <c r="AQ72" s="206"/>
-      <c r="AR72" s="206"/>
-      <c r="AS72" s="206"/>
-      <c r="AT72" s="208"/>
-      <c r="AU72" s="208"/>
-      <c r="AV72" s="208"/>
-      <c r="AW72" s="208"/>
-      <c r="AX72" s="207"/>
-      <c r="AY72" s="206"/>
-      <c r="AZ72" s="206"/>
-      <c r="BA72" s="206"/>
+      <c r="Y72" s="149"/>
+      <c r="Z72" s="150"/>
+      <c r="AA72" s="150"/>
+      <c r="AB72" s="150"/>
+      <c r="AC72" s="150"/>
+      <c r="AD72" s="149"/>
+      <c r="AE72" s="149"/>
+      <c r="AF72" s="149"/>
+      <c r="AG72" s="149"/>
+      <c r="AH72" s="149"/>
+      <c r="AI72" s="149"/>
+      <c r="AJ72" s="149"/>
+      <c r="AK72" s="147"/>
+      <c r="AL72" s="148"/>
+      <c r="AM72" s="147"/>
+      <c r="AN72" s="147"/>
+      <c r="AO72" s="147"/>
+      <c r="AP72" s="147"/>
+      <c r="AQ72" s="147"/>
+      <c r="AR72" s="147"/>
+      <c r="AS72" s="147"/>
+      <c r="AT72" s="149"/>
+      <c r="AU72" s="149"/>
+      <c r="AV72" s="149"/>
+      <c r="AW72" s="149"/>
+      <c r="AX72" s="148"/>
+      <c r="AY72" s="147"/>
+      <c r="AZ72" s="147"/>
+      <c r="BA72" s="147"/>
       <c r="BB72" s="23"/>
       <c r="BC72" s="23"/>
       <c r="BD72" s="21"/>
       <c r="BE72" s="21"/>
-      <c r="BF72" s="206"/>
-      <c r="BG72" s="206"/>
-      <c r="BH72" s="206"/>
-      <c r="BI72" s="207"/>
-      <c r="BJ72" s="206"/>
-      <c r="BK72" s="206"/>
-      <c r="BL72" s="206"/>
-      <c r="BM72" s="207"/>
-      <c r="BN72" s="206"/>
-      <c r="BO72" s="206"/>
-      <c r="BP72" s="205"/>
-      <c r="BQ72" s="207"/>
-      <c r="BR72" s="206"/>
-      <c r="BS72" s="206"/>
-      <c r="BT72" s="205"/>
+      <c r="BF72" s="147"/>
+      <c r="BG72" s="147"/>
+      <c r="BH72" s="147"/>
+      <c r="BI72" s="148"/>
+      <c r="BJ72" s="147"/>
+      <c r="BK72" s="147"/>
+      <c r="BL72" s="147"/>
+      <c r="BM72" s="148"/>
+      <c r="BN72" s="146"/>
+      <c r="BO72" s="148"/>
+      <c r="BP72" s="147"/>
+      <c r="BQ72" s="147"/>
+      <c r="BR72" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="AL4:AW5"/>
-    <mergeCell ref="BM4:BP5"/>
-    <mergeCell ref="BQ4:BT5"/>
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="L5:Q5"/>
-    <mergeCell ref="AX4:BH5"/>
-    <mergeCell ref="BI4:BL5"/>
+    <mergeCell ref="A1:P2"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:AD1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AI1:AQ1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:E5"/>
+    <mergeCell ref="F4:Q4"/>
+    <mergeCell ref="R4:W5"/>
+    <mergeCell ref="X4:AK5"/>
     <mergeCell ref="AT1:AV2"/>
     <mergeCell ref="Q2:T2"/>
     <mergeCell ref="U2:AD2"/>
     <mergeCell ref="AE2:AH2"/>
     <mergeCell ref="AI2:AQ2"/>
     <mergeCell ref="AR1:AS2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:E5"/>
-    <mergeCell ref="F4:Q4"/>
-    <mergeCell ref="R4:W5"/>
-    <mergeCell ref="X4:AK5"/>
-    <mergeCell ref="A1:P2"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AI1:AQ1"/>
+    <mergeCell ref="AL4:AW5"/>
+    <mergeCell ref="BM4:BN5"/>
+    <mergeCell ref="BO4:BR5"/>
+    <mergeCell ref="F5:K5"/>
+    <mergeCell ref="L5:Q5"/>
+    <mergeCell ref="AX4:BH5"/>
+    <mergeCell ref="BI4:BL5"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.39370078740157483" footer="0.39370078740157483"/>
@@ -8234,76 +8239,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="13.8" customHeight="1" thickTop="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="195" t="s">
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="231" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="196"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="183"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
-      <c r="M1" s="185"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="221"/>
       <c r="N1" s="52" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="53"/>
-      <c r="Q1" s="189">
+      <c r="Q1" s="225">
         <v>45575</v>
       </c>
-      <c r="R1" s="190"/>
-      <c r="S1" s="190"/>
-      <c r="T1" s="191"/>
-      <c r="U1" s="172" t="s">
+      <c r="R1" s="226"/>
+      <c r="S1" s="226"/>
+      <c r="T1" s="227"/>
+      <c r="U1" s="196" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="173"/>
-      <c r="W1" s="163"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="165"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="187"/>
+      <c r="X1" s="188"/>
+      <c r="Y1" s="189"/>
     </row>
     <row r="2" spans="1:25" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A2" s="145"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="198" t="s">
+      <c r="A2" s="213"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="234" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="199"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="186" t="s">
+      <c r="G2" s="235"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="187"/>
-      <c r="K2" s="187"/>
-      <c r="L2" s="187"/>
-      <c r="M2" s="188"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
+      <c r="M2" s="224"/>
       <c r="N2" s="50" t="s">
         <v>1</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" s="51"/>
-      <c r="Q2" s="192" t="s">
+      <c r="Q2" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="193"/>
-      <c r="S2" s="193"/>
-      <c r="T2" s="194"/>
-      <c r="U2" s="174"/>
-      <c r="V2" s="175"/>
-      <c r="W2" s="166"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="168"/>
+      <c r="R2" s="229"/>
+      <c r="S2" s="229"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="198"/>
+      <c r="V2" s="199"/>
+      <c r="W2" s="190"/>
+      <c r="X2" s="191"/>
+      <c r="Y2" s="192"/>
     </row>
     <row r="3" spans="1:25" ht="13.8" thickTop="1"/>
     <row r="4" spans="1:25">
@@ -8905,76 +8910,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="13.8" customHeight="1" thickTop="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="195" t="s">
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="231" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="196"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="183"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
-      <c r="M1" s="185"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="221"/>
       <c r="N1" s="52" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="53"/>
-      <c r="Q1" s="189">
+      <c r="Q1" s="225">
         <v>45575</v>
       </c>
-      <c r="R1" s="190"/>
-      <c r="S1" s="190"/>
-      <c r="T1" s="191"/>
-      <c r="U1" s="172" t="s">
+      <c r="R1" s="226"/>
+      <c r="S1" s="226"/>
+      <c r="T1" s="227"/>
+      <c r="U1" s="196" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="173"/>
-      <c r="W1" s="163"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="165"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="187"/>
+      <c r="X1" s="188"/>
+      <c r="Y1" s="189"/>
     </row>
     <row r="2" spans="1:25" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A2" s="145"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="198" t="s">
+      <c r="A2" s="213"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="234" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="199"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="186" t="s">
+      <c r="G2" s="235"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="187"/>
-      <c r="K2" s="187"/>
-      <c r="L2" s="187"/>
-      <c r="M2" s="188"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
+      <c r="M2" s="224"/>
       <c r="N2" s="50" t="s">
         <v>1</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" s="51"/>
-      <c r="Q2" s="192" t="s">
+      <c r="Q2" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="193"/>
-      <c r="S2" s="193"/>
-      <c r="T2" s="194"/>
-      <c r="U2" s="174"/>
-      <c r="V2" s="175"/>
-      <c r="W2" s="166"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="168"/>
+      <c r="R2" s="229"/>
+      <c r="S2" s="229"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="198"/>
+      <c r="V2" s="199"/>
+      <c r="W2" s="190"/>
+      <c r="X2" s="191"/>
+      <c r="Y2" s="192"/>
     </row>
     <row r="3" spans="1:25" ht="13.8" thickTop="1"/>
     <row r="4" spans="1:25">
@@ -9022,8 +9027,8 @@
       <c r="F6" s="63"/>
       <c r="G6" s="62"/>
       <c r="H6" s="64"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="71"/>
@@ -9058,7 +9063,7 @@
     <row r="10" spans="1:25">
       <c r="A10" s="71"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="201" t="s">
+      <c r="C10" s="142" t="s">
         <v>116</v>
       </c>
       <c r="D10" s="63"/>
@@ -9209,15 +9214,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="W1:Y2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="Q2:T2"/>
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="U1:V2"/>
-    <mergeCell ref="W1:Y2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="Q2:T2"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
